--- a/data/output/holdings_FINAL.xlsx
+++ b/data/output/holdings_FINAL.xlsx
@@ -1,20 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Trishakti\Projects\RPA\track_stock_price\data\output\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{593DC1B6-8576-442E-A759-790485A2D372}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-3075" yWindow="-16320" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Result" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="168">
   <si>
     <t>id</t>
   </si>
@@ -136,94 +142,136 @@
     <t>lastUpdated</t>
   </si>
   <si>
-    <t>e5928bea-6243-4300-b7fb-27d3859b3a17</t>
-  </si>
-  <si>
-    <t>104dda54-a30d-4124-ada0-30a5599d457e</t>
-  </si>
-  <si>
-    <t>a900d783-5da9-423e-b017-b0055a2a0fe7</t>
-  </si>
-  <si>
-    <t>ea26a010-da85-41de-9a78-fba7a17c0d67</t>
-  </si>
-  <si>
-    <t>6e504e3a-895a-45b7-a916-bc559dbb0fcb</t>
-  </si>
-  <si>
-    <t>3ae644cd-b489-4804-b2b9-70bfbaffd0f7</t>
-  </si>
-  <si>
-    <t>9f5d6b05-4de0-47ba-81f9-38907ebf1792</t>
-  </si>
-  <si>
-    <t>404dc53d-95ab-47d8-83c6-e5885e9cc133</t>
-  </si>
-  <si>
-    <t>13825946-c752-418b-a258-7d4188df6bd6</t>
-  </si>
-  <si>
-    <t>8a095afd-739f-4098-840c-cb5daa807fc9</t>
-  </si>
-  <si>
-    <t>9d04d569-7c9f-48c6-b533-a21c7f8e8241</t>
-  </si>
-  <si>
-    <t>3dee34a1-91af-4a3d-8174-44a4fde19f08</t>
-  </si>
-  <si>
-    <t>8fc63244-1307-4875-baa0-75edf140dee3</t>
-  </si>
-  <si>
-    <t>80ead310-9443-4ff2-9d5c-20082125782d</t>
-  </si>
-  <si>
-    <t>a96c7ddc-fc89-4466-b42c-4551c61f4085</t>
-  </si>
-  <si>
-    <t>91dc9d74-0a5f-4280-8253-e89e344249d2</t>
-  </si>
-  <si>
-    <t>c68ae583-f0c6-4a93-86c6-f821d1eba6f6</t>
-  </si>
-  <si>
-    <t>7b105916-b893-49df-9af5-c10371729463</t>
-  </si>
-  <si>
-    <t>e0123f26-77ba-4973-8564-ddb3a5a68168</t>
-  </si>
-  <si>
-    <t>3feed7f0-afa1-491f-8687-b670b2fa12a6</t>
-  </si>
-  <si>
-    <t>a90d462c-db16-41d3-a590-390e31305f6c</t>
-  </si>
-  <si>
-    <t>7296a95f-5957-4043-8e9e-e7c447e88e40</t>
+    <t>033edc86-0710-4c63-9cdb-2f948597f889</t>
+  </si>
+  <si>
+    <t>1d009eed-97f4-4854-93ee-032696134bbb</t>
+  </si>
+  <si>
+    <t>b5eef2f2-2a7f-4ef4-b090-321e652165f4</t>
+  </si>
+  <si>
+    <t>df176ecd-0b9c-41dd-b202-0afc4d8914f1</t>
+  </si>
+  <si>
+    <t>4a54d280-268b-4047-89cf-8ff9774a1b7e</t>
+  </si>
+  <si>
+    <t>df2709d9-0943-4420-bc35-bf40e79f112b</t>
+  </si>
+  <si>
+    <t>131953b3-7500-4cff-a1fe-e1d6eb159bd6</t>
+  </si>
+  <si>
+    <t>8fed5e0f-6a7f-4d46-aa82-98ab8ea1ebcc</t>
+  </si>
+  <si>
+    <t>5729c4d6-93be-45ba-ba4a-8241060affba</t>
+  </si>
+  <si>
+    <t>5b5cbb43-17f3-4f02-9348-2135e827415e</t>
+  </si>
+  <si>
+    <t>18fefa21-92d2-4b8c-b210-8663ce44253f</t>
+  </si>
+  <si>
+    <t>5a56928b-9f8f-44f2-989a-b8d806b7c137</t>
+  </si>
+  <si>
+    <t>e68d0be0-880d-461b-ad53-496ffbe41d14</t>
+  </si>
+  <si>
+    <t>06f6cb27-7b4f-4f90-9599-abc7fc9b79ac</t>
+  </si>
+  <si>
+    <t>c9478196-393b-41ca-aae5-ad3d5d6b9a82</t>
+  </si>
+  <si>
+    <t>69d6dd6f-535a-432a-ad90-3c0d398e3a5a</t>
+  </si>
+  <si>
+    <t>779586ad-78d2-42af-8c3d-e224348ee035</t>
+  </si>
+  <si>
+    <t>8731a77f-b61d-4ca3-b387-5a3063d5bec4</t>
+  </si>
+  <si>
+    <t>45118d44-296d-4250-803e-2aecd3bdfda2</t>
+  </si>
+  <si>
+    <t>0ce6dc4a-afe5-4555-8d75-9896289c539c</t>
+  </si>
+  <si>
+    <t>d6c17832-fa80-4f45-9db6-3f819aa6c64f</t>
+  </si>
+  <si>
+    <t>90682b10-879c-4329-bb51-010939f1ad54</t>
+  </si>
+  <si>
+    <t>TIKA BAHADUR GOTAME</t>
+  </si>
+  <si>
+    <t>RAM CHANDRA POKHAREL</t>
+  </si>
+  <si>
+    <t>KUBER THAPA</t>
   </si>
   <si>
     <t>LAXMAN LIMBU SUBBA</t>
   </si>
   <si>
-    <t>TIKA BAHADUR GOTAME</t>
-  </si>
-  <si>
-    <t>KUBER THAPA</t>
-  </si>
-  <si>
-    <t>RAM CHANDRA POKHAREL</t>
+    <t>1301260001744740</t>
+  </si>
+  <si>
+    <t>1301140000216199</t>
+  </si>
+  <si>
+    <t>1301140000233742</t>
   </si>
   <si>
     <t>1301140000236901</t>
   </si>
   <si>
-    <t>1301260001744740</t>
-  </si>
-  <si>
-    <t>1301140000233742</t>
-  </si>
-  <si>
-    <t>1301140000216199</t>
+    <t>NPE402A00005</t>
+  </si>
+  <si>
+    <t>NPE016A00003</t>
+  </si>
+  <si>
+    <t>NPE026A00002</t>
+  </si>
+  <si>
+    <t>NPE403A00003</t>
+  </si>
+  <si>
+    <t>NPE327A00004</t>
+  </si>
+  <si>
+    <t>NPE256A00005</t>
+  </si>
+  <si>
+    <t>NPE406A00006</t>
+  </si>
+  <si>
+    <t>NPE407A00004</t>
+  </si>
+  <si>
+    <t>NPE191A00004</t>
+  </si>
+  <si>
+    <t>NPE046A00000</t>
+  </si>
+  <si>
+    <t>NPE376A00001</t>
+  </si>
+  <si>
+    <t>NPE230A00000</t>
+  </si>
+  <si>
+    <t>NPE387A00008</t>
+  </si>
+  <si>
+    <t>NPE234A00002</t>
   </si>
   <si>
     <t>NPE368A00008</t>
@@ -244,54 +292,54 @@
     <t>NPE167A00004</t>
   </si>
   <si>
-    <t>NPE327A00004</t>
-  </si>
-  <si>
     <t>NPE215A00001</t>
   </si>
   <si>
-    <t>NPE402A00005</t>
-  </si>
-  <si>
-    <t>NPE016A00003</t>
-  </si>
-  <si>
-    <t>NPE026A00002</t>
-  </si>
-  <si>
-    <t>NPE403A00003</t>
-  </si>
-  <si>
-    <t>NPE191A00004</t>
-  </si>
-  <si>
-    <t>NPE046A00000</t>
-  </si>
-  <si>
-    <t>NPE376A00001</t>
-  </si>
-  <si>
-    <t>NPE230A00000</t>
-  </si>
-  <si>
-    <t>NPE387A00008</t>
-  </si>
-  <si>
-    <t>NPE234A00002</t>
-  </si>
-  <si>
-    <t>NPE256A00005</t>
-  </si>
-  <si>
-    <t>NPE406A00006</t>
-  </si>
-  <si>
-    <t>NPE407A00004</t>
-  </si>
-  <si>
     <t xml:space="preserve"> </t>
   </si>
   <si>
+    <t>CYCL</t>
+  </si>
+  <si>
+    <t>EBL</t>
+  </si>
+  <si>
+    <t>NBL</t>
+  </si>
+  <si>
+    <t>RFPL</t>
+  </si>
+  <si>
+    <t>SHIVM</t>
+  </si>
+  <si>
+    <t>API</t>
+  </si>
+  <si>
+    <t>BHDC</t>
+  </si>
+  <si>
+    <t>HHL</t>
+  </si>
+  <si>
+    <t>AHPC</t>
+  </si>
+  <si>
+    <t>CBBL</t>
+  </si>
+  <si>
+    <t>CHDC</t>
+  </si>
+  <si>
+    <t>GBLBS</t>
+  </si>
+  <si>
+    <t>SAHAS</t>
+  </si>
+  <si>
+    <t>SHPC</t>
+  </si>
+  <si>
     <t>CGH</t>
   </si>
   <si>
@@ -310,49 +358,49 @@
     <t>OHL</t>
   </si>
   <si>
-    <t>SHIVM</t>
-  </si>
-  <si>
     <t>SJLIC</t>
   </si>
   <si>
-    <t>CYCL</t>
-  </si>
-  <si>
-    <t>EBL</t>
-  </si>
-  <si>
-    <t>NBL</t>
-  </si>
-  <si>
-    <t>RFPL</t>
-  </si>
-  <si>
-    <t>AHPC</t>
-  </si>
-  <si>
-    <t>CBBL</t>
-  </si>
-  <si>
-    <t>CHDC</t>
-  </si>
-  <si>
-    <t>GBLBS</t>
-  </si>
-  <si>
-    <t>SAHAS</t>
-  </si>
-  <si>
-    <t>SHPC</t>
-  </si>
-  <si>
-    <t>API</t>
-  </si>
-  <si>
-    <t>BHDC</t>
-  </si>
-  <si>
-    <t>HHL</t>
+    <t>CYC NEPAL LAGHUBITTA BITTIYA SANSTHA LIMITED - ORDINARY SHARE</t>
+  </si>
+  <si>
+    <t>EVEREST BANK LIMITED - ORDINARY SHARE</t>
+  </si>
+  <si>
+    <t>NEPAL BANK LIMITED - ORDINARY SHARE</t>
+  </si>
+  <si>
+    <t>RIVER FALLS POWER LIMITED - ORDINARY SHARE</t>
+  </si>
+  <si>
+    <t>SHIVAM CEMENTS LIMITED - ORDINARY SHARE</t>
+  </si>
+  <si>
+    <t>API POWER COMPANY LIMITED- ORDINARY SHARE</t>
+  </si>
+  <si>
+    <t>BINDHYABASINI HYDROPOWER DEVELOPMENT COMPANY LIMITED - ORDINARY SHARE</t>
+  </si>
+  <si>
+    <t>HIMALAYAN HYDROPOWER LIMITED - ORDINARY SHARE</t>
+  </si>
+  <si>
+    <t>ARUN VALLEY HYDROPOWER DEVELOPMENT COMPANY LIMITED - ORDINARY SHARE</t>
+  </si>
+  <si>
+    <t>CHHIMEK LAGHUBITTA BITTIYA SANSTHA  LIMITED - ORDINARY SHARE</t>
+  </si>
+  <si>
+    <t>CEDB HOLDINGS LIMITED - ORDIINARY SHARE</t>
+  </si>
+  <si>
+    <t>GRAMEEN BIKAS LAGHUBITTA BITTIYA SANSTHA LIMITED - ORDINARY SHARE</t>
+  </si>
+  <si>
+    <t>SAHAS URJA LIMITED- ORDINARY SHARE</t>
+  </si>
+  <si>
+    <t>SANIMA MAI HYDROPOWER LIMITED - ORDINARY SHARE</t>
   </si>
   <si>
     <t>CHANDRAGIRI HILLS LIMITED - ORDINARY SHARE</t>
@@ -373,49 +421,28 @@
     <t>ORIENTAL HOTEL LIMITED - ORDINARY SHARE</t>
   </si>
   <si>
-    <t>SHIVAM CEMENTS LIMITED - ORDINARY SHARE</t>
-  </si>
-  <si>
     <t>SURYAJYOTI LIFE INSURANCE COMPANY LIMITED - ORDINARY SHARE</t>
   </si>
   <si>
-    <t>CYC NEPAL LAGHUBITTA BITTIYA SANSTHA LIMITED - ORDINARY SHARE</t>
-  </si>
-  <si>
-    <t>EVEREST BANK LIMITED - ORDINARY SHARE</t>
-  </si>
-  <si>
-    <t>NEPAL BANK LIMITED - ORDINARY SHARE</t>
-  </si>
-  <si>
-    <t>RIVER FALLS POWER LIMITED - ORDINARY SHARE</t>
-  </si>
-  <si>
-    <t>ARUN VALLEY HYDROPOWER DEVELOPMENT COMPANY LIMITED - ORDINARY SHARE</t>
-  </si>
-  <si>
-    <t>CHHIMEK LAGHUBITTA BITTIYA SANSTHA  LIMITED - ORDINARY SHARE</t>
-  </si>
-  <si>
-    <t>CEDB HOLDINGS LIMITED - ORDIINARY SHARE</t>
-  </si>
-  <si>
-    <t>GRAMEEN BIKAS LAGHUBITTA BITTIYA SANSTHA LIMITED - ORDINARY SHARE</t>
-  </si>
-  <si>
-    <t>SAHAS URJA LIMITED- ORDINARY SHARE</t>
-  </si>
-  <si>
-    <t>SANIMA MAI HYDROPOWER LIMITED - ORDINARY SHARE</t>
-  </si>
-  <si>
-    <t>API POWER COMPANY LIMITED- ORDINARY SHARE</t>
-  </si>
-  <si>
-    <t>BINDHYABASINI HYDROPOWER DEVELOPMENT COMPANY LIMITED - ORDINARY SHARE</t>
-  </si>
-  <si>
-    <t>HIMALAYAN HYDROPOWER LIMITED - ORDINARY SHARE</t>
+    <t>500</t>
+  </si>
+  <si>
+    <t>2100</t>
+  </si>
+  <si>
+    <t>7000</t>
+  </si>
+  <si>
+    <t>5700</t>
+  </si>
+  <si>
+    <t>1967, 12</t>
+  </si>
+  <si>
+    <t>5500, 611</t>
+  </si>
+  <si>
+    <t>2650</t>
   </si>
   <si>
     <t>600, 2996</t>
@@ -433,28 +460,25 @@
     <t>3000, 3200</t>
   </si>
   <si>
-    <t>500</t>
-  </si>
-  <si>
-    <t>5700</t>
-  </si>
-  <si>
-    <t>5050</t>
-  </si>
-  <si>
-    <t>1967, 12</t>
-  </si>
-  <si>
-    <t>5500, 611</t>
-  </si>
-  <si>
-    <t>2650</t>
-  </si>
-  <si>
-    <t>2100</t>
-  </si>
-  <si>
-    <t>7000</t>
+    <t>304.1957</t>
+  </si>
+  <si>
+    <t>300.8866</t>
+  </si>
+  <si>
+    <t>439.5169</t>
+  </si>
+  <si>
+    <t>286.1583</t>
+  </si>
+  <si>
+    <t>2403.3708, 2542.5746</t>
+  </si>
+  <si>
+    <t>672.7085, 549.1668</t>
+  </si>
+  <si>
+    <t>496.3731</t>
   </si>
   <si>
     <t>862.7329, 906.1706</t>
@@ -472,68 +496,41 @@
     <t>570.5232, 576.8766</t>
   </si>
   <si>
-    <t>304.1957</t>
-  </si>
-  <si>
-    <t>286.1583</t>
-  </si>
-  <si>
-    <t>985.5959</t>
-  </si>
-  <si>
-    <t>2403.3708, 2542.5746</t>
-  </si>
-  <si>
-    <t>672.7085, 549.1668</t>
-  </si>
-  <si>
-    <t>496.3731</t>
-  </si>
-  <si>
-    <t>300.8866</t>
-  </si>
-  <si>
-    <t>439.5169</t>
+    <t>ON-MARKET</t>
   </si>
   <si>
     <t>ON-MARKET, ON-MARKET</t>
   </si>
   <si>
+    <t>ON-MARKET, BO-BO/FAMILY TRANSFER</t>
+  </si>
+  <si>
     <t>ON-MARKET, ON-MARKET, ON-MARKET</t>
   </si>
   <si>
-    <t>ON-MARKET</t>
-  </si>
-  <si>
-    <t>ON-MARKET, BO-BO/FAMILY TRANSFER</t>
-  </si>
-  <si>
     <t>YES</t>
   </si>
   <si>
+    <t>20240825397</t>
+  </si>
+  <si>
+    <t>20250328769</t>
+  </si>
+  <si>
+    <t>KT188844</t>
+  </si>
+  <si>
     <t>LL284136</t>
   </si>
   <si>
-    <t>20240825397</t>
-  </si>
-  <si>
-    <t>KT188844</t>
-  </si>
-  <si>
-    <t>20250328769</t>
-  </si>
-  <si>
-    <t>2025-11-25 10:47:33</t>
+    <t>2025-11-26 03:01:16</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
-  </numFmts>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -587,7 +584,7 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -597,13 +594,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -641,7 +646,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -675,6 +680,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -709,9 +715,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -884,14 +891,54 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AZ23"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="1" max="52" width="18.7109375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="34.87890625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.17578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.87890625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.29296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.05859375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.64453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.64453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.1171875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.17578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.05859375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.46875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="6.29296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="72.17578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="21" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="8.52734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="16.234375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="19.41015625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="25.17578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="17.1171875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.1171875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="33.703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="12.87890625" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="12.64453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.76171875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="20.29296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="23.76171875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="15.9375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="13.703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="7.703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="12.17578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="23.234375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="7.703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="6" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="11.17578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="21.87890625" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="11.76171875" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="18.46875" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="17.52734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="52" width="18.703125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:40">
+    <row r="1" spans="1:40" x14ac:dyDescent="0.5">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1013,7 +1060,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:40">
+    <row r="2" spans="1:40" x14ac:dyDescent="0.5">
       <c r="A2" s="1" t="s">
         <v>40</v>
       </c>
@@ -1021,22 +1068,22 @@
         <v>62</v>
       </c>
       <c r="C2" s="1">
-        <v>236901</v>
+        <v>1744740</v>
       </c>
       <c r="D2" s="1">
-        <v>11400</v>
+        <v>12600</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>66</v>
       </c>
       <c r="F2" s="1">
-        <v>3596</v>
+        <v>13</v>
       </c>
       <c r="G2" s="1">
         <v>0</v>
       </c>
       <c r="H2" s="1">
-        <v>3596</v>
+        <v>13</v>
       </c>
       <c r="I2" s="1">
         <v>0</v>
@@ -1060,82 +1107,79 @@
         <v>113</v>
       </c>
       <c r="P2" s="1">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q2" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R2" s="1">
-        <v>0</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>147</v>
+        <v>1300</v>
+      </c>
+      <c r="S2" s="1">
+        <v>0</v>
+      </c>
+      <c r="T2" s="1">
+        <v>0</v>
       </c>
       <c r="U2" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V2" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="W2" s="1" t="s">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="X2" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="Y2" s="1">
         <v>0</v>
       </c>
       <c r="Z2" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="AA2" s="1">
-        <v>3232526.8576</v>
+        <v>0</v>
       </c>
       <c r="AB2" s="1">
-        <v>3596</v>
+        <v>0</v>
       </c>
       <c r="AC2" s="1">
-        <v>3232526.8576</v>
+        <v>1300</v>
       </c>
       <c r="AD2" s="1">
-        <v>898.9229303670745</v>
+        <v>100</v>
       </c>
       <c r="AE2" s="1">
-        <v>884</v>
+        <v>1505</v>
       </c>
       <c r="AF2" s="1">
-        <v>3178864</v>
+        <v>19565</v>
       </c>
       <c r="AG2" s="1">
-        <v>9536.592000000001</v>
+        <v>58.695</v>
       </c>
       <c r="AH2" s="1">
-        <v>476.8296</v>
+        <v>2.9347500000000002</v>
       </c>
       <c r="AI2" s="1">
         <v>25</v>
       </c>
       <c r="AJ2" s="1">
-        <v>63701.27919999976</v>
+        <v>-18178.37025</v>
       </c>
       <c r="AK2" s="1">
-        <v>4777.595939999982</v>
+        <v>-1363.3777687500001</v>
       </c>
       <c r="AL2" s="1">
-        <v>-68478.88</v>
+        <v>19541.75</v>
       </c>
       <c r="AM2" s="1">
-        <v>-2.12</v>
+        <v>1503.21</v>
       </c>
       <c r="AN2" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
-    <row r="3" spans="1:40">
+    <row r="3" spans="1:40" x14ac:dyDescent="0.5">
       <c r="A3" s="1" t="s">
         <v>41</v>
       </c>
@@ -1143,22 +1187,22 @@
         <v>62</v>
       </c>
       <c r="C3" s="1">
-        <v>236901</v>
+        <v>1744740</v>
       </c>
       <c r="D3" s="1">
-        <v>11400</v>
+        <v>12600</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>66</v>
       </c>
       <c r="F3" s="1">
-        <v>11641</v>
+        <v>10</v>
       </c>
       <c r="G3" s="1">
         <v>0</v>
       </c>
       <c r="H3" s="1">
-        <v>11641</v>
+        <v>10</v>
       </c>
       <c r="I3" s="1">
         <v>0</v>
@@ -1182,13 +1226,13 @@
         <v>114</v>
       </c>
       <c r="P3" s="1">
-        <v>33241</v>
+        <v>210</v>
       </c>
       <c r="Q3" s="1">
-        <v>256.02</v>
+        <v>642.69000000000005</v>
       </c>
       <c r="R3" s="1">
-        <v>8510258.82</v>
+        <v>134964.14000000001</v>
       </c>
       <c r="S3" s="1">
         <v>0</v>
@@ -1203,13 +1247,13 @@
         <v>0</v>
       </c>
       <c r="X3" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="Y3" s="1">
         <v>0</v>
       </c>
       <c r="Z3" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="AA3" s="1">
         <v>0</v>
@@ -1218,43 +1262,43 @@
         <v>0</v>
       </c>
       <c r="AC3" s="1">
-        <v>2980328.82</v>
+        <v>6426.9000000000005</v>
       </c>
       <c r="AD3" s="1">
-        <v>256.02</v>
+        <v>642.69000000000005</v>
       </c>
       <c r="AE3" s="1">
-        <v>228.5</v>
+        <v>657</v>
       </c>
       <c r="AF3" s="1">
-        <v>2659968.5</v>
+        <v>6570</v>
       </c>
       <c r="AG3" s="1">
-        <v>7979.9055</v>
+        <v>19.71</v>
       </c>
       <c r="AH3" s="1">
-        <v>398.995275</v>
+        <v>0.98549999999999993</v>
       </c>
       <c r="AI3" s="1">
         <v>25</v>
       </c>
       <c r="AJ3" s="1">
-        <v>328764.2207749998</v>
+        <v>-97.404499999999643</v>
       </c>
       <c r="AK3" s="1">
-        <v>24657.31655812499</v>
+        <v>-7.3053374999999727</v>
       </c>
       <c r="AL3" s="1">
-        <v>-353421.54</v>
+        <v>104.71</v>
       </c>
       <c r="AM3" s="1">
-        <v>-11.86</v>
+        <v>1.63</v>
       </c>
       <c r="AN3" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
-    <row r="4" spans="1:40">
+    <row r="4" spans="1:40" x14ac:dyDescent="0.5">
       <c r="A4" s="1" t="s">
         <v>42</v>
       </c>
@@ -1262,22 +1306,22 @@
         <v>62</v>
       </c>
       <c r="C4" s="1">
-        <v>236901</v>
+        <v>1744740</v>
       </c>
       <c r="D4" s="1">
-        <v>11400</v>
+        <v>12600</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>66</v>
       </c>
       <c r="F4" s="1">
-        <v>3200</v>
+        <v>500</v>
       </c>
       <c r="G4" s="1">
         <v>0</v>
       </c>
       <c r="H4" s="1">
-        <v>3200</v>
+        <v>500</v>
       </c>
       <c r="I4" s="1">
         <v>0</v>
@@ -1301,82 +1345,82 @@
         <v>115</v>
       </c>
       <c r="P4" s="1">
-        <v>33241</v>
+        <v>210</v>
       </c>
       <c r="Q4" s="1">
-        <v>256.02</v>
+        <v>642.69000000000005</v>
       </c>
       <c r="R4" s="1">
-        <v>8510258.82</v>
+        <v>134964.14000000001</v>
       </c>
       <c r="S4" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="T4" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="U4" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V4" s="1" t="b">
         <v>1</v>
       </c>
       <c r="W4" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="X4" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="Y4" s="1">
         <v>0</v>
       </c>
       <c r="Z4" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="AA4" s="1">
-        <v>1209353.92</v>
+        <v>152097.85</v>
       </c>
       <c r="AB4" s="1">
-        <v>3200</v>
+        <v>500</v>
       </c>
       <c r="AC4" s="1">
-        <v>1209353.92</v>
+        <v>152097.85</v>
       </c>
       <c r="AD4" s="1">
-        <v>377.9231</v>
+        <v>304.19569999999999</v>
       </c>
       <c r="AE4" s="1">
-        <v>388.9</v>
+        <v>244</v>
       </c>
       <c r="AF4" s="1">
-        <v>1244480</v>
+        <v>122000</v>
       </c>
       <c r="AG4" s="1">
-        <v>3733.44</v>
+        <v>366</v>
       </c>
       <c r="AH4" s="1">
-        <v>186.672</v>
+        <v>18.3</v>
       </c>
       <c r="AI4" s="1">
         <v>25</v>
       </c>
       <c r="AJ4" s="1">
-        <v>-31180.96800000011</v>
+        <v>30507.149999999991</v>
       </c>
       <c r="AK4" s="1">
-        <v>-2338.572600000008</v>
+        <v>2288.0362500000001</v>
       </c>
       <c r="AL4" s="1">
-        <v>33519.54</v>
+        <v>-32795.19</v>
       </c>
       <c r="AM4" s="1">
-        <v>2.77</v>
+        <v>-21.56</v>
       </c>
       <c r="AN4" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
-    <row r="5" spans="1:40">
+    <row r="5" spans="1:40" x14ac:dyDescent="0.5">
       <c r="A5" s="1" t="s">
         <v>43</v>
       </c>
@@ -1384,22 +1428,22 @@
         <v>62</v>
       </c>
       <c r="C5" s="1">
-        <v>236901</v>
+        <v>1744740</v>
       </c>
       <c r="D5" s="1">
-        <v>11400</v>
+        <v>12600</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>66</v>
       </c>
       <c r="F5" s="1">
-        <v>2416</v>
+        <v>10</v>
       </c>
       <c r="G5" s="1">
         <v>0</v>
       </c>
       <c r="H5" s="1">
-        <v>2416</v>
+        <v>10</v>
       </c>
       <c r="I5" s="1">
         <v>0</v>
@@ -1423,82 +1467,79 @@
         <v>116</v>
       </c>
       <c r="P5" s="1">
-        <v>33241</v>
+        <v>10</v>
       </c>
       <c r="Q5" s="1">
-        <v>256.02</v>
+        <v>100</v>
       </c>
       <c r="R5" s="1">
-        <v>8510258.82</v>
-      </c>
-      <c r="S5" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="T5" s="1" t="s">
-        <v>149</v>
+        <v>1000</v>
+      </c>
+      <c r="S5" s="1">
+        <v>0</v>
+      </c>
+      <c r="T5" s="1">
+        <v>0</v>
       </c>
       <c r="U5" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V5" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="W5" s="1" t="s">
-        <v>161</v>
+        <v>0</v>
       </c>
       <c r="X5" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="Y5" s="1">
         <v>0</v>
       </c>
       <c r="Z5" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="AA5" s="1">
-        <v>1102708.0054</v>
+        <v>0</v>
       </c>
       <c r="AB5" s="1">
-        <v>2416</v>
+        <v>0</v>
       </c>
       <c r="AC5" s="1">
-        <v>1102708.0054</v>
+        <v>1000</v>
       </c>
       <c r="AD5" s="1">
-        <v>456.4188764072848</v>
+        <v>100</v>
       </c>
       <c r="AE5" s="1">
-        <v>480</v>
+        <v>358</v>
       </c>
       <c r="AF5" s="1">
-        <v>1159680</v>
+        <v>3580</v>
       </c>
       <c r="AG5" s="1">
-        <v>3479.04</v>
+        <v>10.74</v>
       </c>
       <c r="AH5" s="1">
-        <v>173.952</v>
+        <v>0.53699999999999992</v>
       </c>
       <c r="AI5" s="1">
         <v>25</v>
       </c>
       <c r="AJ5" s="1">
-        <v>-53294.00260000001</v>
+        <v>-2543.723</v>
       </c>
       <c r="AK5" s="1">
-        <v>-3997.050195</v>
+        <v>-190.779225</v>
       </c>
       <c r="AL5" s="1">
-        <v>57291.05</v>
+        <v>2734.5</v>
       </c>
       <c r="AM5" s="1">
-        <v>5.2</v>
+        <v>273.45</v>
       </c>
       <c r="AN5" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
-    <row r="6" spans="1:40">
+    <row r="6" spans="1:40" x14ac:dyDescent="0.5">
       <c r="A6" s="1" t="s">
         <v>44</v>
       </c>
@@ -1506,22 +1547,22 @@
         <v>62</v>
       </c>
       <c r="C6" s="1">
-        <v>236901</v>
+        <v>1744740</v>
       </c>
       <c r="D6" s="1">
-        <v>11400</v>
+        <v>12600</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>66</v>
       </c>
       <c r="F6" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
       </c>
       <c r="H6" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I6" s="1">
         <v>0</v>
@@ -1545,13 +1586,13 @@
         <v>117</v>
       </c>
       <c r="P6" s="1">
-        <v>11000</v>
+        <v>108</v>
       </c>
       <c r="Q6" s="1">
-        <v>274.33</v>
+        <v>520.57000000000005</v>
       </c>
       <c r="R6" s="1">
-        <v>3017632.8</v>
+        <v>56221.96</v>
       </c>
       <c r="S6" s="1">
         <v>0</v>
@@ -1566,13 +1607,13 @@
         <v>0</v>
       </c>
       <c r="X6" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="Y6" s="1">
         <v>0</v>
       </c>
       <c r="Z6" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="AA6" s="1">
         <v>0</v>
@@ -1581,66 +1622,66 @@
         <v>0</v>
       </c>
       <c r="AC6" s="1">
-        <v>1920.31</v>
+        <v>4164.5600000000004</v>
       </c>
       <c r="AD6" s="1">
-        <v>274.33</v>
+        <v>520.57000000000005</v>
       </c>
       <c r="AE6" s="1">
-        <v>247.9</v>
+        <v>617</v>
       </c>
       <c r="AF6" s="1">
-        <v>1735.3</v>
+        <v>4936</v>
       </c>
       <c r="AG6" s="1">
-        <v>5.2059</v>
+        <v>14.808</v>
       </c>
       <c r="AH6" s="1">
-        <v>0.2602949999999999</v>
+        <v>0.74039999999999995</v>
       </c>
       <c r="AI6" s="1">
         <v>25</v>
       </c>
       <c r="AJ6" s="1">
-        <v>215.476195</v>
+        <v>-730.89159999999993</v>
       </c>
       <c r="AK6" s="1">
-        <v>16.160714625</v>
+        <v>-54.816869999999987</v>
       </c>
       <c r="AL6" s="1">
-        <v>-231.64</v>
+        <v>785.71</v>
       </c>
       <c r="AM6" s="1">
-        <v>-12.06</v>
+        <v>18.87</v>
       </c>
       <c r="AN6" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
-    <row r="7" spans="1:40">
+    <row r="7" spans="1:40" x14ac:dyDescent="0.5">
       <c r="A7" s="1" t="s">
         <v>45</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C7" s="1">
-        <v>236901</v>
+        <v>216199</v>
       </c>
       <c r="D7" s="1">
         <v>11400</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F7" s="1">
-        <v>3330</v>
+        <v>2100</v>
       </c>
       <c r="G7" s="1">
         <v>0</v>
       </c>
       <c r="H7" s="1">
-        <v>3330</v>
+        <v>2100</v>
       </c>
       <c r="I7" s="1">
         <v>0</v>
@@ -1664,105 +1705,105 @@
         <v>118</v>
       </c>
       <c r="P7" s="1">
-        <v>11000</v>
+        <v>12000</v>
       </c>
       <c r="Q7" s="1">
-        <v>274.33</v>
+        <v>316.8</v>
       </c>
       <c r="R7" s="1">
-        <v>3017632.8</v>
+        <v>3801551.6</v>
       </c>
       <c r="S7" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="T7" s="1" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="U7" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V7" s="1" t="b">
         <v>1</v>
       </c>
       <c r="W7" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="X7" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="Y7" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="Y7" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z7" s="1" t="s">
-        <v>165</v>
-      </c>
       <c r="AA7" s="1">
-        <v>2357395.686</v>
+        <v>631861.86</v>
       </c>
       <c r="AB7" s="1">
-        <v>3330</v>
+        <v>2100</v>
       </c>
       <c r="AC7" s="1">
-        <v>2357395.686</v>
+        <v>631861.86</v>
       </c>
       <c r="AD7" s="1">
-        <v>707.9266324324324</v>
+        <v>300.88659999999999</v>
       </c>
       <c r="AE7" s="1">
-        <v>698</v>
+        <v>285</v>
       </c>
       <c r="AF7" s="1">
-        <v>2324340</v>
+        <v>598500</v>
       </c>
       <c r="AG7" s="1">
-        <v>6973.02</v>
+        <v>1795.5</v>
       </c>
       <c r="AH7" s="1">
-        <v>348.651</v>
+        <v>89.774999999999991</v>
       </c>
       <c r="AI7" s="1">
         <v>25</v>
       </c>
       <c r="AJ7" s="1">
-        <v>40402.35699999984</v>
+        <v>35272.135000000009</v>
       </c>
       <c r="AK7" s="1">
-        <v>3030.176774999988</v>
+        <v>2645.4101250000008</v>
       </c>
       <c r="AL7" s="1">
-        <v>-43432.53</v>
+        <v>-37917.550000000003</v>
       </c>
       <c r="AM7" s="1">
-        <v>-1.84</v>
+        <v>-6</v>
       </c>
       <c r="AN7" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
-    <row r="8" spans="1:40">
+    <row r="8" spans="1:40" x14ac:dyDescent="0.5">
       <c r="A8" s="1" t="s">
         <v>46</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C8" s="1">
-        <v>236901</v>
+        <v>216199</v>
       </c>
       <c r="D8" s="1">
         <v>11400</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F8" s="1">
-        <v>6200</v>
+        <v>10</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
       </c>
       <c r="H8" s="1">
-        <v>6200</v>
+        <v>10</v>
       </c>
       <c r="I8" s="1">
         <v>0</v>
@@ -1786,105 +1827,102 @@
         <v>119</v>
       </c>
       <c r="P8" s="1">
-        <v>11000</v>
+        <v>2010</v>
       </c>
       <c r="Q8" s="1">
-        <v>274.33</v>
+        <v>572.02</v>
       </c>
       <c r="R8" s="1">
-        <v>3017632.8</v>
-      </c>
-      <c r="S8" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="T8" s="1" t="s">
-        <v>151</v>
+        <v>1149757.5900000001</v>
+      </c>
+      <c r="S8" s="1">
+        <v>0</v>
+      </c>
+      <c r="T8" s="1">
+        <v>0</v>
       </c>
       <c r="U8" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V8" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="W8" s="1" t="s">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="X8" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="Y8" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="Y8" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z8" s="1" t="s">
-        <v>165</v>
-      </c>
       <c r="AA8" s="1">
-        <v>3557574.72</v>
+        <v>0</v>
       </c>
       <c r="AB8" s="1">
-        <v>6200</v>
+        <v>0</v>
       </c>
       <c r="AC8" s="1">
-        <v>3557574.72</v>
+        <v>5720.2</v>
       </c>
       <c r="AD8" s="1">
-        <v>573.8023741935483</v>
+        <v>572.02</v>
       </c>
       <c r="AE8" s="1">
-        <v>617</v>
+        <v>499</v>
       </c>
       <c r="AF8" s="1">
-        <v>3825400</v>
+        <v>4990</v>
       </c>
       <c r="AG8" s="1">
-        <v>11476.2</v>
+        <v>14.97</v>
       </c>
       <c r="AH8" s="1">
-        <v>573.8099999999999</v>
+        <v>0.74849999999999994</v>
       </c>
       <c r="AI8" s="1">
         <v>25</v>
       </c>
       <c r="AJ8" s="1">
-        <v>-255750.27</v>
+        <v>770.91849999999977</v>
       </c>
       <c r="AK8" s="1">
-        <v>-19181.27025</v>
+        <v>57.818887499999981</v>
       </c>
       <c r="AL8" s="1">
-        <v>274931.54</v>
+        <v>-828.74</v>
       </c>
       <c r="AM8" s="1">
-        <v>7.73</v>
+        <v>-14.49</v>
       </c>
       <c r="AN8" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
-    <row r="9" spans="1:40">
+    <row r="9" spans="1:40" x14ac:dyDescent="0.5">
       <c r="A9" s="1" t="s">
         <v>47</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C9" s="1">
-        <v>236901</v>
+        <v>216199</v>
       </c>
       <c r="D9" s="1">
         <v>11400</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F9" s="1">
-        <v>2800</v>
+        <v>7000</v>
       </c>
       <c r="G9" s="1">
         <v>0</v>
       </c>
       <c r="H9" s="1">
-        <v>2800</v>
+        <v>7000</v>
       </c>
       <c r="I9" s="1">
         <v>0</v>
@@ -1908,102 +1946,105 @@
         <v>120</v>
       </c>
       <c r="P9" s="1">
-        <v>3300</v>
+        <v>2010</v>
       </c>
       <c r="Q9" s="1">
-        <v>421.87</v>
+        <v>572.02</v>
       </c>
       <c r="R9" s="1">
-        <v>1392162.84</v>
-      </c>
-      <c r="S9" s="1">
-        <v>0</v>
-      </c>
-      <c r="T9" s="1">
-        <v>0</v>
+        <v>1149757.5900000001</v>
+      </c>
+      <c r="S9" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="T9" s="1" t="s">
+        <v>148</v>
       </c>
       <c r="U9" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V9" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="W9" s="1" t="s">
+        <v>158</v>
       </c>
       <c r="X9" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="Y9" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z9" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="Y9" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z9" s="1" t="s">
-        <v>165</v>
-      </c>
       <c r="AA9" s="1">
-        <v>0</v>
+        <v>3076618.3</v>
       </c>
       <c r="AB9" s="1">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="AC9" s="1">
-        <v>1181236</v>
+        <v>3076618.3</v>
       </c>
       <c r="AD9" s="1">
-        <v>421.87</v>
+        <v>439.51690000000002</v>
       </c>
       <c r="AE9" s="1">
-        <v>469</v>
+        <v>336.5</v>
       </c>
       <c r="AF9" s="1">
-        <v>1313200</v>
+        <v>2355500</v>
       </c>
       <c r="AG9" s="1">
-        <v>3939.6</v>
+        <v>7066.5</v>
       </c>
       <c r="AH9" s="1">
-        <v>196.98</v>
+        <v>353.32499999999999</v>
       </c>
       <c r="AI9" s="1">
         <v>25</v>
       </c>
       <c r="AJ9" s="1">
-        <v>-127802.4199999999</v>
+        <v>728563.12500000047</v>
       </c>
       <c r="AK9" s="1">
-        <v>-9585.181499999993</v>
+        <v>54642.234375000036</v>
       </c>
       <c r="AL9" s="1">
-        <v>137387.6</v>
+        <v>-783205.36</v>
       </c>
       <c r="AM9" s="1">
-        <v>11.63</v>
+        <v>-25.46</v>
       </c>
       <c r="AN9" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
-    <row r="10" spans="1:40">
+    <row r="10" spans="1:40" x14ac:dyDescent="0.5">
       <c r="A10" s="1" t="s">
         <v>48</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C10" s="1">
-        <v>1744740</v>
+        <v>233742</v>
       </c>
       <c r="D10" s="1">
-        <v>12600</v>
+        <v>11400</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F10" s="1">
-        <v>13</v>
+        <v>44250</v>
       </c>
       <c r="G10" s="1">
         <v>0</v>
       </c>
       <c r="H10" s="1">
-        <v>13</v>
+        <v>9250</v>
       </c>
       <c r="I10" s="1">
         <v>0</v>
@@ -2015,7 +2056,7 @@
         <v>0</v>
       </c>
       <c r="L10" s="1">
-        <v>0</v>
+        <v>35000</v>
       </c>
       <c r="M10" s="1" t="s">
         <v>91</v>
@@ -2027,102 +2068,105 @@
         <v>121</v>
       </c>
       <c r="P10" s="1">
-        <v>13</v>
+        <v>38550</v>
       </c>
       <c r="Q10" s="1">
-        <v>100</v>
+        <v>295.27</v>
       </c>
       <c r="R10" s="1">
-        <v>1300</v>
-      </c>
-      <c r="S10" s="1">
-        <v>0</v>
-      </c>
-      <c r="T10" s="1">
-        <v>0</v>
+        <v>11382579.9</v>
+      </c>
+      <c r="S10" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="T10" s="1" t="s">
+        <v>149</v>
       </c>
       <c r="U10" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V10" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="W10" s="1" t="s">
+        <v>158</v>
       </c>
       <c r="X10" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="Y10" s="1">
         <v>0</v>
       </c>
       <c r="Z10" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AA10" s="1">
-        <v>0</v>
+        <v>1631102.31</v>
       </c>
       <c r="AB10" s="1">
-        <v>0</v>
+        <v>5700</v>
       </c>
       <c r="AC10" s="1">
-        <v>1300</v>
+        <v>13013760.810000001</v>
       </c>
       <c r="AD10" s="1">
-        <v>100</v>
+        <v>294.09628949152551</v>
       </c>
       <c r="AE10" s="1">
-        <v>1505</v>
+        <v>284.89999999999998</v>
       </c>
       <c r="AF10" s="1">
-        <v>19565</v>
+        <v>12606825</v>
       </c>
       <c r="AG10" s="1">
-        <v>58.695</v>
+        <v>37820.474999999999</v>
       </c>
       <c r="AH10" s="1">
-        <v>2.93475</v>
+        <v>1891.0237500000001</v>
       </c>
       <c r="AI10" s="1">
         <v>25</v>
       </c>
       <c r="AJ10" s="1">
-        <v>-18178.37025</v>
+        <v>446672.30875000171</v>
       </c>
       <c r="AK10" s="1">
-        <v>-1363.37776875</v>
+        <v>33500.42315625013</v>
       </c>
       <c r="AL10" s="1">
-        <v>19541.75</v>
+        <v>-480172.73</v>
       </c>
       <c r="AM10" s="1">
-        <v>1503.21</v>
+        <v>-3.69</v>
       </c>
       <c r="AN10" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
-    <row r="11" spans="1:40">
+    <row r="11" spans="1:40" x14ac:dyDescent="0.5">
       <c r="A11" s="1" t="s">
         <v>49</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C11" s="1">
-        <v>1744740</v>
+        <v>233742</v>
       </c>
       <c r="D11" s="1">
-        <v>12600</v>
+        <v>11400</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F11" s="1">
-        <v>10</v>
+        <v>10650</v>
       </c>
       <c r="G11" s="1">
         <v>0</v>
       </c>
       <c r="H11" s="1">
-        <v>10</v>
+        <v>3550</v>
       </c>
       <c r="I11" s="1">
         <v>0</v>
@@ -2134,7 +2178,7 @@
         <v>0</v>
       </c>
       <c r="L11" s="1">
-        <v>0</v>
+        <v>7100</v>
       </c>
       <c r="M11" s="1" t="s">
         <v>91</v>
@@ -2146,13 +2190,13 @@
         <v>122</v>
       </c>
       <c r="P11" s="1">
-        <v>210</v>
+        <v>12150</v>
       </c>
       <c r="Q11" s="1">
-        <v>642.6900000000001</v>
+        <v>983.53</v>
       </c>
       <c r="R11" s="1">
-        <v>134964.14</v>
+        <v>11949900.199999999</v>
       </c>
       <c r="S11" s="1">
         <v>0</v>
@@ -2167,13 +2211,13 @@
         <v>0</v>
       </c>
       <c r="X11" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="Y11" s="1">
         <v>0</v>
       </c>
       <c r="Z11" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AA11" s="1">
         <v>0</v>
@@ -2182,66 +2226,66 @@
         <v>0</v>
       </c>
       <c r="AC11" s="1">
-        <v>6426.900000000001</v>
+        <v>10474594.5</v>
       </c>
       <c r="AD11" s="1">
-        <v>642.6900000000001</v>
+        <v>983.53</v>
       </c>
       <c r="AE11" s="1">
-        <v>657</v>
+        <v>1025.0999999999999</v>
       </c>
       <c r="AF11" s="1">
-        <v>6570</v>
+        <v>10917315</v>
       </c>
       <c r="AG11" s="1">
-        <v>19.71</v>
+        <v>32751.945</v>
       </c>
       <c r="AH11" s="1">
-        <v>0.9854999999999999</v>
+        <v>1637.59725</v>
       </c>
       <c r="AI11" s="1">
         <v>25</v>
       </c>
       <c r="AJ11" s="1">
-        <v>-97.40449999999964</v>
+        <v>-408305.9577499982</v>
       </c>
       <c r="AK11" s="1">
-        <v>-7.305337499999973</v>
+        <v>-30622.946831249861</v>
       </c>
       <c r="AL11" s="1">
-        <v>104.71</v>
+        <v>438928.9</v>
       </c>
       <c r="AM11" s="1">
-        <v>1.63</v>
+        <v>4.1900000000000004</v>
       </c>
       <c r="AN11" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
-    <row r="12" spans="1:40">
+    <row r="12" spans="1:40" x14ac:dyDescent="0.5">
       <c r="A12" s="1" t="s">
         <v>50</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C12" s="1">
-        <v>1744740</v>
+        <v>233742</v>
       </c>
       <c r="D12" s="1">
-        <v>12600</v>
+        <v>11400</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F12" s="1">
-        <v>500</v>
+        <v>2189</v>
       </c>
       <c r="G12" s="1">
         <v>0</v>
       </c>
       <c r="H12" s="1">
-        <v>500</v>
+        <v>2189</v>
       </c>
       <c r="I12" s="1">
         <v>0</v>
@@ -2268,102 +2312,102 @@
         <v>210</v>
       </c>
       <c r="Q12" s="1">
-        <v>642.6900000000001</v>
+        <v>2543.42</v>
       </c>
       <c r="R12" s="1">
-        <v>134964.14</v>
+        <v>534117.81999999995</v>
       </c>
       <c r="S12" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="T12" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="U12" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V12" s="1" t="b">
         <v>1</v>
       </c>
       <c r="W12" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="X12" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="X12" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="Y12" s="1">
         <v>0</v>
       </c>
       <c r="Z12" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AA12" s="1">
-        <v>152097.85</v>
+        <v>4757941.2588000009</v>
       </c>
       <c r="AB12" s="1">
-        <v>500</v>
+        <v>1979</v>
       </c>
       <c r="AC12" s="1">
-        <v>152097.85</v>
+        <v>5292059.4588000011</v>
       </c>
       <c r="AD12" s="1">
-        <v>304.1957</v>
+        <v>2417.5694192782098</v>
       </c>
       <c r="AE12" s="1">
-        <v>244</v>
+        <v>2390</v>
       </c>
       <c r="AF12" s="1">
-        <v>122000</v>
+        <v>5231710</v>
       </c>
       <c r="AG12" s="1">
-        <v>366</v>
+        <v>15695.13</v>
       </c>
       <c r="AH12" s="1">
-        <v>18.3</v>
+        <v>784.75649999999996</v>
       </c>
       <c r="AI12" s="1">
         <v>25</v>
       </c>
       <c r="AJ12" s="1">
-        <v>30507.14999999999</v>
+        <v>76854.345300001092</v>
       </c>
       <c r="AK12" s="1">
-        <v>2288.03625</v>
+        <v>5764.0758975000817</v>
       </c>
       <c r="AL12" s="1">
-        <v>-32795.19</v>
+        <v>-82618.42</v>
       </c>
       <c r="AM12" s="1">
-        <v>-21.56</v>
+        <v>-1.56</v>
       </c>
       <c r="AN12" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
-    <row r="13" spans="1:40">
+    <row r="13" spans="1:40" x14ac:dyDescent="0.5">
       <c r="A13" s="1" t="s">
         <v>51</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C13" s="1">
-        <v>1744740</v>
+        <v>233742</v>
       </c>
       <c r="D13" s="1">
-        <v>12600</v>
+        <v>11400</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F13" s="1">
-        <v>10</v>
+        <v>3000</v>
       </c>
       <c r="G13" s="1">
         <v>0</v>
       </c>
       <c r="H13" s="1">
-        <v>10</v>
+        <v>3000</v>
       </c>
       <c r="I13" s="1">
         <v>0</v>
@@ -2387,13 +2431,13 @@
         <v>124</v>
       </c>
       <c r="P13" s="1">
-        <v>10</v>
+        <v>3730</v>
       </c>
       <c r="Q13" s="1">
-        <v>100</v>
+        <v>770.44</v>
       </c>
       <c r="R13" s="1">
-        <v>1000</v>
+        <v>2873726.65</v>
       </c>
       <c r="S13" s="1">
         <v>0</v>
@@ -2408,13 +2452,13 @@
         <v>0</v>
       </c>
       <c r="X13" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="Y13" s="1">
         <v>0</v>
       </c>
       <c r="Z13" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AA13" s="1">
         <v>0</v>
@@ -2423,162 +2467,165 @@
         <v>0</v>
       </c>
       <c r="AC13" s="1">
-        <v>1000</v>
+        <v>2311320</v>
       </c>
       <c r="AD13" s="1">
-        <v>100</v>
+        <v>770.44</v>
       </c>
       <c r="AE13" s="1">
-        <v>358</v>
+        <v>0</v>
       </c>
       <c r="AF13" s="1">
-        <v>3580</v>
+        <v>0</v>
       </c>
       <c r="AG13" s="1">
-        <v>10.74</v>
+        <v>0</v>
       </c>
       <c r="AH13" s="1">
-        <v>0.5369999999999999</v>
+        <v>0</v>
       </c>
       <c r="AI13" s="1">
         <v>25</v>
       </c>
       <c r="AJ13" s="1">
-        <v>-2543.723</v>
+        <v>2311345</v>
       </c>
       <c r="AK13" s="1">
-        <v>-190.779225</v>
+        <v>173350.875</v>
       </c>
       <c r="AL13" s="1">
-        <v>2734.5</v>
+        <v>-2484695.88</v>
       </c>
       <c r="AM13" s="1">
-        <v>273.45</v>
+        <v>-107.5</v>
       </c>
       <c r="AN13" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
-    <row r="14" spans="1:40">
+    <row r="14" spans="1:40" x14ac:dyDescent="0.5">
       <c r="A14" s="1" t="s">
         <v>52</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C14" s="1">
-        <v>1744740</v>
+        <v>233742</v>
       </c>
       <c r="D14" s="1">
-        <v>12600</v>
+        <v>11400</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F14" s="1">
-        <v>8</v>
+        <v>16767</v>
       </c>
       <c r="G14" s="1">
         <v>0</v>
       </c>
       <c r="H14" s="1">
-        <v>8</v>
+        <v>6111</v>
       </c>
       <c r="I14" s="1">
         <v>0</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K14" s="1">
         <v>0</v>
       </c>
       <c r="L14" s="1">
-        <v>0</v>
+        <v>10656</v>
       </c>
       <c r="M14" s="1" t="s">
         <v>91</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="P14" s="1">
-        <v>108</v>
+        <v>12446</v>
       </c>
       <c r="Q14" s="1">
-        <v>520.5700000000001</v>
+        <v>593.01</v>
       </c>
       <c r="R14" s="1">
-        <v>56221.96</v>
-      </c>
-      <c r="S14" s="1">
-        <v>0</v>
-      </c>
-      <c r="T14" s="1">
-        <v>0</v>
+        <v>7380609.1799999997</v>
+      </c>
+      <c r="S14" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="T14" s="1" t="s">
+        <v>151</v>
       </c>
       <c r="U14" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V14" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="W14" s="1" t="s">
+        <v>160</v>
       </c>
       <c r="X14" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="Y14" s="1">
         <v>0</v>
       </c>
       <c r="Z14" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AA14" s="1">
-        <v>0</v>
+        <v>4035437.6647999999</v>
       </c>
       <c r="AB14" s="1">
-        <v>0</v>
+        <v>6111</v>
       </c>
       <c r="AC14" s="1">
-        <v>4164.56</v>
+        <v>10354552.2248</v>
       </c>
       <c r="AD14" s="1">
-        <v>520.5700000000001</v>
+        <v>617.5554496809209</v>
       </c>
       <c r="AE14" s="1">
-        <v>617</v>
+        <v>567.9</v>
       </c>
       <c r="AF14" s="1">
-        <v>4936</v>
+        <v>9521979.2999999989</v>
       </c>
       <c r="AG14" s="1">
-        <v>14.808</v>
+        <v>28565.937900000001</v>
       </c>
       <c r="AH14" s="1">
-        <v>0.7403999999999999</v>
+        <v>1428.2968949999999</v>
       </c>
       <c r="AI14" s="1">
         <v>25</v>
       </c>
       <c r="AJ14" s="1">
-        <v>-730.8915999999999</v>
+        <v>862592.15959499963</v>
       </c>
       <c r="AK14" s="1">
-        <v>-54.81686999999999</v>
+        <v>64694.411969624969</v>
       </c>
       <c r="AL14" s="1">
-        <v>785.71</v>
+        <v>-927286.57</v>
       </c>
       <c r="AM14" s="1">
-        <v>18.87</v>
+        <v>-8.9600000000000009</v>
       </c>
       <c r="AN14" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
-    <row r="15" spans="1:40">
+    <row r="15" spans="1:40" x14ac:dyDescent="0.5">
       <c r="A15" s="1" t="s">
         <v>53</v>
       </c>
@@ -2595,49 +2642,49 @@
         <v>68</v>
       </c>
       <c r="F15" s="1">
-        <v>44250</v>
+        <v>16650</v>
       </c>
       <c r="G15" s="1">
         <v>0</v>
       </c>
       <c r="H15" s="1">
-        <v>9250</v>
+        <v>4600</v>
       </c>
       <c r="I15" s="1">
         <v>0</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K15" s="1">
         <v>0</v>
       </c>
       <c r="L15" s="1">
-        <v>35000</v>
+        <v>12050</v>
       </c>
       <c r="M15" s="1" t="s">
         <v>91</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="P15" s="1">
-        <v>38550</v>
+        <v>20500</v>
       </c>
       <c r="Q15" s="1">
-        <v>295.27</v>
+        <v>653.46</v>
       </c>
       <c r="R15" s="1">
-        <v>11382579.9</v>
+        <v>13395955.449999999</v>
       </c>
       <c r="S15" s="1" t="s">
         <v>140</v>
       </c>
       <c r="T15" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="U15" s="1">
         <v>1</v>
@@ -2646,212 +2693,212 @@
         <v>1</v>
       </c>
       <c r="W15" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="X15" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="X15" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="Y15" s="1">
         <v>0</v>
       </c>
       <c r="Z15" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="AA15" s="1">
-        <v>1631102.31</v>
+        <v>1315388.7150000001</v>
       </c>
       <c r="AB15" s="1">
-        <v>5700</v>
+        <v>2650</v>
       </c>
       <c r="AC15" s="1">
-        <v>13013760.81</v>
+        <v>10463828.715</v>
       </c>
       <c r="AD15" s="1">
-        <v>294.0962894915255</v>
+        <v>628.45818108108108</v>
       </c>
       <c r="AE15" s="1">
-        <v>284.9</v>
+        <v>525</v>
       </c>
       <c r="AF15" s="1">
-        <v>12606825</v>
+        <v>8741250</v>
       </c>
       <c r="AG15" s="1">
-        <v>37820.475</v>
+        <v>26223.75</v>
       </c>
       <c r="AH15" s="1">
-        <v>1891.02375</v>
+        <v>1311.1875</v>
       </c>
       <c r="AI15" s="1">
         <v>25</v>
       </c>
       <c r="AJ15" s="1">
-        <v>446672.3087500017</v>
+        <v>1750138.6525000001</v>
       </c>
       <c r="AK15" s="1">
-        <v>33500.42315625013</v>
+        <v>131260.39893749999</v>
       </c>
       <c r="AL15" s="1">
-        <v>-480172.73</v>
+        <v>-1881399.05</v>
       </c>
       <c r="AM15" s="1">
-        <v>-3.69</v>
+        <v>-17.98</v>
       </c>
       <c r="AN15" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
-    <row r="16" spans="1:40">
+    <row r="16" spans="1:40" x14ac:dyDescent="0.5">
       <c r="A16" s="1" t="s">
         <v>54</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C16" s="1">
-        <v>233742</v>
+        <v>236901</v>
       </c>
       <c r="D16" s="1">
         <v>11400</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F16" s="1">
-        <v>12150</v>
+        <v>3596</v>
       </c>
       <c r="G16" s="1">
         <v>0</v>
       </c>
       <c r="H16" s="1">
-        <v>5050</v>
+        <v>3596</v>
       </c>
       <c r="I16" s="1">
         <v>0</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K16" s="1">
         <v>0</v>
       </c>
       <c r="L16" s="1">
-        <v>7100</v>
+        <v>0</v>
       </c>
       <c r="M16" s="1" t="s">
         <v>91</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O16" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="P16" s="1">
-        <v>8100</v>
+        <v>0</v>
       </c>
       <c r="Q16" s="1">
-        <v>982.0599999999999</v>
+        <v>0</v>
       </c>
       <c r="R16" s="1">
-        <v>7954702.86</v>
+        <v>0</v>
       </c>
       <c r="S16" s="1" t="s">
         <v>141</v>
       </c>
       <c r="T16" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="U16" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V16" s="1" t="b">
         <v>1</v>
       </c>
       <c r="W16" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="X16" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="X16" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="Y16" s="1">
         <v>0</v>
       </c>
       <c r="Z16" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AA16" s="1">
-        <v>4977259.295</v>
+        <v>3232526.8576000002</v>
       </c>
       <c r="AB16" s="1">
-        <v>5050</v>
+        <v>3596</v>
       </c>
       <c r="AC16" s="1">
-        <v>11949885.295</v>
+        <v>3232526.8576000002</v>
       </c>
       <c r="AD16" s="1">
-        <v>983.529653909465</v>
+        <v>898.92293036707451</v>
       </c>
       <c r="AE16" s="1">
-        <v>1025.1</v>
+        <v>884</v>
       </c>
       <c r="AF16" s="1">
-        <v>12454965</v>
+        <v>3178864</v>
       </c>
       <c r="AG16" s="1">
-        <v>37364.895</v>
+        <v>9536.5920000000006</v>
       </c>
       <c r="AH16" s="1">
-        <v>1868.24475</v>
+        <v>476.82960000000003</v>
       </c>
       <c r="AI16" s="1">
         <v>25</v>
       </c>
       <c r="AJ16" s="1">
-        <v>-465821.5652499981</v>
+        <v>63701.279199999757</v>
       </c>
       <c r="AK16" s="1">
-        <v>-34936.61739374986</v>
+        <v>4777.595939999982</v>
       </c>
       <c r="AL16" s="1">
-        <v>500758.18</v>
+        <v>-68478.880000000005</v>
       </c>
       <c r="AM16" s="1">
-        <v>4.19</v>
+        <v>-2.12</v>
       </c>
       <c r="AN16" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
-    <row r="17" spans="1:40">
+    <row r="17" spans="1:40" x14ac:dyDescent="0.5">
       <c r="A17" s="1" t="s">
         <v>55</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C17" s="1">
-        <v>233742</v>
+        <v>236901</v>
       </c>
       <c r="D17" s="1">
         <v>11400</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F17" s="1">
-        <v>2189</v>
+        <v>11641</v>
       </c>
       <c r="G17" s="1">
         <v>0</v>
       </c>
       <c r="H17" s="1">
-        <v>2189</v>
+        <v>11641</v>
       </c>
       <c r="I17" s="1">
         <v>0</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K17" s="1">
         <v>0</v>
@@ -2863,117 +2910,114 @@
         <v>91</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O17" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="P17" s="1">
-        <v>210</v>
+        <v>33241</v>
       </c>
       <c r="Q17" s="1">
-        <v>2543.42</v>
+        <v>256.02</v>
       </c>
       <c r="R17" s="1">
-        <v>534117.8199999999</v>
-      </c>
-      <c r="S17" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="T17" s="1" t="s">
-        <v>155</v>
+        <v>8510258.8200000003</v>
+      </c>
+      <c r="S17" s="1">
+        <v>0</v>
+      </c>
+      <c r="T17" s="1">
+        <v>0</v>
       </c>
       <c r="U17" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V17" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="W17" s="1" t="s">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="X17" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="Y17" s="1">
         <v>0</v>
       </c>
       <c r="Z17" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AA17" s="1">
-        <v>4757941.258800001</v>
+        <v>0</v>
       </c>
       <c r="AB17" s="1">
-        <v>1979</v>
+        <v>0</v>
       </c>
       <c r="AC17" s="1">
-        <v>5292059.458800001</v>
+        <v>2980328.82</v>
       </c>
       <c r="AD17" s="1">
-        <v>2417.56941927821</v>
+        <v>256.02</v>
       </c>
       <c r="AE17" s="1">
-        <v>2390</v>
+        <v>228.5</v>
       </c>
       <c r="AF17" s="1">
-        <v>5231710</v>
+        <v>2659968.5</v>
       </c>
       <c r="AG17" s="1">
-        <v>15695.13</v>
+        <v>7979.9054999999998</v>
       </c>
       <c r="AH17" s="1">
-        <v>784.7565</v>
+        <v>398.99527499999999</v>
       </c>
       <c r="AI17" s="1">
         <v>25</v>
       </c>
       <c r="AJ17" s="1">
-        <v>76854.34530000109</v>
+        <v>328764.22077499982</v>
       </c>
       <c r="AK17" s="1">
-        <v>5764.075897500082</v>
+        <v>24657.316558124989</v>
       </c>
       <c r="AL17" s="1">
-        <v>-82618.42</v>
+        <v>-353421.54</v>
       </c>
       <c r="AM17" s="1">
-        <v>-1.56</v>
+        <v>-11.86</v>
       </c>
       <c r="AN17" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
-    <row r="18" spans="1:40">
+    <row r="18" spans="1:40" x14ac:dyDescent="0.5">
       <c r="A18" s="1" t="s">
         <v>56</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C18" s="1">
-        <v>233742</v>
+        <v>236901</v>
       </c>
       <c r="D18" s="1">
         <v>11400</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F18" s="1">
-        <v>3000</v>
+        <v>3200</v>
       </c>
       <c r="G18" s="1">
         <v>0</v>
       </c>
       <c r="H18" s="1">
-        <v>3000</v>
+        <v>3200</v>
       </c>
       <c r="I18" s="1">
         <v>0</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K18" s="1">
         <v>0</v>
@@ -2985,329 +3029,329 @@
         <v>91</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O18" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="P18" s="1">
-        <v>3730</v>
+        <v>33241</v>
       </c>
       <c r="Q18" s="1">
-        <v>770.4400000000001</v>
+        <v>256.02</v>
       </c>
       <c r="R18" s="1">
-        <v>2873726.65</v>
-      </c>
-      <c r="S18" s="1">
-        <v>0</v>
-      </c>
-      <c r="T18" s="1">
-        <v>0</v>
+        <v>8510258.8200000003</v>
+      </c>
+      <c r="S18" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="T18" s="1" t="s">
+        <v>154</v>
       </c>
       <c r="U18" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V18" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="W18" s="1" t="s">
+        <v>159</v>
       </c>
       <c r="X18" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="Y18" s="1">
         <v>0</v>
       </c>
       <c r="Z18" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AA18" s="1">
-        <v>0</v>
+        <v>1209353.92</v>
       </c>
       <c r="AB18" s="1">
-        <v>0</v>
+        <v>3200</v>
       </c>
       <c r="AC18" s="1">
-        <v>2311320</v>
+        <v>1209353.92</v>
       </c>
       <c r="AD18" s="1">
-        <v>770.4400000000001</v>
+        <v>377.92309999999998</v>
       </c>
       <c r="AE18" s="1">
-        <v>0</v>
+        <v>388.9</v>
       </c>
       <c r="AF18" s="1">
-        <v>0</v>
+        <v>1244480</v>
       </c>
       <c r="AG18" s="1">
-        <v>0</v>
+        <v>3733.44</v>
       </c>
       <c r="AH18" s="1">
-        <v>0</v>
+        <v>186.672</v>
       </c>
       <c r="AI18" s="1">
         <v>25</v>
       </c>
       <c r="AJ18" s="1">
-        <v>2311345</v>
+        <v>-31180.96800000011</v>
       </c>
       <c r="AK18" s="1">
-        <v>173350.875</v>
+        <v>-2338.5726000000082</v>
       </c>
       <c r="AL18" s="1">
-        <v>-2484695.88</v>
+        <v>33519.54</v>
       </c>
       <c r="AM18" s="1">
-        <v>-107.5</v>
+        <v>2.77</v>
       </c>
       <c r="AN18" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
-    <row r="19" spans="1:40">
+    <row r="19" spans="1:40" x14ac:dyDescent="0.5">
       <c r="A19" s="1" t="s">
         <v>57</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C19" s="1">
-        <v>233742</v>
+        <v>236901</v>
       </c>
       <c r="D19" s="1">
         <v>11400</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F19" s="1">
-        <v>16767</v>
+        <v>2416</v>
       </c>
       <c r="G19" s="1">
         <v>0</v>
       </c>
       <c r="H19" s="1">
-        <v>6111</v>
+        <v>2416</v>
       </c>
       <c r="I19" s="1">
         <v>0</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K19" s="1">
         <v>0</v>
       </c>
       <c r="L19" s="1">
-        <v>10656</v>
+        <v>0</v>
       </c>
       <c r="M19" s="1" t="s">
         <v>91</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O19" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="P19" s="1">
-        <v>12446</v>
+        <v>33241</v>
       </c>
       <c r="Q19" s="1">
-        <v>593.01</v>
+        <v>256.02</v>
       </c>
       <c r="R19" s="1">
-        <v>7380609.18</v>
+        <v>8510258.8200000003</v>
       </c>
       <c r="S19" s="1" t="s">
         <v>143</v>
       </c>
       <c r="T19" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="U19" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V19" s="1" t="b">
         <v>1</v>
       </c>
       <c r="W19" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="X19" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="Y19" s="1">
         <v>0</v>
       </c>
       <c r="Z19" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AA19" s="1">
-        <v>4035437.6648</v>
+        <v>1102708.0053999999</v>
       </c>
       <c r="AB19" s="1">
-        <v>6111</v>
+        <v>2416</v>
       </c>
       <c r="AC19" s="1">
-        <v>10354552.2248</v>
+        <v>1102708.0053999999</v>
       </c>
       <c r="AD19" s="1">
-        <v>617.5554496809209</v>
+        <v>456.41887640728481</v>
       </c>
       <c r="AE19" s="1">
-        <v>567.9</v>
+        <v>480</v>
       </c>
       <c r="AF19" s="1">
-        <v>9521979.299999999</v>
+        <v>1159680</v>
       </c>
       <c r="AG19" s="1">
-        <v>28565.9379</v>
+        <v>3479.04</v>
       </c>
       <c r="AH19" s="1">
-        <v>1428.296895</v>
+        <v>173.952</v>
       </c>
       <c r="AI19" s="1">
         <v>25</v>
       </c>
       <c r="AJ19" s="1">
-        <v>862592.1595949996</v>
+        <v>-53294.002600000007</v>
       </c>
       <c r="AK19" s="1">
-        <v>64694.41196962497</v>
+        <v>-3997.0501949999998</v>
       </c>
       <c r="AL19" s="1">
-        <v>-927286.5699999999</v>
+        <v>57291.05</v>
       </c>
       <c r="AM19" s="1">
-        <v>-8.960000000000001</v>
+        <v>5.2</v>
       </c>
       <c r="AN19" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
-    <row r="20" spans="1:40">
+    <row r="20" spans="1:40" x14ac:dyDescent="0.5">
       <c r="A20" s="1" t="s">
         <v>58</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C20" s="1">
-        <v>233742</v>
+        <v>236901</v>
       </c>
       <c r="D20" s="1">
         <v>11400</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F20" s="1">
-        <v>16650</v>
+        <v>7</v>
       </c>
       <c r="G20" s="1">
         <v>0</v>
       </c>
       <c r="H20" s="1">
-        <v>4600</v>
+        <v>7</v>
       </c>
       <c r="I20" s="1">
         <v>0</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K20" s="1">
         <v>0</v>
       </c>
       <c r="L20" s="1">
-        <v>12050</v>
+        <v>0</v>
       </c>
       <c r="M20" s="1" t="s">
         <v>91</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O20" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="P20" s="1">
-        <v>20500</v>
+        <v>11000</v>
       </c>
       <c r="Q20" s="1">
-        <v>653.46</v>
+        <v>274.33</v>
       </c>
       <c r="R20" s="1">
-        <v>13395955.45</v>
-      </c>
-      <c r="S20" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="T20" s="1" t="s">
-        <v>157</v>
+        <v>3017632.8</v>
+      </c>
+      <c r="S20" s="1">
+        <v>0</v>
+      </c>
+      <c r="T20" s="1">
+        <v>0</v>
       </c>
       <c r="U20" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V20" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="W20" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="X20" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="X20" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="Y20" s="1">
         <v>0</v>
       </c>
       <c r="Z20" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AA20" s="1">
-        <v>1315388.715</v>
+        <v>0</v>
       </c>
       <c r="AB20" s="1">
-        <v>2650</v>
+        <v>0</v>
       </c>
       <c r="AC20" s="1">
-        <v>10463828.715</v>
+        <v>1920.31</v>
       </c>
       <c r="AD20" s="1">
-        <v>628.4581810810811</v>
+        <v>274.33</v>
       </c>
       <c r="AE20" s="1">
-        <v>525</v>
+        <v>247.9</v>
       </c>
       <c r="AF20" s="1">
-        <v>8741250</v>
+        <v>1735.3</v>
       </c>
       <c r="AG20" s="1">
-        <v>26223.75</v>
+        <v>5.2058999999999997</v>
       </c>
       <c r="AH20" s="1">
-        <v>1311.1875</v>
+        <v>0.26029499999999989</v>
       </c>
       <c r="AI20" s="1">
         <v>25</v>
       </c>
       <c r="AJ20" s="1">
-        <v>1750138.6525</v>
+        <v>215.47619499999999</v>
       </c>
       <c r="AK20" s="1">
-        <v>131260.3989375</v>
+        <v>16.160714625000001</v>
       </c>
       <c r="AL20" s="1">
-        <v>-1881399.05</v>
+        <v>-231.64</v>
       </c>
       <c r="AM20" s="1">
-        <v>-17.98</v>
+        <v>-12.06</v>
       </c>
       <c r="AN20" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
-    <row r="21" spans="1:40">
+    <row r="21" spans="1:40" x14ac:dyDescent="0.5">
       <c r="A21" s="1" t="s">
         <v>59</v>
       </c>
@@ -3315,7 +3359,7 @@
         <v>65</v>
       </c>
       <c r="C21" s="1">
-        <v>216199</v>
+        <v>236901</v>
       </c>
       <c r="D21" s="1">
         <v>11400</v>
@@ -3324,19 +3368,19 @@
         <v>69</v>
       </c>
       <c r="F21" s="1">
-        <v>2100</v>
+        <v>3330</v>
       </c>
       <c r="G21" s="1">
         <v>0</v>
       </c>
       <c r="H21" s="1">
-        <v>2100</v>
+        <v>3330</v>
       </c>
       <c r="I21" s="1">
         <v>0</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K21" s="1">
         <v>0</v>
@@ -3348,88 +3392,88 @@
         <v>91</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="O21" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="P21" s="1">
-        <v>12000</v>
+        <v>11000</v>
       </c>
       <c r="Q21" s="1">
-        <v>316.8</v>
+        <v>274.33</v>
       </c>
       <c r="R21" s="1">
-        <v>3801551.6</v>
+        <v>3017632.8</v>
       </c>
       <c r="S21" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="T21" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="U21" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V21" s="1" t="b">
         <v>1</v>
       </c>
       <c r="W21" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="X21" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="X21" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="Y21" s="1">
         <v>0</v>
       </c>
       <c r="Z21" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="AA21" s="1">
-        <v>631861.86</v>
+        <v>2357395.6860000002</v>
       </c>
       <c r="AB21" s="1">
-        <v>2100</v>
+        <v>3330</v>
       </c>
       <c r="AC21" s="1">
-        <v>631861.86</v>
+        <v>2357395.6860000002</v>
       </c>
       <c r="AD21" s="1">
-        <v>300.8866</v>
+        <v>707.92663243243237</v>
       </c>
       <c r="AE21" s="1">
-        <v>285</v>
+        <v>698</v>
       </c>
       <c r="AF21" s="1">
-        <v>598500</v>
+        <v>2324340</v>
       </c>
       <c r="AG21" s="1">
-        <v>1795.5</v>
+        <v>6973.02</v>
       </c>
       <c r="AH21" s="1">
-        <v>89.77499999999999</v>
+        <v>348.65100000000001</v>
       </c>
       <c r="AI21" s="1">
         <v>25</v>
       </c>
       <c r="AJ21" s="1">
-        <v>35272.13500000001</v>
+        <v>40402.356999999844</v>
       </c>
       <c r="AK21" s="1">
-        <v>2645.410125000001</v>
+        <v>3030.1767749999881</v>
       </c>
       <c r="AL21" s="1">
-        <v>-37917.55</v>
+        <v>-43432.53</v>
       </c>
       <c r="AM21" s="1">
-        <v>-6</v>
+        <v>-1.84</v>
       </c>
       <c r="AN21" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
-    <row r="22" spans="1:40">
+    <row r="22" spans="1:40" x14ac:dyDescent="0.5">
       <c r="A22" s="1" t="s">
         <v>60</v>
       </c>
@@ -3437,7 +3481,7 @@
         <v>65</v>
       </c>
       <c r="C22" s="1">
-        <v>216199</v>
+        <v>236901</v>
       </c>
       <c r="D22" s="1">
         <v>11400</v>
@@ -3446,19 +3490,19 @@
         <v>69</v>
       </c>
       <c r="F22" s="1">
-        <v>10</v>
+        <v>6200</v>
       </c>
       <c r="G22" s="1">
         <v>0</v>
       </c>
       <c r="H22" s="1">
-        <v>10</v>
+        <v>6200</v>
       </c>
       <c r="I22" s="1">
         <v>0</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="K22" s="1">
         <v>0</v>
@@ -3470,85 +3514,88 @@
         <v>91</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="O22" s="1" t="s">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="P22" s="1">
-        <v>2010</v>
+        <v>11000</v>
       </c>
       <c r="Q22" s="1">
-        <v>572.02</v>
+        <v>274.33</v>
       </c>
       <c r="R22" s="1">
-        <v>1149757.59</v>
-      </c>
-      <c r="S22" s="1">
-        <v>0</v>
-      </c>
-      <c r="T22" s="1">
-        <v>0</v>
+        <v>3017632.8</v>
+      </c>
+      <c r="S22" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="T22" s="1" t="s">
+        <v>157</v>
       </c>
       <c r="U22" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V22" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="W22" s="1" t="s">
+        <v>159</v>
       </c>
       <c r="X22" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="Y22" s="1">
         <v>0</v>
       </c>
       <c r="Z22" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="AA22" s="1">
-        <v>0</v>
+        <v>3557574.72</v>
       </c>
       <c r="AB22" s="1">
-        <v>0</v>
+        <v>6200</v>
       </c>
       <c r="AC22" s="1">
-        <v>5720.2</v>
+        <v>3557574.72</v>
       </c>
       <c r="AD22" s="1">
-        <v>572.02</v>
+        <v>573.8023741935483</v>
       </c>
       <c r="AE22" s="1">
-        <v>499</v>
+        <v>617</v>
       </c>
       <c r="AF22" s="1">
-        <v>4990</v>
+        <v>3825400</v>
       </c>
       <c r="AG22" s="1">
-        <v>14.97</v>
+        <v>11476.2</v>
       </c>
       <c r="AH22" s="1">
-        <v>0.7484999999999999</v>
+        <v>573.80999999999995</v>
       </c>
       <c r="AI22" s="1">
         <v>25</v>
       </c>
       <c r="AJ22" s="1">
-        <v>770.9184999999998</v>
+        <v>-255750.27</v>
       </c>
       <c r="AK22" s="1">
-        <v>57.81888749999998</v>
+        <v>-19181.270250000001</v>
       </c>
       <c r="AL22" s="1">
-        <v>-828.74</v>
+        <v>274931.53999999998</v>
       </c>
       <c r="AM22" s="1">
-        <v>-14.49</v>
+        <v>7.73</v>
       </c>
       <c r="AN22" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
-    <row r="23" spans="1:40">
+    <row r="23" spans="1:40" x14ac:dyDescent="0.5">
       <c r="A23" s="1" t="s">
         <v>61</v>
       </c>
@@ -3556,7 +3603,7 @@
         <v>65</v>
       </c>
       <c r="C23" s="1">
-        <v>216199</v>
+        <v>236901</v>
       </c>
       <c r="D23" s="1">
         <v>11400</v>
@@ -3565,13 +3612,13 @@
         <v>69</v>
       </c>
       <c r="F23" s="1">
-        <v>7000</v>
+        <v>2800</v>
       </c>
       <c r="G23" s="1">
         <v>0</v>
       </c>
       <c r="H23" s="1">
-        <v>7000</v>
+        <v>2800</v>
       </c>
       <c r="I23" s="1">
         <v>0</v>
@@ -3595,79 +3642,76 @@
         <v>133</v>
       </c>
       <c r="P23" s="1">
-        <v>2010</v>
+        <v>3300</v>
       </c>
       <c r="Q23" s="1">
-        <v>572.02</v>
+        <v>421.87</v>
       </c>
       <c r="R23" s="1">
-        <v>1149757.59</v>
-      </c>
-      <c r="S23" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="T23" s="1" t="s">
-        <v>159</v>
+        <v>1392162.84</v>
+      </c>
+      <c r="S23" s="1">
+        <v>0</v>
+      </c>
+      <c r="T23" s="1">
+        <v>0</v>
       </c>
       <c r="U23" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V23" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="W23" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="X23" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="X23" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="Y23" s="1">
         <v>0</v>
       </c>
       <c r="Z23" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="AA23" s="1">
-        <v>3076618.3</v>
+        <v>0</v>
       </c>
       <c r="AB23" s="1">
-        <v>7000</v>
+        <v>0</v>
       </c>
       <c r="AC23" s="1">
-        <v>3076618.3</v>
+        <v>1181236</v>
       </c>
       <c r="AD23" s="1">
-        <v>439.5169</v>
+        <v>421.87</v>
       </c>
       <c r="AE23" s="1">
-        <v>336.5</v>
+        <v>469</v>
       </c>
       <c r="AF23" s="1">
-        <v>2355500</v>
+        <v>1313200</v>
       </c>
       <c r="AG23" s="1">
-        <v>7066.5</v>
+        <v>3939.6</v>
       </c>
       <c r="AH23" s="1">
-        <v>353.325</v>
+        <v>196.98</v>
       </c>
       <c r="AI23" s="1">
         <v>25</v>
       </c>
       <c r="AJ23" s="1">
-        <v>728563.1250000005</v>
+        <v>-127802.4199999999</v>
       </c>
       <c r="AK23" s="1">
-        <v>54642.23437500004</v>
+        <v>-9585.1814999999933</v>
       </c>
       <c r="AL23" s="1">
-        <v>-783205.36</v>
+        <v>137387.6</v>
       </c>
       <c r="AM23" s="1">
-        <v>-25.46</v>
+        <v>11.63</v>
       </c>
       <c r="AN23" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
   </sheetData>

--- a/data/output/holdings_FINAL.xlsx
+++ b/data/output/holdings_FINAL.xlsx
@@ -1,21 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Trishakti\Projects\RPA\track_stock_price\data\output\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{593DC1B6-8576-442E-A759-790485A2D372}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-3075" yWindow="-16320" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Result" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -142,70 +136,70 @@
     <t>lastUpdated</t>
   </si>
   <si>
-    <t>033edc86-0710-4c63-9cdb-2f948597f889</t>
-  </si>
-  <si>
-    <t>1d009eed-97f4-4854-93ee-032696134bbb</t>
-  </si>
-  <si>
-    <t>b5eef2f2-2a7f-4ef4-b090-321e652165f4</t>
-  </si>
-  <si>
-    <t>df176ecd-0b9c-41dd-b202-0afc4d8914f1</t>
-  </si>
-  <si>
-    <t>4a54d280-268b-4047-89cf-8ff9774a1b7e</t>
-  </si>
-  <si>
-    <t>df2709d9-0943-4420-bc35-bf40e79f112b</t>
-  </si>
-  <si>
-    <t>131953b3-7500-4cff-a1fe-e1d6eb159bd6</t>
-  </si>
-  <si>
-    <t>8fed5e0f-6a7f-4d46-aa82-98ab8ea1ebcc</t>
-  </si>
-  <si>
-    <t>5729c4d6-93be-45ba-ba4a-8241060affba</t>
-  </si>
-  <si>
-    <t>5b5cbb43-17f3-4f02-9348-2135e827415e</t>
-  </si>
-  <si>
-    <t>18fefa21-92d2-4b8c-b210-8663ce44253f</t>
-  </si>
-  <si>
-    <t>5a56928b-9f8f-44f2-989a-b8d806b7c137</t>
-  </si>
-  <si>
-    <t>e68d0be0-880d-461b-ad53-496ffbe41d14</t>
-  </si>
-  <si>
-    <t>06f6cb27-7b4f-4f90-9599-abc7fc9b79ac</t>
-  </si>
-  <si>
-    <t>c9478196-393b-41ca-aae5-ad3d5d6b9a82</t>
-  </si>
-  <si>
-    <t>69d6dd6f-535a-432a-ad90-3c0d398e3a5a</t>
-  </si>
-  <si>
-    <t>779586ad-78d2-42af-8c3d-e224348ee035</t>
-  </si>
-  <si>
-    <t>8731a77f-b61d-4ca3-b387-5a3063d5bec4</t>
-  </si>
-  <si>
-    <t>45118d44-296d-4250-803e-2aecd3bdfda2</t>
-  </si>
-  <si>
-    <t>0ce6dc4a-afe5-4555-8d75-9896289c539c</t>
-  </si>
-  <si>
-    <t>d6c17832-fa80-4f45-9db6-3f819aa6c64f</t>
-  </si>
-  <si>
-    <t>90682b10-879c-4329-bb51-010939f1ad54</t>
+    <t>9a25f4b0-38b5-4ee6-8045-4bea31a62e63</t>
+  </si>
+  <si>
+    <t>279ae609-862e-48df-941c-d16815536c35</t>
+  </si>
+  <si>
+    <t>c757d4bc-0ee1-4e28-8f10-036d0b6012ee</t>
+  </si>
+  <si>
+    <t>d5ca27e4-c674-47d5-9816-5713289a7a0c</t>
+  </si>
+  <si>
+    <t>eaafc7fa-0212-46d6-825b-839b69a6a409</t>
+  </si>
+  <si>
+    <t>f29ef589-7354-4961-b94c-7adc7119c2c9</t>
+  </si>
+  <si>
+    <t>feab2474-ae79-4019-8b85-afd370bbcbf5</t>
+  </si>
+  <si>
+    <t>7c5a270b-0931-4dee-8b24-7681f7c8b3a3</t>
+  </si>
+  <si>
+    <t>849e6167-4795-475c-a080-ab99f6ef8540</t>
+  </si>
+  <si>
+    <t>3a42d6d8-e93f-4c38-84e8-537ede57e28d</t>
+  </si>
+  <si>
+    <t>05866eef-9b89-4ccb-9fb9-80aaa4f383dc</t>
+  </si>
+  <si>
+    <t>b18efb95-f2ef-4a11-8650-faf92d5a1ed1</t>
+  </si>
+  <si>
+    <t>d5731acd-6318-468a-aae9-8dfd9a12f606</t>
+  </si>
+  <si>
+    <t>94252ceb-494b-45b6-88ab-81a19737cc9c</t>
+  </si>
+  <si>
+    <t>a2e9990d-1adf-4991-b8a4-bc128aa3157e</t>
+  </si>
+  <si>
+    <t>ba62bdab-ae78-4b37-8ded-3c959be592f9</t>
+  </si>
+  <si>
+    <t>5cdc748f-e51e-47e2-95cc-c660e8dae986</t>
+  </si>
+  <si>
+    <t>daac0d0c-8d3f-4c3f-a4fd-bc489c95f848</t>
+  </si>
+  <si>
+    <t>7b27e730-5e7a-4f2e-b259-4dc50f01a248</t>
+  </si>
+  <si>
+    <t>bbd97d60-ccba-49dc-87bd-796edce00b14</t>
+  </si>
+  <si>
+    <t>65c7017a-1081-4315-b1d6-313ce6f8d4a5</t>
+  </si>
+  <si>
+    <t>b0e97192-1c0e-4988-ad46-6ecd89bd67d9</t>
   </si>
   <si>
     <t>TIKA BAHADUR GOTAME</t>
@@ -523,14 +517,17 @@
     <t>LL284136</t>
   </si>
   <si>
-    <t>2025-11-26 03:01:16</t>
+    <t>2025-11-26 04:50:02</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="#,##0.00"/>
+  </numFmts>
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -584,7 +581,7 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -594,21 +591,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -646,7 +635,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -680,7 +669,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -715,10 +703,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -891,54 +878,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AZ23"/>
-  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="34.87890625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.17578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.87890625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.29296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.05859375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.64453125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.64453125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.1171875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.17578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.05859375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.46875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="6.29296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="72.17578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="21" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="8.52734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="16.234375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="19.41015625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="25.17578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="17.1171875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="12.1171875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="33.703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="12.87890625" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="12.64453125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.76171875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="20.29296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="23.76171875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="15.9375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="13.703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="7.703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="12.17578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="23.234375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="7.703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="11.17578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="21.87890625" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="11.76171875" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="18.46875" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="17.52734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="52" width="18.703125" style="1" customWidth="1"/>
+    <col min="1" max="52" width="18.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:40" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:40">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1060,7 +1007,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:40" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:40">
       <c r="A2" s="1" t="s">
         <v>40</v>
       </c>
@@ -1158,7 +1105,7 @@
         <v>58.695</v>
       </c>
       <c r="AH2" s="1">
-        <v>2.9347500000000002</v>
+        <v>2.93475</v>
       </c>
       <c r="AI2" s="1">
         <v>25</v>
@@ -1167,7 +1114,7 @@
         <v>-18178.37025</v>
       </c>
       <c r="AK2" s="1">
-        <v>-1363.3777687500001</v>
+        <v>-1363.37776875</v>
       </c>
       <c r="AL2" s="1">
         <v>19541.75</v>
@@ -1179,7 +1126,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="3" spans="1:40" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:40">
       <c r="A3" s="1" t="s">
         <v>41</v>
       </c>
@@ -1229,10 +1176,10 @@
         <v>210</v>
       </c>
       <c r="Q3" s="1">
-        <v>642.69000000000005</v>
+        <v>642.6900000000001</v>
       </c>
       <c r="R3" s="1">
-        <v>134964.14000000001</v>
+        <v>134964.14</v>
       </c>
       <c r="S3" s="1">
         <v>0</v>
@@ -1262,10 +1209,10 @@
         <v>0</v>
       </c>
       <c r="AC3" s="1">
-        <v>6426.9000000000005</v>
+        <v>6426.900000000001</v>
       </c>
       <c r="AD3" s="1">
-        <v>642.69000000000005</v>
+        <v>642.6900000000001</v>
       </c>
       <c r="AE3" s="1">
         <v>657</v>
@@ -1277,16 +1224,16 @@
         <v>19.71</v>
       </c>
       <c r="AH3" s="1">
-        <v>0.98549999999999993</v>
+        <v>0.9854999999999999</v>
       </c>
       <c r="AI3" s="1">
         <v>25</v>
       </c>
       <c r="AJ3" s="1">
-        <v>-97.404499999999643</v>
+        <v>-97.40449999999964</v>
       </c>
       <c r="AK3" s="1">
-        <v>-7.3053374999999727</v>
+        <v>-7.305337499999973</v>
       </c>
       <c r="AL3" s="1">
         <v>104.71</v>
@@ -1298,7 +1245,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="4" spans="1:40" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:40">
       <c r="A4" s="1" t="s">
         <v>42</v>
       </c>
@@ -1348,10 +1295,10 @@
         <v>210</v>
       </c>
       <c r="Q4" s="1">
-        <v>642.69000000000005</v>
+        <v>642.6900000000001</v>
       </c>
       <c r="R4" s="1">
-        <v>134964.14000000001</v>
+        <v>134964.14</v>
       </c>
       <c r="S4" s="1" t="s">
         <v>134</v>
@@ -1387,7 +1334,7 @@
         <v>152097.85</v>
       </c>
       <c r="AD4" s="1">
-        <v>304.19569999999999</v>
+        <v>304.1957</v>
       </c>
       <c r="AE4" s="1">
         <v>244</v>
@@ -1405,10 +1352,10 @@
         <v>25</v>
       </c>
       <c r="AJ4" s="1">
-        <v>30507.149999999991</v>
+        <v>30507.14999999999</v>
       </c>
       <c r="AK4" s="1">
-        <v>2288.0362500000001</v>
+        <v>2288.03625</v>
       </c>
       <c r="AL4" s="1">
         <v>-32795.19</v>
@@ -1420,7 +1367,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:40">
       <c r="A5" s="1" t="s">
         <v>43</v>
       </c>
@@ -1518,7 +1465,7 @@
         <v>10.74</v>
       </c>
       <c r="AH5" s="1">
-        <v>0.53699999999999992</v>
+        <v>0.5369999999999999</v>
       </c>
       <c r="AI5" s="1">
         <v>25</v>
@@ -1539,7 +1486,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:40">
       <c r="A6" s="1" t="s">
         <v>44</v>
       </c>
@@ -1589,7 +1536,7 @@
         <v>108</v>
       </c>
       <c r="Q6" s="1">
-        <v>520.57000000000005</v>
+        <v>520.5700000000001</v>
       </c>
       <c r="R6" s="1">
         <v>56221.96</v>
@@ -1622,10 +1569,10 @@
         <v>0</v>
       </c>
       <c r="AC6" s="1">
-        <v>4164.5600000000004</v>
+        <v>4164.56</v>
       </c>
       <c r="AD6" s="1">
-        <v>520.57000000000005</v>
+        <v>520.5700000000001</v>
       </c>
       <c r="AE6" s="1">
         <v>617</v>
@@ -1637,16 +1584,16 @@
         <v>14.808</v>
       </c>
       <c r="AH6" s="1">
-        <v>0.74039999999999995</v>
+        <v>0.7403999999999999</v>
       </c>
       <c r="AI6" s="1">
         <v>25</v>
       </c>
       <c r="AJ6" s="1">
-        <v>-730.89159999999993</v>
+        <v>-730.8915999999999</v>
       </c>
       <c r="AK6" s="1">
-        <v>-54.816869999999987</v>
+        <v>-54.81686999999999</v>
       </c>
       <c r="AL6" s="1">
         <v>785.71</v>
@@ -1658,7 +1605,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:40">
       <c r="A7" s="1" t="s">
         <v>45</v>
       </c>
@@ -1747,7 +1694,7 @@
         <v>631861.86</v>
       </c>
       <c r="AD7" s="1">
-        <v>300.88659999999999</v>
+        <v>300.8866</v>
       </c>
       <c r="AE7" s="1">
         <v>285</v>
@@ -1759,19 +1706,19 @@
         <v>1795.5</v>
       </c>
       <c r="AH7" s="1">
-        <v>89.774999999999991</v>
+        <v>89.77499999999999</v>
       </c>
       <c r="AI7" s="1">
         <v>25</v>
       </c>
       <c r="AJ7" s="1">
-        <v>35272.135000000009</v>
+        <v>35272.13500000001</v>
       </c>
       <c r="AK7" s="1">
-        <v>2645.4101250000008</v>
+        <v>2645.410125000001</v>
       </c>
       <c r="AL7" s="1">
-        <v>-37917.550000000003</v>
+        <v>-37917.55</v>
       </c>
       <c r="AM7" s="1">
         <v>-6</v>
@@ -1780,7 +1727,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:40">
       <c r="A8" s="1" t="s">
         <v>46</v>
       </c>
@@ -1833,7 +1780,7 @@
         <v>572.02</v>
       </c>
       <c r="R8" s="1">
-        <v>1149757.5900000001</v>
+        <v>1149757.59</v>
       </c>
       <c r="S8" s="1">
         <v>0</v>
@@ -1878,16 +1825,16 @@
         <v>14.97</v>
       </c>
       <c r="AH8" s="1">
-        <v>0.74849999999999994</v>
+        <v>0.7484999999999999</v>
       </c>
       <c r="AI8" s="1">
         <v>25</v>
       </c>
       <c r="AJ8" s="1">
-        <v>770.91849999999977</v>
+        <v>770.9184999999998</v>
       </c>
       <c r="AK8" s="1">
-        <v>57.818887499999981</v>
+        <v>57.81888749999998</v>
       </c>
       <c r="AL8" s="1">
         <v>-828.74</v>
@@ -1899,7 +1846,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:40">
       <c r="A9" s="1" t="s">
         <v>47</v>
       </c>
@@ -1952,7 +1899,7 @@
         <v>572.02</v>
       </c>
       <c r="R9" s="1">
-        <v>1149757.5900000001</v>
+        <v>1149757.59</v>
       </c>
       <c r="S9" s="1" t="s">
         <v>136</v>
@@ -1988,7 +1935,7 @@
         <v>3076618.3</v>
       </c>
       <c r="AD9" s="1">
-        <v>439.51690000000002</v>
+        <v>439.5169</v>
       </c>
       <c r="AE9" s="1">
         <v>336.5</v>
@@ -2000,16 +1947,16 @@
         <v>7066.5</v>
       </c>
       <c r="AH9" s="1">
-        <v>353.32499999999999</v>
+        <v>353.325</v>
       </c>
       <c r="AI9" s="1">
         <v>25</v>
       </c>
       <c r="AJ9" s="1">
-        <v>728563.12500000047</v>
+        <v>728563.1250000005</v>
       </c>
       <c r="AK9" s="1">
-        <v>54642.234375000036</v>
+        <v>54642.23437500004</v>
       </c>
       <c r="AL9" s="1">
         <v>-783205.36</v>
@@ -2021,7 +1968,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:40">
       <c r="A10" s="1" t="s">
         <v>48</v>
       </c>
@@ -2107,28 +2054,28 @@
         <v>5700</v>
       </c>
       <c r="AC10" s="1">
-        <v>13013760.810000001</v>
+        <v>13013760.81</v>
       </c>
       <c r="AD10" s="1">
-        <v>294.09628949152551</v>
+        <v>294.0962894915255</v>
       </c>
       <c r="AE10" s="1">
-        <v>284.89999999999998</v>
+        <v>284.9</v>
       </c>
       <c r="AF10" s="1">
         <v>12606825</v>
       </c>
       <c r="AG10" s="1">
-        <v>37820.474999999999</v>
+        <v>37820.475</v>
       </c>
       <c r="AH10" s="1">
-        <v>1891.0237500000001</v>
+        <v>1891.02375</v>
       </c>
       <c r="AI10" s="1">
         <v>25</v>
       </c>
       <c r="AJ10" s="1">
-        <v>446672.30875000171</v>
+        <v>446672.3087500017</v>
       </c>
       <c r="AK10" s="1">
         <v>33500.42315625013</v>
@@ -2143,7 +2090,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:40">
       <c r="A11" s="1" t="s">
         <v>49</v>
       </c>
@@ -2196,7 +2143,7 @@
         <v>983.53</v>
       </c>
       <c r="R11" s="1">
-        <v>11949900.199999999</v>
+        <v>11949900.2</v>
       </c>
       <c r="S11" s="1">
         <v>0</v>
@@ -2232,7 +2179,7 @@
         <v>983.53</v>
       </c>
       <c r="AE11" s="1">
-        <v>1025.0999999999999</v>
+        <v>1025.1</v>
       </c>
       <c r="AF11" s="1">
         <v>10917315</v>
@@ -2250,19 +2197,19 @@
         <v>-408305.9577499982</v>
       </c>
       <c r="AK11" s="1">
-        <v>-30622.946831249861</v>
+        <v>-30622.94683124986</v>
       </c>
       <c r="AL11" s="1">
         <v>438928.9</v>
       </c>
       <c r="AM11" s="1">
-        <v>4.1900000000000004</v>
+        <v>4.19</v>
       </c>
       <c r="AN11" s="1" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:40">
       <c r="A12" s="1" t="s">
         <v>50</v>
       </c>
@@ -2315,7 +2262,7 @@
         <v>2543.42</v>
       </c>
       <c r="R12" s="1">
-        <v>534117.81999999995</v>
+        <v>534117.8199999999</v>
       </c>
       <c r="S12" s="1" t="s">
         <v>138</v>
@@ -2342,16 +2289,16 @@
         <v>165</v>
       </c>
       <c r="AA12" s="1">
-        <v>4757941.2588000009</v>
+        <v>4757941.258800001</v>
       </c>
       <c r="AB12" s="1">
         <v>1979</v>
       </c>
       <c r="AC12" s="1">
-        <v>5292059.4588000011</v>
+        <v>5292059.458800001</v>
       </c>
       <c r="AD12" s="1">
-        <v>2417.5694192782098</v>
+        <v>2417.56941927821</v>
       </c>
       <c r="AE12" s="1">
         <v>2390</v>
@@ -2363,16 +2310,16 @@
         <v>15695.13</v>
       </c>
       <c r="AH12" s="1">
-        <v>784.75649999999996</v>
+        <v>784.7565</v>
       </c>
       <c r="AI12" s="1">
         <v>25</v>
       </c>
       <c r="AJ12" s="1">
-        <v>76854.345300001092</v>
+        <v>76854.34530000109</v>
       </c>
       <c r="AK12" s="1">
-        <v>5764.0758975000817</v>
+        <v>5764.075897500082</v>
       </c>
       <c r="AL12" s="1">
         <v>-82618.42</v>
@@ -2384,7 +2331,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:40">
       <c r="A13" s="1" t="s">
         <v>51</v>
       </c>
@@ -2434,7 +2381,7 @@
         <v>3730</v>
       </c>
       <c r="Q13" s="1">
-        <v>770.44</v>
+        <v>770.4400000000001</v>
       </c>
       <c r="R13" s="1">
         <v>2873726.65</v>
@@ -2470,7 +2417,7 @@
         <v>2311320</v>
       </c>
       <c r="AD13" s="1">
-        <v>770.44</v>
+        <v>770.4400000000001</v>
       </c>
       <c r="AE13" s="1">
         <v>0</v>
@@ -2503,7 +2450,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:40">
       <c r="A14" s="1" t="s">
         <v>52</v>
       </c>
@@ -2556,7 +2503,7 @@
         <v>593.01</v>
       </c>
       <c r="R14" s="1">
-        <v>7380609.1799999997</v>
+        <v>7380609.18</v>
       </c>
       <c r="S14" s="1" t="s">
         <v>139</v>
@@ -2583,7 +2530,7 @@
         <v>165</v>
       </c>
       <c r="AA14" s="1">
-        <v>4035437.6647999999</v>
+        <v>4035437.6648</v>
       </c>
       <c r="AB14" s="1">
         <v>6111</v>
@@ -2598,34 +2545,34 @@
         <v>567.9</v>
       </c>
       <c r="AF14" s="1">
-        <v>9521979.2999999989</v>
+        <v>9521979.299999999</v>
       </c>
       <c r="AG14" s="1">
-        <v>28565.937900000001</v>
+        <v>28565.9379</v>
       </c>
       <c r="AH14" s="1">
-        <v>1428.2968949999999</v>
+        <v>1428.296895</v>
       </c>
       <c r="AI14" s="1">
         <v>25</v>
       </c>
       <c r="AJ14" s="1">
-        <v>862592.15959499963</v>
+        <v>862592.1595949996</v>
       </c>
       <c r="AK14" s="1">
-        <v>64694.411969624969</v>
+        <v>64694.41196962497</v>
       </c>
       <c r="AL14" s="1">
-        <v>-927286.57</v>
+        <v>-927286.5699999999</v>
       </c>
       <c r="AM14" s="1">
-        <v>-8.9600000000000009</v>
+        <v>-8.960000000000001</v>
       </c>
       <c r="AN14" s="1" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:40">
       <c r="A15" s="1" t="s">
         <v>53</v>
       </c>
@@ -2678,7 +2625,7 @@
         <v>653.46</v>
       </c>
       <c r="R15" s="1">
-        <v>13395955.449999999</v>
+        <v>13395955.45</v>
       </c>
       <c r="S15" s="1" t="s">
         <v>140</v>
@@ -2705,7 +2652,7 @@
         <v>165</v>
       </c>
       <c r="AA15" s="1">
-        <v>1315388.7150000001</v>
+        <v>1315388.715</v>
       </c>
       <c r="AB15" s="1">
         <v>2650</v>
@@ -2714,7 +2661,7 @@
         <v>10463828.715</v>
       </c>
       <c r="AD15" s="1">
-        <v>628.45818108108108</v>
+        <v>628.4581810810811</v>
       </c>
       <c r="AE15" s="1">
         <v>525</v>
@@ -2732,10 +2679,10 @@
         <v>25</v>
       </c>
       <c r="AJ15" s="1">
-        <v>1750138.6525000001</v>
+        <v>1750138.6525</v>
       </c>
       <c r="AK15" s="1">
-        <v>131260.39893749999</v>
+        <v>131260.3989375</v>
       </c>
       <c r="AL15" s="1">
         <v>-1881399.05</v>
@@ -2747,7 +2694,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.5">
+    <row r="16" spans="1:40">
       <c r="A16" s="1" t="s">
         <v>54</v>
       </c>
@@ -2827,16 +2774,16 @@
         <v>166</v>
       </c>
       <c r="AA16" s="1">
-        <v>3232526.8576000002</v>
+        <v>3232526.8576</v>
       </c>
       <c r="AB16" s="1">
         <v>3596</v>
       </c>
       <c r="AC16" s="1">
-        <v>3232526.8576000002</v>
+        <v>3232526.8576</v>
       </c>
       <c r="AD16" s="1">
-        <v>898.92293036707451</v>
+        <v>898.9229303670745</v>
       </c>
       <c r="AE16" s="1">
         <v>884</v>
@@ -2845,22 +2792,22 @@
         <v>3178864</v>
       </c>
       <c r="AG16" s="1">
-        <v>9536.5920000000006</v>
+        <v>9536.592000000001</v>
       </c>
       <c r="AH16" s="1">
-        <v>476.82960000000003</v>
+        <v>476.8296</v>
       </c>
       <c r="AI16" s="1">
         <v>25</v>
       </c>
       <c r="AJ16" s="1">
-        <v>63701.279199999757</v>
+        <v>63701.27919999976</v>
       </c>
       <c r="AK16" s="1">
         <v>4777.595939999982</v>
       </c>
       <c r="AL16" s="1">
-        <v>-68478.880000000005</v>
+        <v>-68478.88</v>
       </c>
       <c r="AM16" s="1">
         <v>-2.12</v>
@@ -2869,7 +2816,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="17" spans="1:40" x14ac:dyDescent="0.5">
+    <row r="17" spans="1:40">
       <c r="A17" s="1" t="s">
         <v>55</v>
       </c>
@@ -2922,7 +2869,7 @@
         <v>256.02</v>
       </c>
       <c r="R17" s="1">
-        <v>8510258.8200000003</v>
+        <v>8510258.82</v>
       </c>
       <c r="S17" s="1">
         <v>0</v>
@@ -2964,19 +2911,19 @@
         <v>2659968.5</v>
       </c>
       <c r="AG17" s="1">
-        <v>7979.9054999999998</v>
+        <v>7979.9055</v>
       </c>
       <c r="AH17" s="1">
-        <v>398.99527499999999</v>
+        <v>398.995275</v>
       </c>
       <c r="AI17" s="1">
         <v>25</v>
       </c>
       <c r="AJ17" s="1">
-        <v>328764.22077499982</v>
+        <v>328764.2207749998</v>
       </c>
       <c r="AK17" s="1">
-        <v>24657.316558124989</v>
+        <v>24657.31655812499</v>
       </c>
       <c r="AL17" s="1">
         <v>-353421.54</v>
@@ -2988,7 +2935,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="18" spans="1:40" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:40">
       <c r="A18" s="1" t="s">
         <v>56</v>
       </c>
@@ -3041,7 +2988,7 @@
         <v>256.02</v>
       </c>
       <c r="R18" s="1">
-        <v>8510258.8200000003</v>
+        <v>8510258.82</v>
       </c>
       <c r="S18" s="1" t="s">
         <v>142</v>
@@ -3077,7 +3024,7 @@
         <v>1209353.92</v>
       </c>
       <c r="AD18" s="1">
-        <v>377.92309999999998</v>
+        <v>377.9231</v>
       </c>
       <c r="AE18" s="1">
         <v>388.9</v>
@@ -3098,7 +3045,7 @@
         <v>-31180.96800000011</v>
       </c>
       <c r="AK18" s="1">
-        <v>-2338.5726000000082</v>
+        <v>-2338.572600000008</v>
       </c>
       <c r="AL18" s="1">
         <v>33519.54</v>
@@ -3110,7 +3057,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="19" spans="1:40" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:40">
       <c r="A19" s="1" t="s">
         <v>57</v>
       </c>
@@ -3163,7 +3110,7 @@
         <v>256.02</v>
       </c>
       <c r="R19" s="1">
-        <v>8510258.8200000003</v>
+        <v>8510258.82</v>
       </c>
       <c r="S19" s="1" t="s">
         <v>143</v>
@@ -3190,16 +3137,16 @@
         <v>166</v>
       </c>
       <c r="AA19" s="1">
-        <v>1102708.0053999999</v>
+        <v>1102708.0054</v>
       </c>
       <c r="AB19" s="1">
         <v>2416</v>
       </c>
       <c r="AC19" s="1">
-        <v>1102708.0053999999</v>
+        <v>1102708.0054</v>
       </c>
       <c r="AD19" s="1">
-        <v>456.41887640728481</v>
+        <v>456.4188764072848</v>
       </c>
       <c r="AE19" s="1">
         <v>480</v>
@@ -3217,10 +3164,10 @@
         <v>25</v>
       </c>
       <c r="AJ19" s="1">
-        <v>-53294.002600000007</v>
+        <v>-53294.00260000001</v>
       </c>
       <c r="AK19" s="1">
-        <v>-3997.0501949999998</v>
+        <v>-3997.050195</v>
       </c>
       <c r="AL19" s="1">
         <v>57291.05</v>
@@ -3232,7 +3179,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="20" spans="1:40" x14ac:dyDescent="0.5">
+    <row r="20" spans="1:40">
       <c r="A20" s="1" t="s">
         <v>58</v>
       </c>
@@ -3327,19 +3274,19 @@
         <v>1735.3</v>
       </c>
       <c r="AG20" s="1">
-        <v>5.2058999999999997</v>
+        <v>5.2059</v>
       </c>
       <c r="AH20" s="1">
-        <v>0.26029499999999989</v>
+        <v>0.2602949999999999</v>
       </c>
       <c r="AI20" s="1">
         <v>25</v>
       </c>
       <c r="AJ20" s="1">
-        <v>215.47619499999999</v>
+        <v>215.476195</v>
       </c>
       <c r="AK20" s="1">
-        <v>16.160714625000001</v>
+        <v>16.160714625</v>
       </c>
       <c r="AL20" s="1">
         <v>-231.64</v>
@@ -3351,7 +3298,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="21" spans="1:40" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:40">
       <c r="A21" s="1" t="s">
         <v>59</v>
       </c>
@@ -3431,16 +3378,16 @@
         <v>166</v>
       </c>
       <c r="AA21" s="1">
-        <v>2357395.6860000002</v>
+        <v>2357395.686</v>
       </c>
       <c r="AB21" s="1">
         <v>3330</v>
       </c>
       <c r="AC21" s="1">
-        <v>2357395.6860000002</v>
+        <v>2357395.686</v>
       </c>
       <c r="AD21" s="1">
-        <v>707.92663243243237</v>
+        <v>707.9266324324324</v>
       </c>
       <c r="AE21" s="1">
         <v>698</v>
@@ -3452,16 +3399,16 @@
         <v>6973.02</v>
       </c>
       <c r="AH21" s="1">
-        <v>348.65100000000001</v>
+        <v>348.651</v>
       </c>
       <c r="AI21" s="1">
         <v>25</v>
       </c>
       <c r="AJ21" s="1">
-        <v>40402.356999999844</v>
+        <v>40402.35699999984</v>
       </c>
       <c r="AK21" s="1">
-        <v>3030.1767749999881</v>
+        <v>3030.176774999988</v>
       </c>
       <c r="AL21" s="1">
         <v>-43432.53</v>
@@ -3473,7 +3420,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="22" spans="1:40" x14ac:dyDescent="0.5">
+    <row r="22" spans="1:40">
       <c r="A22" s="1" t="s">
         <v>60</v>
       </c>
@@ -3574,7 +3521,7 @@
         <v>11476.2</v>
       </c>
       <c r="AH22" s="1">
-        <v>573.80999999999995</v>
+        <v>573.8099999999999</v>
       </c>
       <c r="AI22" s="1">
         <v>25</v>
@@ -3583,10 +3530,10 @@
         <v>-255750.27</v>
       </c>
       <c r="AK22" s="1">
-        <v>-19181.270250000001</v>
+        <v>-19181.27025</v>
       </c>
       <c r="AL22" s="1">
-        <v>274931.53999999998</v>
+        <v>274931.54</v>
       </c>
       <c r="AM22" s="1">
         <v>7.73</v>
@@ -3595,7 +3542,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="23" spans="1:40" x14ac:dyDescent="0.5">
+    <row r="23" spans="1:40">
       <c r="A23" s="1" t="s">
         <v>61</v>
       </c>
@@ -3702,7 +3649,7 @@
         <v>-127802.4199999999</v>
       </c>
       <c r="AK23" s="1">
-        <v>-9585.1814999999933</v>
+        <v>-9585.181499999993</v>
       </c>
       <c r="AL23" s="1">
         <v>137387.6</v>

--- a/data/output/holdings_FINAL.xlsx
+++ b/data/output/holdings_FINAL.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="627" uniqueCount="265">
   <si>
     <t>id</t>
   </si>
@@ -136,388 +136,679 @@
     <t>lastUpdated</t>
   </si>
   <si>
-    <t>9a25f4b0-38b5-4ee6-8045-4bea31a62e63</t>
-  </si>
-  <si>
-    <t>279ae609-862e-48df-941c-d16815536c35</t>
-  </si>
-  <si>
-    <t>c757d4bc-0ee1-4e28-8f10-036d0b6012ee</t>
-  </si>
-  <si>
-    <t>d5ca27e4-c674-47d5-9816-5713289a7a0c</t>
-  </si>
-  <si>
-    <t>eaafc7fa-0212-46d6-825b-839b69a6a409</t>
-  </si>
-  <si>
-    <t>f29ef589-7354-4961-b94c-7adc7119c2c9</t>
-  </si>
-  <si>
-    <t>feab2474-ae79-4019-8b85-afd370bbcbf5</t>
-  </si>
-  <si>
-    <t>7c5a270b-0931-4dee-8b24-7681f7c8b3a3</t>
-  </si>
-  <si>
-    <t>849e6167-4795-475c-a080-ab99f6ef8540</t>
-  </si>
-  <si>
-    <t>3a42d6d8-e93f-4c38-84e8-537ede57e28d</t>
-  </si>
-  <si>
-    <t>05866eef-9b89-4ccb-9fb9-80aaa4f383dc</t>
-  </si>
-  <si>
-    <t>b18efb95-f2ef-4a11-8650-faf92d5a1ed1</t>
-  </si>
-  <si>
-    <t>d5731acd-6318-468a-aae9-8dfd9a12f606</t>
-  </si>
-  <si>
-    <t>94252ceb-494b-45b6-88ab-81a19737cc9c</t>
-  </si>
-  <si>
-    <t>a2e9990d-1adf-4991-b8a4-bc128aa3157e</t>
-  </si>
-  <si>
-    <t>ba62bdab-ae78-4b37-8ded-3c959be592f9</t>
-  </si>
-  <si>
-    <t>5cdc748f-e51e-47e2-95cc-c660e8dae986</t>
-  </si>
-  <si>
-    <t>daac0d0c-8d3f-4c3f-a4fd-bc489c95f848</t>
-  </si>
-  <si>
-    <t>7b27e730-5e7a-4f2e-b259-4dc50f01a248</t>
-  </si>
-  <si>
-    <t>bbd97d60-ccba-49dc-87bd-796edce00b14</t>
-  </si>
-  <si>
-    <t>65c7017a-1081-4315-b1d6-313ce6f8d4a5</t>
-  </si>
-  <si>
-    <t>b0e97192-1c0e-4988-ad46-6ecd89bd67d9</t>
+    <t>bro</t>
+  </si>
+  <si>
+    <t>4f160a4d-f853-447e-b3df-11f2d01a908e</t>
+  </si>
+  <si>
+    <t>09dc97b0-1b64-4c3d-8430-9dcfb9957a0f</t>
+  </si>
+  <si>
+    <t>101f45ab-fdd7-47ed-8559-d9457c17deab</t>
+  </si>
+  <si>
+    <t>dcf71ac7-6e32-4c32-9233-54ca6d1e17b6</t>
+  </si>
+  <si>
+    <t>c9eb2e85-24fa-482f-a144-2a985f2d2cf5</t>
+  </si>
+  <si>
+    <t>d3906b6e-9039-4ed4-9f9e-262199bbcdae</t>
+  </si>
+  <si>
+    <t>3518d321-b2f5-4390-8117-435f0ed1bb03</t>
+  </si>
+  <si>
+    <t>4e54c04e-328b-4af9-85f6-c8f55f986016</t>
+  </si>
+  <si>
+    <t>a021a93c-9862-444d-9355-4c5d38b12740</t>
+  </si>
+  <si>
+    <t>f439c0aa-4260-45ce-811a-22fb002e3927</t>
+  </si>
+  <si>
+    <t>3e3c659e-52c0-4ab4-bda2-f11d35851bfb</t>
+  </si>
+  <si>
+    <t>aaf6ad71-6884-4ca2-882c-b1be592bd5d6</t>
+  </si>
+  <si>
+    <t>79bc1f04-ccad-478b-b88c-b338c93ec5eb</t>
+  </si>
+  <si>
+    <t>0ee69550-337b-44b8-a1cd-8ca70003efc0</t>
+  </si>
+  <si>
+    <t>875b8b98-5dcf-4623-91bf-c7e776a5f046</t>
+  </si>
+  <si>
+    <t>56fce414-0775-4644-a24e-04ef22bcfab9</t>
+  </si>
+  <si>
+    <t>07b38591-dddc-4f88-b7b5-53465fc9e26c</t>
+  </si>
+  <si>
+    <t>5b80ce7f-0c8d-4fa1-a8c0-073b77cbaf6b</t>
+  </si>
+  <si>
+    <t>3ac27185-0517-4cb6-9eff-f63d30846826</t>
+  </si>
+  <si>
+    <t>6dae730f-ddb8-4f02-afd3-348437c29b54</t>
+  </si>
+  <si>
+    <t>6c60709b-df20-427d-ad90-c927a843a56c</t>
+  </si>
+  <si>
+    <t>06c857d7-ad5d-4bc6-a8de-dc735f815ce8</t>
+  </si>
+  <si>
+    <t>661bee85-2633-435f-857b-f89b108a196e</t>
+  </si>
+  <si>
+    <t>28c96f3e-d3ff-40c2-9694-324eb006a8b3</t>
+  </si>
+  <si>
+    <t>a8cc5146-33a5-46ae-b4cd-94e1863573f0</t>
+  </si>
+  <si>
+    <t>250ec4bd-9427-47fd-bba2-acc239274f92</t>
+  </si>
+  <si>
+    <t>ec713934-5f9d-48c2-b0e8-9d7d14ae1336</t>
+  </si>
+  <si>
+    <t>a72a8393-5e48-4794-806a-73af4831521a</t>
+  </si>
+  <si>
+    <t>d3c5cbf7-7945-4341-a0b3-13284aca363b</t>
+  </si>
+  <si>
+    <t>fa312a24-cc64-4345-a2e3-09b10974e173</t>
+  </si>
+  <si>
+    <t>f54cea66-db65-4a4b-8604-440cda491779</t>
+  </si>
+  <si>
+    <t>e26b124d-9ca2-4c44-90a8-b874de2229e8</t>
+  </si>
+  <si>
+    <t>bd46043d-1063-4833-973f-42bef5c9b41a</t>
+  </si>
+  <si>
+    <t>21ef66ba-da14-42e4-843f-64442d384f06</t>
+  </si>
+  <si>
+    <t>2f15305e-9028-45f2-83f5-6ca8db72f853</t>
+  </si>
+  <si>
+    <t>c333a5dc-1602-42e9-a278-c243a79ca0d7</t>
+  </si>
+  <si>
+    <t>5aa49315-f1d8-46cc-9dbc-b04bae539e30</t>
+  </si>
+  <si>
+    <t>b025f0b6-50fb-4835-ad68-84981391eadb</t>
+  </si>
+  <si>
+    <t>8abc8c77-3c1d-4a9c-8f38-0a8b7eb8b867</t>
+  </si>
+  <si>
+    <t>3cefe806-87af-46f7-8e5b-49466c7ef9ee</t>
+  </si>
+  <si>
+    <t>d82378ce-872a-4fee-826b-64465a4d248f</t>
+  </si>
+  <si>
+    <t>bb7a5653-36a2-4c13-be6d-ec01f3d1a362</t>
+  </si>
+  <si>
+    <t>5c34a4a2-f3e3-47b1-b920-5eeb71bf18c5</t>
+  </si>
+  <si>
+    <t>92f59c4f-2cbe-4220-9883-2224452d53ab</t>
+  </si>
+  <si>
+    <t>BHIM PRASAD SAPKOTA</t>
+  </si>
+  <si>
+    <t>LAXMAN LIMBU SUBBA</t>
+  </si>
+  <si>
+    <t>RAM CHANDRA POKHAREL</t>
+  </si>
+  <si>
+    <t>KUBER THAPA</t>
   </si>
   <si>
     <t>TIKA BAHADUR GOTAME</t>
   </si>
   <si>
-    <t>RAM CHANDRA POKHAREL</t>
-  </si>
-  <si>
-    <t>KUBER THAPA</t>
-  </si>
-  <si>
-    <t>LAXMAN LIMBU SUBBA</t>
+    <t>1301140000243900</t>
+  </si>
+  <si>
+    <t>1301140000236901</t>
+  </si>
+  <si>
+    <t>1301140000216199</t>
+  </si>
+  <si>
+    <t>1301140000233742</t>
   </si>
   <si>
     <t>1301260001744740</t>
   </si>
   <si>
-    <t>1301140000216199</t>
-  </si>
-  <si>
-    <t>1301140000233742</t>
-  </si>
-  <si>
-    <t>1301140000236901</t>
+    <t>NPE325A00008</t>
+  </si>
+  <si>
+    <t>NPE010A00006</t>
+  </si>
+  <si>
+    <t>NPE407A00004</t>
+  </si>
+  <si>
+    <t>NPE406A00006</t>
+  </si>
+  <si>
+    <t>NPE387A00008</t>
+  </si>
+  <si>
+    <t>NPE282A00001</t>
+  </si>
+  <si>
+    <t>NPE234A00002</t>
+  </si>
+  <si>
+    <t>NPE262A00003</t>
+  </si>
+  <si>
+    <t>NPE191A00004</t>
+  </si>
+  <si>
+    <t>NPE137A00007</t>
+  </si>
+  <si>
+    <t>NPE256A00005</t>
+  </si>
+  <si>
+    <t>NPE233A00004</t>
+  </si>
+  <si>
+    <t>NPE403A00003</t>
+  </si>
+  <si>
+    <t>NPE327A00004</t>
+  </si>
+  <si>
+    <t>NPE457A00009</t>
+  </si>
+  <si>
+    <t>NPE017A00001</t>
+  </si>
+  <si>
+    <t>NPE464A00005</t>
+  </si>
+  <si>
+    <t>NPE026A00002</t>
+  </si>
+  <si>
+    <t>NPE215A00001</t>
+  </si>
+  <si>
+    <t>NPE451A00002</t>
+  </si>
+  <si>
+    <t>NPE030A00012</t>
+  </si>
+  <si>
+    <t>NPE081A00007</t>
+  </si>
+  <si>
+    <t>NPE097A00003</t>
+  </si>
+  <si>
+    <t>NPE320A00009</t>
+  </si>
+  <si>
+    <t>NPE230A00000</t>
+  </si>
+  <si>
+    <t>NPE029A00006</t>
+  </si>
+  <si>
+    <t>NPE046A00000</t>
+  </si>
+  <si>
+    <t>NPE425A00006</t>
+  </si>
+  <si>
+    <t>NPE016A00003</t>
+  </si>
+  <si>
+    <t>NPE382A00009</t>
+  </si>
+  <si>
+    <t>NPE368A00008</t>
+  </si>
+  <si>
+    <t>NPE399A00003</t>
   </si>
   <si>
     <t>NPE402A00005</t>
   </si>
   <si>
-    <t>NPE016A00003</t>
-  </si>
-  <si>
-    <t>NPE026A00002</t>
-  </si>
-  <si>
-    <t>NPE403A00003</t>
-  </si>
-  <si>
-    <t>NPE327A00004</t>
-  </si>
-  <si>
-    <t>NPE256A00005</t>
-  </si>
-  <si>
-    <t>NPE406A00006</t>
-  </si>
-  <si>
-    <t>NPE407A00004</t>
-  </si>
-  <si>
-    <t>NPE191A00004</t>
-  </si>
-  <si>
-    <t>NPE046A00000</t>
+    <t>NPE298A00007</t>
   </si>
   <si>
     <t>NPE376A00001</t>
   </si>
   <si>
-    <t>NPE230A00000</t>
-  </si>
-  <si>
-    <t>NPE387A00008</t>
-  </si>
-  <si>
-    <t>NPE234A00002</t>
-  </si>
-  <si>
-    <t>NPE368A00008</t>
-  </si>
-  <si>
-    <t>NPE017A00001</t>
-  </si>
-  <si>
-    <t>NPE010A00006</t>
-  </si>
-  <si>
-    <t>NPE451A00002</t>
-  </si>
-  <si>
-    <t>NPE030A00012</t>
+    <t>NPE375A00003</t>
+  </si>
+  <si>
+    <t>NPE263A00001</t>
+  </si>
+  <si>
+    <t>NPE293A00008</t>
   </si>
   <si>
     <t>NPE167A00004</t>
   </si>
   <si>
-    <t>NPE215A00001</t>
+    <t>NPE329A00000</t>
   </si>
   <si>
     <t xml:space="preserve"> </t>
   </si>
   <si>
+    <t>GHL</t>
+  </si>
+  <si>
+    <t>HLI</t>
+  </si>
+  <si>
+    <t>HHL</t>
+  </si>
+  <si>
+    <t>BHDC</t>
+  </si>
+  <si>
+    <t>SAHAS</t>
+  </si>
+  <si>
+    <t>NGPL</t>
+  </si>
+  <si>
+    <t>SHPC</t>
+  </si>
+  <si>
+    <t>SWMF</t>
+  </si>
+  <si>
+    <t>AHPC</t>
+  </si>
+  <si>
+    <t>MFIL</t>
+  </si>
+  <si>
+    <t>API</t>
+  </si>
+  <si>
+    <t>SKBBL</t>
+  </si>
+  <si>
+    <t>RFPL</t>
+  </si>
+  <si>
+    <t>SHIVM</t>
+  </si>
+  <si>
+    <t>SNLI</t>
+  </si>
+  <si>
+    <t>GBIME</t>
+  </si>
+  <si>
+    <t>SONA</t>
+  </si>
+  <si>
+    <t>NBL</t>
+  </si>
+  <si>
+    <t>SJLIC</t>
+  </si>
+  <si>
+    <t>ILI</t>
+  </si>
+  <si>
+    <t>NMB</t>
+  </si>
+  <si>
+    <t>NMLBBL</t>
+  </si>
+  <si>
+    <t>SHINE</t>
+  </si>
+  <si>
+    <t>AKJCL</t>
+  </si>
+  <si>
+    <t>GBLBS</t>
+  </si>
+  <si>
+    <t>NICA</t>
+  </si>
+  <si>
+    <t>CBBL</t>
+  </si>
+  <si>
+    <t>PHCL</t>
+  </si>
+  <si>
+    <t>EBL</t>
+  </si>
+  <si>
+    <t>SRLI</t>
+  </si>
+  <si>
+    <t>CGH</t>
+  </si>
+  <si>
+    <t>BHL</t>
+  </si>
+  <si>
     <t>CYCL</t>
   </si>
   <si>
-    <t>EBL</t>
-  </si>
-  <si>
-    <t>NBL</t>
-  </si>
-  <si>
-    <t>RFPL</t>
-  </si>
-  <si>
-    <t>SHIVM</t>
-  </si>
-  <si>
-    <t>API</t>
-  </si>
-  <si>
-    <t>BHDC</t>
-  </si>
-  <si>
-    <t>HHL</t>
-  </si>
-  <si>
-    <t>AHPC</t>
-  </si>
-  <si>
-    <t>CBBL</t>
+    <t>SMATA</t>
   </si>
   <si>
     <t>CHDC</t>
   </si>
   <si>
-    <t>GBLBS</t>
-  </si>
-  <si>
-    <t>SAHAS</t>
-  </si>
-  <si>
-    <t>SHPC</t>
-  </si>
-  <si>
-    <t>CGH</t>
-  </si>
-  <si>
-    <t>GBIME</t>
-  </si>
-  <si>
-    <t>HLI</t>
-  </si>
-  <si>
-    <t>ILI</t>
-  </si>
-  <si>
-    <t>NMB</t>
+    <t>SHEL</t>
+  </si>
+  <si>
+    <t>RIDI</t>
+  </si>
+  <si>
+    <t>AKPL</t>
   </si>
   <si>
     <t>OHL</t>
   </si>
   <si>
-    <t>SJLIC</t>
+    <t>MHNL</t>
+  </si>
+  <si>
+    <t>GHALEMDI HYDRO LIMITED - ORDINARY SHARE</t>
+  </si>
+  <si>
+    <t>HIMALAYAN LIFE INSURANCE LIMITED - ORDINARY SHARE</t>
+  </si>
+  <si>
+    <t>HIMALAYAN HYDROPOWER LIMITED - ORDINARY SHARE</t>
+  </si>
+  <si>
+    <t>BINDHYABASINI HYDROPOWER DEVELOPMENT COMPANY LIMITED - ORDINARY SHARE</t>
+  </si>
+  <si>
+    <t>SAHAS URJA LIMITED- ORDINARY SHARE</t>
+  </si>
+  <si>
+    <t>NGADI GROUP POWER LIMITED - ORDINARY SHARE</t>
+  </si>
+  <si>
+    <t>SANIMA MAI HYDROPOWER LIMITED - ORDINARY SHARE</t>
+  </si>
+  <si>
+    <t>SURYODAYA WOMI LAGHUBITTA BITTIYA SANSTHA LIMITED- ORDINARY SHARE</t>
+  </si>
+  <si>
+    <t>ARUN VALLEY HYDROPOWER DEVELOPMENT COMPANY LIMITED - ORDINARY SHARE</t>
+  </si>
+  <si>
+    <t>MANJUSHREE FINANCE LIMITED - ORDINARY SHARE</t>
+  </si>
+  <si>
+    <t>API POWER COMPANY LIMITED- ORDINARY SHARE</t>
+  </si>
+  <si>
+    <t>SANA KISAN BIKAS LAGHUBITTA BITTIYA SANSTHA LIMITED - ORDINARY SHARE</t>
+  </si>
+  <si>
+    <t>RIVER FALLS POWER LIMITED - ORDINARY SHARE</t>
+  </si>
+  <si>
+    <t>SHIVAM CEMENTS LIMITED - ORDINARY SHARE</t>
+  </si>
+  <si>
+    <t>SUN NEPAL LIFE INSURANCE COMPANY LIMITED - ORDINARY SHARE</t>
+  </si>
+  <si>
+    <t>GLOBAL IME BANK LIMITED - ORDINARY SHARE</t>
+  </si>
+  <si>
+    <t>SONAPUR MINERALS AND OIL LIMITED - ORDINARY SHARE</t>
+  </si>
+  <si>
+    <t>NEPAL BANK LIMITED - ORDINARY SHARE</t>
+  </si>
+  <si>
+    <t>SURYAJYOTI LIFE INSURANCE COMPANY LIMITED - ORDINARY SHARE</t>
+  </si>
+  <si>
+    <t>IME LIFE INSURANCE COMPANY LIMITED - ORDINARY SHARE</t>
+  </si>
+  <si>
+    <t>NMB BANK LIMITED-ORDINARY SHARE</t>
+  </si>
+  <si>
+    <t>NERUDE MIRMIRE LAGHUBITA BITTIYA SANSTHA LIMITED - ORDINARY SHARE</t>
+  </si>
+  <si>
+    <t>SHINE RESUNGA DEVELOPMENT BANK LIMITED - ORDINARY SHARE</t>
+  </si>
+  <si>
+    <t>ANKHU KHOLA JALVIDHYUT COMPANY LIMITED - ORDIANRY SHARE</t>
+  </si>
+  <si>
+    <t>GRAMEEN BIKAS LAGHUBITTA BITTIYA SANSTHA LIMITED - ORDINARY SHARE</t>
+  </si>
+  <si>
+    <t>NIC ASIA BANK LIMITED - ORDINARY SHARE</t>
+  </si>
+  <si>
+    <t>CHHIMEK LAGHUBITTA BITTIYA SANSTHA  LIMITED - ORDINARY SHARE</t>
+  </si>
+  <si>
+    <t>PEOPLES HYDROPOWER COMPANY LIMITED - ORDINARY SHARE</t>
+  </si>
+  <si>
+    <t>EVEREST BANK LIMITED - ORDINARY SHARE</t>
+  </si>
+  <si>
+    <t>SANIMA RELIANCE LIFE INSURANCE LIMITED - ORDINARY SHARE</t>
+  </si>
+  <si>
+    <t>CHANDRAGIRI HILLS LIMITED - ORDINARY SHARE</t>
+  </si>
+  <si>
+    <t>BALEPHI HYDROPOWER LIMITED-ORDINARY SHARE</t>
   </si>
   <si>
     <t>CYC NEPAL LAGHUBITTA BITTIYA SANSTHA LIMITED - ORDINARY SHARE</t>
   </si>
   <si>
-    <t>EVEREST BANK LIMITED - ORDINARY SHARE</t>
-  </si>
-  <si>
-    <t>NEPAL BANK LIMITED - ORDINARY SHARE</t>
-  </si>
-  <si>
-    <t>RIVER FALLS POWER LIMITED - ORDINARY SHARE</t>
-  </si>
-  <si>
-    <t>SHIVAM CEMENTS LIMITED - ORDINARY SHARE</t>
-  </si>
-  <si>
-    <t>API POWER COMPANY LIMITED- ORDINARY SHARE</t>
-  </si>
-  <si>
-    <t>BINDHYABASINI HYDROPOWER DEVELOPMENT COMPANY LIMITED - ORDINARY SHARE</t>
-  </si>
-  <si>
-    <t>HIMALAYAN HYDROPOWER LIMITED - ORDINARY SHARE</t>
-  </si>
-  <si>
-    <t>ARUN VALLEY HYDROPOWER DEVELOPMENT COMPANY LIMITED - ORDINARY SHARE</t>
-  </si>
-  <si>
-    <t>CHHIMEK LAGHUBITTA BITTIYA SANSTHA  LIMITED - ORDINARY SHARE</t>
+    <t>SAMATA GHARELU LAGHUBITTA BITTIYA SANSTHA LIMITED - ORDINARY SHARE</t>
   </si>
   <si>
     <t>CEDB HOLDINGS LIMITED - ORDIINARY SHARE</t>
   </si>
   <si>
-    <t>GRAMEEN BIKAS LAGHUBITTA BITTIYA SANSTHA LIMITED - ORDINARY SHARE</t>
-  </si>
-  <si>
-    <t>SAHAS URJA LIMITED- ORDINARY SHARE</t>
-  </si>
-  <si>
-    <t>SANIMA MAI HYDROPOWER LIMITED - ORDINARY SHARE</t>
-  </si>
-  <si>
-    <t>CHANDRAGIRI HILLS LIMITED - ORDINARY SHARE</t>
-  </si>
-  <si>
-    <t>GLOBAL IME BANK LIMITED - ORDINARY SHARE</t>
-  </si>
-  <si>
-    <t>HIMALAYAN LIFE INSURANCE LIMITED - ORDINARY SHARE</t>
-  </si>
-  <si>
-    <t>IME LIFE INSURANCE COMPANY LIMITED - ORDINARY SHARE</t>
-  </si>
-  <si>
-    <t>NMB BANK LIMITED-ORDINARY SHARE</t>
+    <t>SINGATI HYDRO ENERGY LIMITED- ORDINARY SHARE</t>
+  </si>
+  <si>
+    <t>RIDI POWER COMPANY LIMITED- ORDINARY SHARE</t>
+  </si>
+  <si>
+    <t>ARUN KABELI POWER LIMITED - ORDINARY SHARE</t>
   </si>
   <si>
     <t>ORIENTAL HOTEL LIMITED - ORDINARY SHARE</t>
   </si>
   <si>
-    <t>SURYAJYOTI LIFE INSURANCE COMPANY LIMITED - ORDINARY SHARE</t>
+    <t>MOUNTAIN HYDRO NEPAL LIMITED - ORDINARY SHARE</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>1600, 1600</t>
+  </si>
+  <si>
+    <t>7000</t>
+  </si>
+  <si>
+    <t>5500, 611</t>
+  </si>
+  <si>
+    <t>2650</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>2100</t>
+  </si>
+  <si>
+    <t>5700</t>
   </si>
   <si>
     <t>500</t>
   </si>
   <si>
-    <t>2100</t>
-  </si>
-  <si>
-    <t>7000</t>
-  </si>
-  <si>
-    <t>5700</t>
+    <t>398, 1600, 418</t>
+  </si>
+  <si>
+    <t>149</t>
+  </si>
+  <si>
+    <t>3000, 3200</t>
+  </si>
+  <si>
+    <t>10501</t>
+  </si>
+  <si>
+    <t>600, 2996</t>
   </si>
   <si>
     <t>1967, 12</t>
   </si>
   <si>
-    <t>5500, 611</t>
-  </si>
-  <si>
-    <t>2650</t>
-  </si>
-  <si>
-    <t>600, 2996</t>
-  </si>
-  <si>
-    <t>1600, 1600</t>
-  </si>
-  <si>
-    <t>398, 1600, 418</t>
-  </si>
-  <si>
     <t>600, 2730</t>
   </si>
   <si>
-    <t>3000, 3200</t>
+    <t>376.3112, 379.535</t>
+  </si>
+  <si>
+    <t>439.5169</t>
+  </si>
+  <si>
+    <t>672.7085, 549.1668</t>
+  </si>
+  <si>
+    <t>496.3731</t>
+  </si>
+  <si>
+    <t>281.3</t>
+  </si>
+  <si>
+    <t>300.8866</t>
+  </si>
+  <si>
+    <t>286.1583</t>
   </si>
   <si>
     <t>304.1957</t>
   </si>
   <si>
-    <t>300.8866</t>
-  </si>
-  <si>
-    <t>439.5169</t>
-  </si>
-  <si>
-    <t>286.1583</t>
+    <t>455.0858, 460.6176, 441.6165</t>
+  </si>
+  <si>
+    <t>408.5719</t>
+  </si>
+  <si>
+    <t>191.709</t>
+  </si>
+  <si>
+    <t>570.5232, 576.8766</t>
+  </si>
+  <si>
+    <t>100.0</t>
+  </si>
+  <si>
+    <t>862.7329, 906.1706</t>
   </si>
   <si>
     <t>2403.3708, 2542.5746</t>
   </si>
   <si>
-    <t>672.7085, 549.1668</t>
-  </si>
-  <si>
-    <t>496.3731</t>
-  </si>
-  <si>
-    <t>862.7329, 906.1706</t>
-  </si>
-  <si>
-    <t>376.3112, 379.535</t>
-  </si>
-  <si>
-    <t>455.0858, 460.6176, 441.6165</t>
+    <t>300.0816</t>
   </si>
   <si>
     <t>692.4222, 711.3342</t>
   </si>
   <si>
-    <t>570.5232, 576.8766</t>
+    <t>ON-MARKET, ON-MARKET</t>
   </si>
   <si>
     <t>ON-MARKET</t>
   </si>
   <si>
-    <t>ON-MARKET, ON-MARKET</t>
-  </si>
-  <si>
     <t>ON-MARKET, BO-BO/FAMILY TRANSFER</t>
   </si>
   <si>
     <t>ON-MARKET, ON-MARKET, ON-MARKET</t>
   </si>
   <si>
+    <t>BO-BO/FAMILY TRANSFER</t>
+  </si>
+  <si>
     <t>YES</t>
   </si>
   <si>
+    <t>NO</t>
+  </si>
+  <si>
+    <t>20250835366</t>
+  </si>
+  <si>
+    <t>LL284136</t>
+  </si>
+  <si>
+    <t>KT188844</t>
+  </si>
+  <si>
     <t>20240825397</t>
   </si>
   <si>
-    <t>20250328769</t>
-  </si>
-  <si>
-    <t>KT188844</t>
-  </si>
-  <si>
-    <t>LL284136</t>
-  </si>
-  <si>
-    <t>2025-11-26 04:50:02</t>
+    <t>2025-12-02 02:28:01</t>
+  </si>
+  <si>
+    <t>SAJAN</t>
+  </si>
+  <si>
+    <t>YUBARAJ</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>THAKUR</t>
   </si>
 </sst>
 </file>
@@ -879,13 +1170,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AZ23"/>
+  <dimension ref="A1:AZ45"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="52" width="18.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:40">
+    <row r="1" spans="1:41">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1006,37 +1297,40 @@
       <c r="AN1" s="2" t="s">
         <v>39</v>
       </c>
+      <c r="AO1" s="2" t="s">
+        <v>40</v>
+      </c>
     </row>
-    <row r="2" spans="1:40">
+    <row r="2" spans="1:41">
       <c r="A2" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>62</v>
+        <v>85</v>
       </c>
       <c r="C2" s="1">
-        <v>1744740</v>
+        <v>243900</v>
       </c>
       <c r="D2" s="1">
-        <v>12600</v>
+        <v>11400</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="F2" s="1">
-        <v>13</v>
+        <v>2995</v>
       </c>
       <c r="G2" s="1">
         <v>0</v>
       </c>
       <c r="H2" s="1">
-        <v>13</v>
+        <v>2995</v>
       </c>
       <c r="I2" s="1">
         <v>0</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="K2" s="1">
         <v>0</v>
@@ -1045,28 +1339,28 @@
         <v>0</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>91</v>
+        <v>135</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>92</v>
+        <v>136</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>113</v>
+        <v>176</v>
       </c>
       <c r="P2" s="1">
-        <v>13</v>
+        <v>2995</v>
       </c>
       <c r="Q2" s="1">
-        <v>100</v>
+        <v>249.45</v>
       </c>
       <c r="R2" s="1">
-        <v>1300</v>
-      </c>
-      <c r="S2" s="1">
-        <v>0</v>
-      </c>
-      <c r="T2" s="1">
-        <v>0</v>
+        <v>747102.0699999999</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>216</v>
       </c>
       <c r="U2" s="1">
         <v>0</v>
@@ -1075,13 +1369,13 @@
         <v>0</v>
       </c>
       <c r="X2" s="1" t="s">
-        <v>162</v>
+        <v>254</v>
       </c>
       <c r="Y2" s="1">
-        <v>0</v>
+        <v>1624741.28</v>
       </c>
       <c r="Z2" s="1" t="s">
-        <v>163</v>
+        <v>256</v>
       </c>
       <c r="AA2" s="1">
         <v>0</v>
@@ -1090,72 +1384,75 @@
         <v>0</v>
       </c>
       <c r="AC2" s="1">
-        <v>1300</v>
+        <v>747102.75</v>
       </c>
       <c r="AD2" s="1">
-        <v>100</v>
+        <v>249.45</v>
       </c>
       <c r="AE2" s="1">
-        <v>1505</v>
+        <v>214.2</v>
       </c>
       <c r="AF2" s="1">
-        <v>19565</v>
+        <v>641529</v>
       </c>
       <c r="AG2" s="1">
-        <v>58.695</v>
+        <v>1924.587</v>
       </c>
       <c r="AH2" s="1">
-        <v>2.93475</v>
+        <v>96.22935</v>
       </c>
       <c r="AI2" s="1">
         <v>25</v>
       </c>
       <c r="AJ2" s="1">
-        <v>-18178.37025</v>
+        <v>107619.5663500001</v>
       </c>
       <c r="AK2" s="1">
-        <v>-1363.37776875</v>
+        <v>8071.467476250007</v>
       </c>
       <c r="AL2" s="1">
-        <v>19541.75</v>
+        <v>-115691.03</v>
       </c>
       <c r="AM2" s="1">
-        <v>1503.21</v>
+        <v>-15.49</v>
       </c>
       <c r="AN2" s="1" t="s">
-        <v>167</v>
+        <v>260</v>
+      </c>
+      <c r="AO2" s="1" t="s">
+        <v>261</v>
       </c>
     </row>
-    <row r="3" spans="1:40">
+    <row r="3" spans="1:41">
       <c r="A3" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="C3" s="1">
-        <v>1744740</v>
+        <v>236901</v>
       </c>
       <c r="D3" s="1">
-        <v>12600</v>
+        <v>11400</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>66</v>
+        <v>91</v>
       </c>
       <c r="F3" s="1">
-        <v>10</v>
+        <v>3200</v>
       </c>
       <c r="G3" s="1">
         <v>0</v>
       </c>
       <c r="H3" s="1">
-        <v>10</v>
+        <v>3200</v>
       </c>
       <c r="I3" s="1">
         <v>0</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>71</v>
+        <v>96</v>
       </c>
       <c r="K3" s="1">
         <v>0</v>
@@ -1164,117 +1461,123 @@
         <v>0</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>91</v>
+        <v>135</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>93</v>
+        <v>137</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>114</v>
+        <v>177</v>
       </c>
       <c r="P3" s="1">
-        <v>210</v>
+        <v>33241</v>
       </c>
       <c r="Q3" s="1">
-        <v>642.6900000000001</v>
+        <v>256.02</v>
       </c>
       <c r="R3" s="1">
-        <v>134964.14</v>
-      </c>
-      <c r="S3" s="1">
-        <v>0</v>
-      </c>
-      <c r="T3" s="1">
-        <v>0</v>
+        <v>8510258.82</v>
+      </c>
+      <c r="S3" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="T3" s="1" t="s">
+        <v>232</v>
       </c>
       <c r="U3" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V3" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="W3" s="1" t="s">
+        <v>249</v>
       </c>
       <c r="X3" s="1" t="s">
-        <v>162</v>
+        <v>254</v>
       </c>
       <c r="Y3" s="1">
-        <v>0</v>
+        <v>442.24</v>
       </c>
       <c r="Z3" s="1" t="s">
-        <v>163</v>
+        <v>257</v>
       </c>
       <c r="AA3" s="1">
-        <v>0</v>
+        <v>1209353.92</v>
       </c>
       <c r="AB3" s="1">
-        <v>0</v>
+        <v>3200</v>
       </c>
       <c r="AC3" s="1">
-        <v>6426.900000000001</v>
+        <v>1209353.92</v>
       </c>
       <c r="AD3" s="1">
-        <v>642.6900000000001</v>
+        <v>377.9231</v>
       </c>
       <c r="AE3" s="1">
-        <v>657</v>
+        <v>379.8</v>
       </c>
       <c r="AF3" s="1">
-        <v>6570</v>
+        <v>1215360</v>
       </c>
       <c r="AG3" s="1">
-        <v>19.71</v>
+        <v>3646.08</v>
       </c>
       <c r="AH3" s="1">
-        <v>0.9854999999999999</v>
+        <v>182.304</v>
       </c>
       <c r="AI3" s="1">
         <v>25</v>
       </c>
       <c r="AJ3" s="1">
-        <v>-97.40449999999964</v>
+        <v>-2152.695999999996</v>
       </c>
       <c r="AK3" s="1">
-        <v>-7.305337499999973</v>
+        <v>-161.4521999999997</v>
       </c>
       <c r="AL3" s="1">
-        <v>104.71</v>
+        <v>2314.15</v>
       </c>
       <c r="AM3" s="1">
-        <v>1.63</v>
+        <v>0.19</v>
       </c>
       <c r="AN3" s="1" t="s">
-        <v>167</v>
+        <v>260</v>
+      </c>
+      <c r="AO3" s="1" t="s">
+        <v>262</v>
       </c>
     </row>
-    <row r="4" spans="1:40">
+    <row r="4" spans="1:41">
       <c r="A4" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="C4" s="1">
-        <v>1744740</v>
+        <v>216199</v>
       </c>
       <c r="D4" s="1">
-        <v>12600</v>
+        <v>11400</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="F4" s="1">
-        <v>500</v>
+        <v>7000</v>
       </c>
       <c r="G4" s="1">
         <v>0</v>
       </c>
       <c r="H4" s="1">
-        <v>500</v>
+        <v>7000</v>
       </c>
       <c r="I4" s="1">
         <v>0</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="K4" s="1">
         <v>0</v>
@@ -1283,28 +1586,28 @@
         <v>0</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>91</v>
+        <v>135</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>94</v>
+        <v>138</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>115</v>
+        <v>178</v>
       </c>
       <c r="P4" s="1">
-        <v>210</v>
+        <v>2010</v>
       </c>
       <c r="Q4" s="1">
-        <v>642.6900000000001</v>
+        <v>572.02</v>
       </c>
       <c r="R4" s="1">
-        <v>134964.14</v>
+        <v>1149757.59</v>
       </c>
       <c r="S4" s="1" t="s">
-        <v>134</v>
+        <v>218</v>
       </c>
       <c r="T4" s="1" t="s">
-        <v>146</v>
+        <v>233</v>
       </c>
       <c r="U4" s="1">
         <v>1</v>
@@ -1313,75 +1616,75 @@
         <v>1</v>
       </c>
       <c r="W4" s="1" t="s">
-        <v>158</v>
+        <v>250</v>
       </c>
       <c r="X4" s="1" t="s">
-        <v>162</v>
+        <v>255</v>
       </c>
       <c r="Y4" s="1">
         <v>0</v>
       </c>
-      <c r="Z4" s="1" t="s">
-        <v>163</v>
-      </c>
       <c r="AA4" s="1">
-        <v>152097.85</v>
+        <v>3076618.3</v>
       </c>
       <c r="AB4" s="1">
-        <v>500</v>
+        <v>7000</v>
       </c>
       <c r="AC4" s="1">
-        <v>152097.85</v>
+        <v>3076618.3</v>
       </c>
       <c r="AD4" s="1">
-        <v>304.1957</v>
+        <v>439.5169</v>
       </c>
       <c r="AE4" s="1">
-        <v>244</v>
+        <v>344</v>
       </c>
       <c r="AF4" s="1">
-        <v>122000</v>
+        <v>2408000</v>
       </c>
       <c r="AG4" s="1">
-        <v>366</v>
+        <v>7224</v>
       </c>
       <c r="AH4" s="1">
-        <v>18.3</v>
+        <v>361.2</v>
       </c>
       <c r="AI4" s="1">
         <v>25</v>
       </c>
       <c r="AJ4" s="1">
-        <v>30507.14999999999</v>
+        <v>676228.5000000005</v>
       </c>
       <c r="AK4" s="1">
-        <v>2288.03625</v>
+        <v>50717.13750000003</v>
       </c>
       <c r="AL4" s="1">
-        <v>-32795.19</v>
+        <v>-726945.64</v>
       </c>
       <c r="AM4" s="1">
-        <v>-21.56</v>
+        <v>-23.63</v>
       </c>
       <c r="AN4" s="1" t="s">
-        <v>167</v>
+        <v>260</v>
+      </c>
+      <c r="AO4" s="1" t="s">
+        <v>263</v>
       </c>
     </row>
-    <row r="5" spans="1:40">
+    <row r="5" spans="1:41">
       <c r="A5" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="C5" s="1">
-        <v>1744740</v>
+        <v>216199</v>
       </c>
       <c r="D5" s="1">
-        <v>12600</v>
+        <v>11400</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="F5" s="1">
         <v>10</v>
@@ -1396,7 +1699,7 @@
         <v>0</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="K5" s="1">
         <v>0</v>
@@ -1405,28 +1708,28 @@
         <v>0</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>91</v>
+        <v>135</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>95</v>
+        <v>139</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>116</v>
+        <v>179</v>
       </c>
       <c r="P5" s="1">
-        <v>10</v>
+        <v>2010</v>
       </c>
       <c r="Q5" s="1">
-        <v>100</v>
+        <v>572.02</v>
       </c>
       <c r="R5" s="1">
-        <v>1000</v>
-      </c>
-      <c r="S5" s="1">
-        <v>0</v>
-      </c>
-      <c r="T5" s="1">
-        <v>0</v>
+        <v>1149757.59</v>
+      </c>
+      <c r="S5" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="T5" s="1" t="s">
+        <v>216</v>
       </c>
       <c r="U5" s="1">
         <v>0</v>
@@ -1435,14 +1738,11 @@
         <v>0</v>
       </c>
       <c r="X5" s="1" t="s">
-        <v>162</v>
+        <v>255</v>
       </c>
       <c r="Y5" s="1">
         <v>0</v>
       </c>
-      <c r="Z5" s="1" t="s">
-        <v>163</v>
-      </c>
       <c r="AA5" s="1">
         <v>0</v>
       </c>
@@ -1450,191 +1750,200 @@
         <v>0</v>
       </c>
       <c r="AC5" s="1">
-        <v>1000</v>
+        <v>5720.2</v>
       </c>
       <c r="AD5" s="1">
-        <v>100</v>
+        <v>572.02</v>
       </c>
       <c r="AE5" s="1">
-        <v>358</v>
+        <v>485.1</v>
       </c>
       <c r="AF5" s="1">
-        <v>3580</v>
+        <v>4851</v>
       </c>
       <c r="AG5" s="1">
-        <v>10.74</v>
+        <v>14.553</v>
       </c>
       <c r="AH5" s="1">
-        <v>0.5369999999999999</v>
+        <v>0.7276499999999999</v>
       </c>
       <c r="AI5" s="1">
         <v>25</v>
       </c>
       <c r="AJ5" s="1">
-        <v>-2543.723</v>
+        <v>909.4806499999995</v>
       </c>
       <c r="AK5" s="1">
-        <v>-190.779225</v>
+        <v>68.21104874999996</v>
       </c>
       <c r="AL5" s="1">
-        <v>2734.5</v>
+        <v>-977.6900000000001</v>
       </c>
       <c r="AM5" s="1">
-        <v>273.45</v>
+        <v>-17.09</v>
       </c>
       <c r="AN5" s="1" t="s">
-        <v>167</v>
+        <v>260</v>
+      </c>
+      <c r="AO5" s="1" t="s">
+        <v>263</v>
       </c>
     </row>
-    <row r="6" spans="1:40">
+    <row r="6" spans="1:41">
       <c r="A6" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="C6" s="1">
-        <v>1744740</v>
+        <v>233742</v>
       </c>
       <c r="D6" s="1">
-        <v>12600</v>
+        <v>11400</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>66</v>
+        <v>93</v>
       </c>
       <c r="F6" s="1">
-        <v>8</v>
+        <v>16767</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
       </c>
       <c r="H6" s="1">
-        <v>8</v>
+        <v>6111</v>
       </c>
       <c r="I6" s="1">
         <v>0</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="K6" s="1">
         <v>0</v>
       </c>
       <c r="L6" s="1">
-        <v>0</v>
+        <v>10656</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>91</v>
+        <v>135</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>96</v>
+        <v>140</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>117</v>
+        <v>180</v>
       </c>
       <c r="P6" s="1">
-        <v>108</v>
+        <v>12446</v>
       </c>
       <c r="Q6" s="1">
-        <v>520.5700000000001</v>
+        <v>593.01</v>
       </c>
       <c r="R6" s="1">
-        <v>56221.96</v>
-      </c>
-      <c r="S6" s="1">
-        <v>0</v>
-      </c>
-      <c r="T6" s="1">
-        <v>0</v>
+        <v>7380609.18</v>
+      </c>
+      <c r="S6" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="T6" s="1" t="s">
+        <v>234</v>
       </c>
       <c r="U6" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V6" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="W6" s="1" t="s">
+        <v>251</v>
       </c>
       <c r="X6" s="1" t="s">
-        <v>162</v>
+        <v>254</v>
       </c>
       <c r="Y6" s="1">
-        <v>0</v>
+        <v>592006.89</v>
       </c>
       <c r="Z6" s="1" t="s">
-        <v>163</v>
+        <v>258</v>
       </c>
       <c r="AA6" s="1">
-        <v>0</v>
+        <v>4035437.6648</v>
       </c>
       <c r="AB6" s="1">
-        <v>0</v>
+        <v>6111</v>
       </c>
       <c r="AC6" s="1">
-        <v>4164.56</v>
+        <v>10354552.2248</v>
       </c>
       <c r="AD6" s="1">
-        <v>520.5700000000001</v>
+        <v>617.5554496809209</v>
       </c>
       <c r="AE6" s="1">
-        <v>617</v>
+        <v>555.9</v>
       </c>
       <c r="AF6" s="1">
-        <v>4936</v>
+        <v>9320775.299999999</v>
       </c>
       <c r="AG6" s="1">
-        <v>14.808</v>
+        <v>27962.3259</v>
       </c>
       <c r="AH6" s="1">
-        <v>0.7403999999999999</v>
+        <v>1398.116295</v>
       </c>
       <c r="AI6" s="1">
         <v>25</v>
       </c>
       <c r="AJ6" s="1">
-        <v>-730.8915999999999</v>
+        <v>1063162.366995001</v>
       </c>
       <c r="AK6" s="1">
-        <v>-54.81686999999999</v>
+        <v>79737.17752462509</v>
       </c>
       <c r="AL6" s="1">
-        <v>785.71</v>
+        <v>-1142899.54</v>
       </c>
       <c r="AM6" s="1">
-        <v>18.87</v>
+        <v>-11.04</v>
       </c>
       <c r="AN6" s="1" t="s">
-        <v>167</v>
+        <v>260</v>
+      </c>
+      <c r="AO6" s="1" t="s">
+        <v>262</v>
       </c>
     </row>
-    <row r="7" spans="1:40">
+    <row r="7" spans="1:41">
       <c r="A7" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>63</v>
+        <v>85</v>
       </c>
       <c r="C7" s="1">
-        <v>216199</v>
+        <v>243900</v>
       </c>
       <c r="D7" s="1">
         <v>11400</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>67</v>
+        <v>90</v>
       </c>
       <c r="F7" s="1">
-        <v>2100</v>
+        <v>500</v>
       </c>
       <c r="G7" s="1">
         <v>0</v>
       </c>
       <c r="H7" s="1">
-        <v>2100</v>
+        <v>500</v>
       </c>
       <c r="I7" s="1">
         <v>0</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="K7" s="1">
         <v>0</v>
@@ -1643,391 +1952,397 @@
         <v>0</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>91</v>
+        <v>135</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>97</v>
+        <v>141</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>118</v>
+        <v>181</v>
       </c>
       <c r="P7" s="1">
-        <v>12000</v>
+        <v>1000</v>
       </c>
       <c r="Q7" s="1">
-        <v>316.8</v>
+        <v>385.35</v>
       </c>
       <c r="R7" s="1">
-        <v>3801551.6</v>
+        <v>385349.8</v>
       </c>
       <c r="S7" s="1" t="s">
-        <v>135</v>
+        <v>216</v>
       </c>
       <c r="T7" s="1" t="s">
-        <v>147</v>
+        <v>216</v>
       </c>
       <c r="U7" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V7" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="W7" s="1" t="s">
-        <v>158</v>
+        <v>0</v>
       </c>
       <c r="X7" s="1" t="s">
-        <v>162</v>
+        <v>254</v>
       </c>
       <c r="Y7" s="1">
-        <v>0</v>
+        <v>1624741.28</v>
       </c>
       <c r="Z7" s="1" t="s">
-        <v>164</v>
+        <v>256</v>
       </c>
       <c r="AA7" s="1">
-        <v>631861.86</v>
+        <v>0</v>
       </c>
       <c r="AB7" s="1">
-        <v>2100</v>
+        <v>0</v>
       </c>
       <c r="AC7" s="1">
-        <v>631861.86</v>
+        <v>192675</v>
       </c>
       <c r="AD7" s="1">
-        <v>300.8866</v>
+        <v>385.35</v>
       </c>
       <c r="AE7" s="1">
-        <v>285</v>
+        <v>398.2</v>
       </c>
       <c r="AF7" s="1">
-        <v>598500</v>
+        <v>199100</v>
       </c>
       <c r="AG7" s="1">
-        <v>1795.5</v>
+        <v>597.3000000000001</v>
       </c>
       <c r="AH7" s="1">
-        <v>89.77499999999999</v>
+        <v>29.865</v>
       </c>
       <c r="AI7" s="1">
         <v>25</v>
       </c>
       <c r="AJ7" s="1">
-        <v>35272.13500000001</v>
+        <v>-5772.835000000021</v>
       </c>
       <c r="AK7" s="1">
-        <v>2645.410125000001</v>
+        <v>-432.9626250000015</v>
       </c>
       <c r="AL7" s="1">
-        <v>-37917.55</v>
+        <v>6205.8</v>
       </c>
       <c r="AM7" s="1">
-        <v>-6</v>
+        <v>3.22</v>
       </c>
       <c r="AN7" s="1" t="s">
-        <v>167</v>
+        <v>260</v>
+      </c>
+      <c r="AO7" s="1" t="s">
+        <v>261</v>
       </c>
     </row>
-    <row r="8" spans="1:40">
+    <row r="8" spans="1:41">
       <c r="A8" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>63</v>
+        <v>88</v>
       </c>
       <c r="C8" s="1">
-        <v>216199</v>
+        <v>233742</v>
       </c>
       <c r="D8" s="1">
         <v>11400</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>67</v>
+        <v>93</v>
       </c>
       <c r="F8" s="1">
-        <v>10</v>
+        <v>16650</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
       </c>
       <c r="H8" s="1">
-        <v>10</v>
+        <v>4600</v>
       </c>
       <c r="I8" s="1">
         <v>0</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>76</v>
+        <v>101</v>
       </c>
       <c r="K8" s="1">
         <v>0</v>
       </c>
       <c r="L8" s="1">
-        <v>0</v>
+        <v>12050</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>91</v>
+        <v>135</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>98</v>
+        <v>142</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>119</v>
+        <v>182</v>
       </c>
       <c r="P8" s="1">
-        <v>2010</v>
+        <v>20500</v>
       </c>
       <c r="Q8" s="1">
-        <v>572.02</v>
+        <v>653.46</v>
       </c>
       <c r="R8" s="1">
-        <v>1149757.59</v>
-      </c>
-      <c r="S8" s="1">
-        <v>0</v>
-      </c>
-      <c r="T8" s="1">
-        <v>0</v>
+        <v>13395955.45</v>
+      </c>
+      <c r="S8" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="T8" s="1" t="s">
+        <v>235</v>
       </c>
       <c r="U8" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V8" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="W8" s="1" t="s">
+        <v>250</v>
       </c>
       <c r="X8" s="1" t="s">
-        <v>162</v>
+        <v>254</v>
       </c>
       <c r="Y8" s="1">
-        <v>0</v>
+        <v>592006.89</v>
       </c>
       <c r="Z8" s="1" t="s">
-        <v>164</v>
+        <v>258</v>
       </c>
       <c r="AA8" s="1">
-        <v>0</v>
+        <v>1315388.715</v>
       </c>
       <c r="AB8" s="1">
-        <v>0</v>
+        <v>2650</v>
       </c>
       <c r="AC8" s="1">
-        <v>5720.2</v>
+        <v>10463828.715</v>
       </c>
       <c r="AD8" s="1">
-        <v>572.02</v>
+        <v>628.4581810810811</v>
       </c>
       <c r="AE8" s="1">
-        <v>499</v>
+        <v>538.3</v>
       </c>
       <c r="AF8" s="1">
-        <v>4990</v>
+        <v>8962695</v>
       </c>
       <c r="AG8" s="1">
-        <v>14.97</v>
+        <v>26888.085</v>
       </c>
       <c r="AH8" s="1">
-        <v>0.7484999999999999</v>
+        <v>1344.40425</v>
       </c>
       <c r="AI8" s="1">
         <v>25</v>
       </c>
       <c r="AJ8" s="1">
-        <v>770.9184999999998</v>
+        <v>1529391.20425</v>
       </c>
       <c r="AK8" s="1">
-        <v>57.81888749999998</v>
+        <v>114704.34031875</v>
       </c>
       <c r="AL8" s="1">
-        <v>-828.74</v>
+        <v>-1644095.54</v>
       </c>
       <c r="AM8" s="1">
-        <v>-14.49</v>
+        <v>-15.71</v>
       </c>
       <c r="AN8" s="1" t="s">
-        <v>167</v>
+        <v>260</v>
+      </c>
+      <c r="AO8" s="1" t="s">
+        <v>262</v>
       </c>
     </row>
-    <row r="9" spans="1:40">
+    <row r="9" spans="1:41">
       <c r="A9" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>63</v>
+        <v>85</v>
       </c>
       <c r="C9" s="1">
-        <v>216199</v>
+        <v>243900</v>
       </c>
       <c r="D9" s="1">
         <v>11400</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>67</v>
+        <v>90</v>
       </c>
       <c r="F9" s="1">
-        <v>7000</v>
+        <v>500</v>
       </c>
       <c r="G9" s="1">
         <v>0</v>
       </c>
       <c r="H9" s="1">
-        <v>7000</v>
+        <v>0</v>
       </c>
       <c r="I9" s="1">
         <v>0</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>77</v>
+        <v>102</v>
       </c>
       <c r="K9" s="1">
         <v>0</v>
       </c>
       <c r="L9" s="1">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>91</v>
+        <v>135</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>99</v>
+        <v>143</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>120</v>
+        <v>183</v>
       </c>
       <c r="P9" s="1">
-        <v>2010</v>
+        <v>500</v>
       </c>
       <c r="Q9" s="1">
-        <v>572.02</v>
+        <v>715.5</v>
       </c>
       <c r="R9" s="1">
-        <v>1149757.59</v>
+        <v>357749.96</v>
       </c>
       <c r="S9" s="1" t="s">
-        <v>136</v>
+        <v>216</v>
       </c>
       <c r="T9" s="1" t="s">
-        <v>148</v>
+        <v>216</v>
       </c>
       <c r="U9" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V9" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="W9" s="1" t="s">
-        <v>158</v>
+        <v>0</v>
       </c>
       <c r="X9" s="1" t="s">
-        <v>162</v>
+        <v>254</v>
       </c>
       <c r="Y9" s="1">
-        <v>0</v>
+        <v>1624741.28</v>
       </c>
       <c r="Z9" s="1" t="s">
-        <v>164</v>
+        <v>256</v>
       </c>
       <c r="AA9" s="1">
-        <v>3076618.3</v>
+        <v>0</v>
       </c>
       <c r="AB9" s="1">
-        <v>7000</v>
+        <v>0</v>
       </c>
       <c r="AC9" s="1">
-        <v>3076618.3</v>
+        <v>357750</v>
       </c>
       <c r="AD9" s="1">
-        <v>439.5169</v>
+        <v>715.5</v>
       </c>
       <c r="AE9" s="1">
-        <v>336.5</v>
+        <v>703.5</v>
       </c>
       <c r="AF9" s="1">
-        <v>2355500</v>
+        <v>351750</v>
       </c>
       <c r="AG9" s="1">
-        <v>7066.5</v>
+        <v>1055.25</v>
       </c>
       <c r="AH9" s="1">
-        <v>353.325</v>
+        <v>52.7625</v>
       </c>
       <c r="AI9" s="1">
         <v>25</v>
       </c>
       <c r="AJ9" s="1">
-        <v>728563.1250000005</v>
+        <v>7133.012500000012</v>
       </c>
       <c r="AK9" s="1">
-        <v>54642.23437500004</v>
+        <v>534.9759375000009</v>
       </c>
       <c r="AL9" s="1">
-        <v>-783205.36</v>
+        <v>-7667.99</v>
       </c>
       <c r="AM9" s="1">
-        <v>-25.46</v>
+        <v>-2.14</v>
       </c>
       <c r="AN9" s="1" t="s">
-        <v>167</v>
+        <v>260</v>
+      </c>
+      <c r="AO9" s="1" t="s">
+        <v>261</v>
       </c>
     </row>
-    <row r="10" spans="1:40">
+    <row r="10" spans="1:41">
       <c r="A10" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>64</v>
+        <v>85</v>
       </c>
       <c r="C10" s="1">
-        <v>233742</v>
+        <v>243900</v>
       </c>
       <c r="D10" s="1">
         <v>11400</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="F10" s="1">
-        <v>44250</v>
+        <v>100</v>
       </c>
       <c r="G10" s="1">
         <v>0</v>
       </c>
       <c r="H10" s="1">
-        <v>9250</v>
+        <v>100</v>
       </c>
       <c r="I10" s="1">
         <v>0</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>78</v>
+        <v>103</v>
       </c>
       <c r="K10" s="1">
         <v>0</v>
       </c>
       <c r="L10" s="1">
-        <v>35000</v>
+        <v>0</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>91</v>
+        <v>135</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>100</v>
+        <v>144</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>121</v>
+        <v>184</v>
       </c>
       <c r="P10" s="1">
-        <v>38550</v>
+        <v>0</v>
       </c>
       <c r="Q10" s="1">
-        <v>295.27</v>
+        <v>0</v>
       </c>
       <c r="R10" s="1">
-        <v>11382579.9</v>
+        <v>0</v>
       </c>
       <c r="S10" s="1" t="s">
-        <v>137</v>
+        <v>221</v>
       </c>
       <c r="T10" s="1" t="s">
-        <v>149</v>
+        <v>236</v>
       </c>
       <c r="U10" s="1">
         <v>1</v>
@@ -2036,120 +2351,123 @@
         <v>1</v>
       </c>
       <c r="W10" s="1" t="s">
-        <v>158</v>
+        <v>250</v>
       </c>
       <c r="X10" s="1" t="s">
-        <v>162</v>
+        <v>254</v>
       </c>
       <c r="Y10" s="1">
-        <v>0</v>
+        <v>1624741.28</v>
       </c>
       <c r="Z10" s="1" t="s">
-        <v>165</v>
+        <v>256</v>
       </c>
       <c r="AA10" s="1">
-        <v>1631102.31</v>
+        <v>28130</v>
       </c>
       <c r="AB10" s="1">
-        <v>5700</v>
+        <v>100</v>
       </c>
       <c r="AC10" s="1">
-        <v>13013760.81</v>
+        <v>28130</v>
       </c>
       <c r="AD10" s="1">
-        <v>294.0962894915255</v>
+        <v>281.3</v>
       </c>
       <c r="AE10" s="1">
-        <v>284.9</v>
+        <v>285</v>
       </c>
       <c r="AF10" s="1">
-        <v>12606825</v>
+        <v>28500</v>
       </c>
       <c r="AG10" s="1">
-        <v>37820.475</v>
+        <v>85.5</v>
       </c>
       <c r="AH10" s="1">
-        <v>1891.02375</v>
+        <v>4.274999999999999</v>
       </c>
       <c r="AI10" s="1">
         <v>25</v>
       </c>
       <c r="AJ10" s="1">
-        <v>446672.3087500017</v>
+        <v>-255.2249999999985</v>
       </c>
       <c r="AK10" s="1">
-        <v>33500.42315625013</v>
+        <v>-19.14187499999989</v>
       </c>
       <c r="AL10" s="1">
-        <v>-480172.73</v>
+        <v>274.37</v>
       </c>
       <c r="AM10" s="1">
-        <v>-3.69</v>
+        <v>0.98</v>
       </c>
       <c r="AN10" s="1" t="s">
-        <v>167</v>
+        <v>260</v>
+      </c>
+      <c r="AO10" s="1" t="s">
+        <v>261</v>
       </c>
     </row>
-    <row r="11" spans="1:40">
+    <row r="11" spans="1:41">
       <c r="A11" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>64</v>
+        <v>85</v>
       </c>
       <c r="C11" s="1">
-        <v>233742</v>
+        <v>243900</v>
       </c>
       <c r="D11" s="1">
         <v>11400</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="F11" s="1">
-        <v>10650</v>
+        <v>1000</v>
       </c>
       <c r="G11" s="1">
         <v>0</v>
       </c>
       <c r="H11" s="1">
-        <v>3550</v>
+        <v>0</v>
       </c>
       <c r="I11" s="1">
         <v>0</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>79</v>
+        <v>104</v>
       </c>
       <c r="K11" s="1">
         <v>0</v>
       </c>
       <c r="L11" s="1">
-        <v>7100</v>
+        <v>1000</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>91</v>
+        <v>135</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>101</v>
+        <v>145</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>122</v>
+        <v>185</v>
       </c>
       <c r="P11" s="1">
-        <v>12150</v>
+        <v>1260</v>
       </c>
       <c r="Q11" s="1">
-        <v>983.53</v>
+        <v>634.27</v>
       </c>
       <c r="R11" s="1">
-        <v>11949900.2</v>
-      </c>
-      <c r="S11" s="1">
-        <v>0</v>
-      </c>
-      <c r="T11" s="1">
-        <v>0</v>
+        <v>799177.62</v>
+      </c>
+      <c r="S11" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="T11" s="1" t="s">
+        <v>216</v>
       </c>
       <c r="U11" s="1">
         <v>0</v>
@@ -2158,13 +2476,13 @@
         <v>0</v>
       </c>
       <c r="X11" s="1" t="s">
-        <v>162</v>
+        <v>254</v>
       </c>
       <c r="Y11" s="1">
-        <v>0</v>
+        <v>1624741.28</v>
       </c>
       <c r="Z11" s="1" t="s">
-        <v>165</v>
+        <v>256</v>
       </c>
       <c r="AA11" s="1">
         <v>0</v>
@@ -2173,72 +2491,75 @@
         <v>0</v>
       </c>
       <c r="AC11" s="1">
-        <v>10474594.5</v>
+        <v>634270</v>
       </c>
       <c r="AD11" s="1">
-        <v>983.53</v>
+        <v>634.27</v>
       </c>
       <c r="AE11" s="1">
-        <v>1025.1</v>
+        <v>603.4</v>
       </c>
       <c r="AF11" s="1">
-        <v>10917315</v>
+        <v>603400</v>
       </c>
       <c r="AG11" s="1">
-        <v>32751.945</v>
+        <v>1810.2</v>
       </c>
       <c r="AH11" s="1">
-        <v>1637.59725</v>
+        <v>90.50999999999999</v>
       </c>
       <c r="AI11" s="1">
         <v>25</v>
       </c>
       <c r="AJ11" s="1">
-        <v>-408305.9577499982</v>
+        <v>32795.70999999996</v>
       </c>
       <c r="AK11" s="1">
-        <v>-30622.94683124986</v>
+        <v>2459.678249999997</v>
       </c>
       <c r="AL11" s="1">
-        <v>438928.9</v>
+        <v>-35255.39</v>
       </c>
       <c r="AM11" s="1">
-        <v>4.19</v>
+        <v>-5.56</v>
       </c>
       <c r="AN11" s="1" t="s">
-        <v>167</v>
+        <v>260</v>
+      </c>
+      <c r="AO11" s="1" t="s">
+        <v>261</v>
       </c>
     </row>
-    <row r="12" spans="1:40">
+    <row r="12" spans="1:41">
       <c r="A12" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>64</v>
+        <v>87</v>
       </c>
       <c r="C12" s="1">
-        <v>233742</v>
+        <v>216199</v>
       </c>
       <c r="D12" s="1">
         <v>11400</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="F12" s="1">
-        <v>2189</v>
+        <v>2100</v>
       </c>
       <c r="G12" s="1">
         <v>0</v>
       </c>
       <c r="H12" s="1">
-        <v>2189</v>
+        <v>2100</v>
       </c>
       <c r="I12" s="1">
         <v>0</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>80</v>
+        <v>105</v>
       </c>
       <c r="K12" s="1">
         <v>0</v>
@@ -2247,150 +2568,150 @@
         <v>0</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>91</v>
+        <v>135</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>102</v>
+        <v>146</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>123</v>
+        <v>186</v>
       </c>
       <c r="P12" s="1">
-        <v>210</v>
+        <v>12000</v>
       </c>
       <c r="Q12" s="1">
-        <v>2543.42</v>
+        <v>316.8</v>
       </c>
       <c r="R12" s="1">
-        <v>534117.8199999999</v>
+        <v>3801551.6</v>
       </c>
       <c r="S12" s="1" t="s">
-        <v>138</v>
+        <v>222</v>
       </c>
       <c r="T12" s="1" t="s">
-        <v>150</v>
+        <v>237</v>
       </c>
       <c r="U12" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V12" s="1" t="b">
         <v>1</v>
       </c>
       <c r="W12" s="1" t="s">
-        <v>159</v>
+        <v>250</v>
       </c>
       <c r="X12" s="1" t="s">
-        <v>162</v>
+        <v>255</v>
       </c>
       <c r="Y12" s="1">
         <v>0</v>
       </c>
-      <c r="Z12" s="1" t="s">
-        <v>165</v>
-      </c>
       <c r="AA12" s="1">
-        <v>4757941.258800001</v>
+        <v>631861.86</v>
       </c>
       <c r="AB12" s="1">
-        <v>1979</v>
+        <v>2100</v>
       </c>
       <c r="AC12" s="1">
-        <v>5292059.458800001</v>
+        <v>631861.86</v>
       </c>
       <c r="AD12" s="1">
-        <v>2417.56941927821</v>
+        <v>300.8866</v>
       </c>
       <c r="AE12" s="1">
-        <v>2390</v>
+        <v>291.9</v>
       </c>
       <c r="AF12" s="1">
-        <v>5231710</v>
+        <v>612990</v>
       </c>
       <c r="AG12" s="1">
-        <v>15695.13</v>
+        <v>1838.97</v>
       </c>
       <c r="AH12" s="1">
-        <v>784.7565</v>
+        <v>91.9485</v>
       </c>
       <c r="AI12" s="1">
         <v>25</v>
       </c>
       <c r="AJ12" s="1">
-        <v>76854.34530000109</v>
+        <v>20827.77850000001</v>
       </c>
       <c r="AK12" s="1">
-        <v>5764.075897500082</v>
+        <v>1562.083387500001</v>
       </c>
       <c r="AL12" s="1">
-        <v>-82618.42</v>
+        <v>-22389.86</v>
       </c>
       <c r="AM12" s="1">
-        <v>-1.56</v>
+        <v>-3.54</v>
       </c>
       <c r="AN12" s="1" t="s">
-        <v>167</v>
+        <v>260</v>
+      </c>
+      <c r="AO12" s="1" t="s">
+        <v>263</v>
       </c>
     </row>
-    <row r="13" spans="1:40">
+    <row r="13" spans="1:41">
       <c r="A13" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>64</v>
+        <v>85</v>
       </c>
       <c r="C13" s="1">
-        <v>233742</v>
+        <v>243900</v>
       </c>
       <c r="D13" s="1">
         <v>11400</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="F13" s="1">
-        <v>3000</v>
+        <v>500</v>
       </c>
       <c r="G13" s="1">
         <v>0</v>
       </c>
       <c r="H13" s="1">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="I13" s="1">
         <v>0</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>81</v>
+        <v>106</v>
       </c>
       <c r="K13" s="1">
         <v>0</v>
       </c>
       <c r="L13" s="1">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>91</v>
+        <v>135</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>103</v>
+        <v>147</v>
       </c>
       <c r="O13" s="1" t="s">
-        <v>124</v>
+        <v>187</v>
       </c>
       <c r="P13" s="1">
-        <v>3730</v>
+        <v>500</v>
       </c>
       <c r="Q13" s="1">
-        <v>770.4400000000001</v>
+        <v>871.3099999999999</v>
       </c>
       <c r="R13" s="1">
-        <v>2873726.65</v>
-      </c>
-      <c r="S13" s="1">
-        <v>0</v>
-      </c>
-      <c r="T13" s="1">
-        <v>0</v>
+        <v>435656.27</v>
+      </c>
+      <c r="S13" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="T13" s="1" t="s">
+        <v>216</v>
       </c>
       <c r="U13" s="1">
         <v>0</v>
@@ -2399,13 +2720,13 @@
         <v>0</v>
       </c>
       <c r="X13" s="1" t="s">
-        <v>162</v>
+        <v>254</v>
       </c>
       <c r="Y13" s="1">
-        <v>0</v>
+        <v>1624741.28</v>
       </c>
       <c r="Z13" s="1" t="s">
-        <v>165</v>
+        <v>256</v>
       </c>
       <c r="AA13" s="1">
         <v>0</v>
@@ -2414,316 +2735,319 @@
         <v>0</v>
       </c>
       <c r="AC13" s="1">
-        <v>2311320</v>
+        <v>435655</v>
       </c>
       <c r="AD13" s="1">
-        <v>770.4400000000001</v>
+        <v>871.3099999999999</v>
       </c>
       <c r="AE13" s="1">
-        <v>0</v>
+        <v>871.5</v>
       </c>
       <c r="AF13" s="1">
-        <v>0</v>
+        <v>435750</v>
       </c>
       <c r="AG13" s="1">
-        <v>0</v>
+        <v>1307.25</v>
       </c>
       <c r="AH13" s="1">
-        <v>0</v>
+        <v>65.3625</v>
       </c>
       <c r="AI13" s="1">
         <v>25</v>
       </c>
       <c r="AJ13" s="1">
-        <v>2311345</v>
+        <v>1302.612499999988</v>
       </c>
       <c r="AK13" s="1">
-        <v>173350.875</v>
+        <v>97.69593749999912</v>
       </c>
       <c r="AL13" s="1">
-        <v>-2484695.88</v>
+        <v>-1400.31</v>
       </c>
       <c r="AM13" s="1">
-        <v>-107.5</v>
+        <v>-0.32</v>
       </c>
       <c r="AN13" s="1" t="s">
-        <v>167</v>
+        <v>260</v>
+      </c>
+      <c r="AO13" s="1" t="s">
+        <v>261</v>
       </c>
     </row>
-    <row r="14" spans="1:40">
+    <row r="14" spans="1:41">
       <c r="A14" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>64</v>
+        <v>85</v>
       </c>
       <c r="C14" s="1">
-        <v>233742</v>
+        <v>243900</v>
       </c>
       <c r="D14" s="1">
         <v>11400</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="F14" s="1">
-        <v>16767</v>
+        <v>2000</v>
       </c>
       <c r="G14" s="1">
         <v>0</v>
       </c>
       <c r="H14" s="1">
-        <v>6111</v>
+        <v>0</v>
       </c>
       <c r="I14" s="1">
         <v>0</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="K14" s="1">
         <v>0</v>
       </c>
       <c r="L14" s="1">
-        <v>10656</v>
+        <v>2000</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>91</v>
+        <v>135</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>104</v>
+        <v>146</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>125</v>
+        <v>186</v>
       </c>
       <c r="P14" s="1">
-        <v>12446</v>
+        <v>2000</v>
       </c>
       <c r="Q14" s="1">
-        <v>593.01</v>
+        <v>295.43</v>
       </c>
       <c r="R14" s="1">
-        <v>7380609.18</v>
+        <v>590868.8</v>
       </c>
       <c r="S14" s="1" t="s">
-        <v>139</v>
+        <v>216</v>
       </c>
       <c r="T14" s="1" t="s">
-        <v>151</v>
+        <v>216</v>
       </c>
       <c r="U14" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V14" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="W14" s="1" t="s">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="X14" s="1" t="s">
-        <v>162</v>
+        <v>254</v>
       </c>
       <c r="Y14" s="1">
-        <v>0</v>
+        <v>1624741.28</v>
       </c>
       <c r="Z14" s="1" t="s">
-        <v>165</v>
+        <v>256</v>
       </c>
       <c r="AA14" s="1">
-        <v>4035437.6648</v>
+        <v>0</v>
       </c>
       <c r="AB14" s="1">
-        <v>6111</v>
+        <v>0</v>
       </c>
       <c r="AC14" s="1">
-        <v>10354552.2248</v>
+        <v>590860</v>
       </c>
       <c r="AD14" s="1">
-        <v>617.5554496809209</v>
+        <v>295.43</v>
       </c>
       <c r="AE14" s="1">
-        <v>567.9</v>
+        <v>291.9</v>
       </c>
       <c r="AF14" s="1">
-        <v>9521979.299999999</v>
+        <v>583800</v>
       </c>
       <c r="AG14" s="1">
-        <v>28565.9379</v>
+        <v>1751.4</v>
       </c>
       <c r="AH14" s="1">
-        <v>1428.296895</v>
+        <v>87.56999999999999</v>
       </c>
       <c r="AI14" s="1">
         <v>25</v>
       </c>
       <c r="AJ14" s="1">
-        <v>862592.1595949996</v>
+        <v>8923.969999999972</v>
       </c>
       <c r="AK14" s="1">
-        <v>64694.41196962497</v>
+        <v>669.2977499999979</v>
       </c>
       <c r="AL14" s="1">
-        <v>-927286.5699999999</v>
+        <v>-9593.27</v>
       </c>
       <c r="AM14" s="1">
-        <v>-8.960000000000001</v>
+        <v>-1.62</v>
       </c>
       <c r="AN14" s="1" t="s">
-        <v>167</v>
+        <v>260</v>
+      </c>
+      <c r="AO14" s="1" t="s">
+        <v>261</v>
       </c>
     </row>
-    <row r="15" spans="1:40">
+    <row r="15" spans="1:41">
       <c r="A15" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>64</v>
+        <v>89</v>
       </c>
       <c r="C15" s="1">
-        <v>233742</v>
+        <v>1744740</v>
       </c>
       <c r="D15" s="1">
-        <v>11400</v>
+        <v>12600</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>68</v>
+        <v>94</v>
       </c>
       <c r="F15" s="1">
-        <v>16650</v>
+        <v>10</v>
       </c>
       <c r="G15" s="1">
         <v>0</v>
       </c>
       <c r="H15" s="1">
-        <v>4600</v>
+        <v>10</v>
       </c>
       <c r="I15" s="1">
         <v>0</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="K15" s="1">
         <v>0</v>
       </c>
       <c r="L15" s="1">
-        <v>12050</v>
+        <v>0</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>91</v>
+        <v>135</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>105</v>
+        <v>148</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>126</v>
+        <v>188</v>
       </c>
       <c r="P15" s="1">
-        <v>20500</v>
+        <v>10</v>
       </c>
       <c r="Q15" s="1">
-        <v>653.46</v>
+        <v>100</v>
       </c>
       <c r="R15" s="1">
-        <v>13395955.45</v>
+        <v>1000</v>
       </c>
       <c r="S15" s="1" t="s">
-        <v>140</v>
+        <v>216</v>
       </c>
       <c r="T15" s="1" t="s">
-        <v>152</v>
+        <v>216</v>
       </c>
       <c r="U15" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V15" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="W15" s="1" t="s">
-        <v>158</v>
+        <v>0</v>
       </c>
       <c r="X15" s="1" t="s">
-        <v>162</v>
+        <v>254</v>
       </c>
       <c r="Y15" s="1">
         <v>0</v>
       </c>
       <c r="Z15" s="1" t="s">
-        <v>165</v>
+        <v>259</v>
       </c>
       <c r="AA15" s="1">
-        <v>1315388.715</v>
+        <v>0</v>
       </c>
       <c r="AB15" s="1">
-        <v>2650</v>
+        <v>0</v>
       </c>
       <c r="AC15" s="1">
-        <v>10463828.715</v>
+        <v>1000</v>
       </c>
       <c r="AD15" s="1">
-        <v>628.4581810810811</v>
+        <v>100</v>
       </c>
       <c r="AE15" s="1">
-        <v>525</v>
+        <v>407</v>
       </c>
       <c r="AF15" s="1">
-        <v>8741250</v>
+        <v>4070</v>
       </c>
       <c r="AG15" s="1">
-        <v>26223.75</v>
+        <v>12.21</v>
       </c>
       <c r="AH15" s="1">
-        <v>1311.1875</v>
+        <v>0.6104999999999999</v>
       </c>
       <c r="AI15" s="1">
         <v>25</v>
       </c>
       <c r="AJ15" s="1">
-        <v>1750138.6525</v>
+        <v>-3032.1795</v>
       </c>
       <c r="AK15" s="1">
-        <v>131260.3989375</v>
+        <v>-227.4134625</v>
       </c>
       <c r="AL15" s="1">
-        <v>-1881399.05</v>
+        <v>3259.59</v>
       </c>
       <c r="AM15" s="1">
-        <v>-17.98</v>
+        <v>325.96</v>
       </c>
       <c r="AN15" s="1" t="s">
-        <v>167</v>
+        <v>260</v>
+      </c>
+      <c r="AO15" s="1" t="s">
+        <v>264</v>
       </c>
     </row>
-    <row r="16" spans="1:40">
+    <row r="16" spans="1:41">
       <c r="A16" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>65</v>
+        <v>89</v>
       </c>
       <c r="C16" s="1">
-        <v>236901</v>
+        <v>1744740</v>
       </c>
       <c r="D16" s="1">
-        <v>11400</v>
+        <v>12600</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>69</v>
+        <v>94</v>
       </c>
       <c r="F16" s="1">
-        <v>3596</v>
+        <v>8</v>
       </c>
       <c r="G16" s="1">
         <v>0</v>
       </c>
       <c r="H16" s="1">
-        <v>3596</v>
+        <v>8</v>
       </c>
       <c r="I16" s="1">
         <v>0</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>84</v>
+        <v>108</v>
       </c>
       <c r="K16" s="1">
         <v>0</v>
@@ -2732,337 +3056,343 @@
         <v>0</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>91</v>
+        <v>135</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>106</v>
+        <v>149</v>
       </c>
       <c r="O16" s="1" t="s">
-        <v>127</v>
+        <v>189</v>
       </c>
       <c r="P16" s="1">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="Q16" s="1">
-        <v>0</v>
+        <v>520.5700000000001</v>
       </c>
       <c r="R16" s="1">
-        <v>0</v>
+        <v>56221.96</v>
       </c>
       <c r="S16" s="1" t="s">
-        <v>141</v>
+        <v>216</v>
       </c>
       <c r="T16" s="1" t="s">
-        <v>153</v>
+        <v>216</v>
       </c>
       <c r="U16" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V16" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="W16" s="1" t="s">
-        <v>159</v>
+        <v>0</v>
       </c>
       <c r="X16" s="1" t="s">
-        <v>162</v>
+        <v>254</v>
       </c>
       <c r="Y16" s="1">
         <v>0</v>
       </c>
       <c r="Z16" s="1" t="s">
-        <v>166</v>
+        <v>259</v>
       </c>
       <c r="AA16" s="1">
-        <v>3232526.8576</v>
+        <v>0</v>
       </c>
       <c r="AB16" s="1">
-        <v>3596</v>
+        <v>0</v>
       </c>
       <c r="AC16" s="1">
-        <v>3232526.8576</v>
+        <v>4164.56</v>
       </c>
       <c r="AD16" s="1">
-        <v>898.9229303670745</v>
+        <v>520.5700000000001</v>
       </c>
       <c r="AE16" s="1">
-        <v>884</v>
+        <v>588</v>
       </c>
       <c r="AF16" s="1">
-        <v>3178864</v>
+        <v>4704</v>
       </c>
       <c r="AG16" s="1">
-        <v>9536.592000000001</v>
+        <v>14.112</v>
       </c>
       <c r="AH16" s="1">
-        <v>476.8296</v>
+        <v>0.7055999999999999</v>
       </c>
       <c r="AI16" s="1">
         <v>25</v>
       </c>
       <c r="AJ16" s="1">
-        <v>63701.27919999976</v>
+        <v>-499.6223999999993</v>
       </c>
       <c r="AK16" s="1">
-        <v>4777.595939999982</v>
+        <v>-37.47167999999994</v>
       </c>
       <c r="AL16" s="1">
-        <v>-68478.88</v>
+        <v>537.09</v>
       </c>
       <c r="AM16" s="1">
-        <v>-2.12</v>
+        <v>12.9</v>
       </c>
       <c r="AN16" s="1" t="s">
-        <v>167</v>
+        <v>260</v>
+      </c>
+      <c r="AO16" s="1" t="s">
+        <v>264</v>
       </c>
     </row>
-    <row r="17" spans="1:40">
+    <row r="17" spans="1:41">
       <c r="A17" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>65</v>
+        <v>88</v>
       </c>
       <c r="C17" s="1">
-        <v>236901</v>
+        <v>233742</v>
       </c>
       <c r="D17" s="1">
         <v>11400</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="F17" s="1">
-        <v>11641</v>
+        <v>44250</v>
       </c>
       <c r="G17" s="1">
         <v>0</v>
       </c>
       <c r="H17" s="1">
-        <v>11641</v>
+        <v>9250</v>
       </c>
       <c r="I17" s="1">
         <v>0</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="K17" s="1">
         <v>0</v>
       </c>
       <c r="L17" s="1">
-        <v>0</v>
+        <v>35000</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>91</v>
+        <v>135</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>107</v>
+        <v>144</v>
       </c>
       <c r="O17" s="1" t="s">
-        <v>128</v>
+        <v>184</v>
       </c>
       <c r="P17" s="1">
-        <v>33241</v>
+        <v>38550</v>
       </c>
       <c r="Q17" s="1">
-        <v>256.02</v>
+        <v>295.27</v>
       </c>
       <c r="R17" s="1">
-        <v>8510258.82</v>
-      </c>
-      <c r="S17" s="1">
-        <v>0</v>
-      </c>
-      <c r="T17" s="1">
-        <v>0</v>
+        <v>11382579.9</v>
+      </c>
+      <c r="S17" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="T17" s="1" t="s">
+        <v>238</v>
       </c>
       <c r="U17" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V17" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="W17" s="1" t="s">
+        <v>250</v>
       </c>
       <c r="X17" s="1" t="s">
-        <v>162</v>
+        <v>254</v>
       </c>
       <c r="Y17" s="1">
-        <v>0</v>
+        <v>592006.89</v>
       </c>
       <c r="Z17" s="1" t="s">
-        <v>166</v>
+        <v>258</v>
       </c>
       <c r="AA17" s="1">
-        <v>0</v>
+        <v>1631102.31</v>
       </c>
       <c r="AB17" s="1">
-        <v>0</v>
+        <v>5700</v>
       </c>
       <c r="AC17" s="1">
-        <v>2980328.82</v>
+        <v>13013760.81</v>
       </c>
       <c r="AD17" s="1">
-        <v>256.02</v>
+        <v>294.0962894915255</v>
       </c>
       <c r="AE17" s="1">
-        <v>228.5</v>
+        <v>285</v>
       </c>
       <c r="AF17" s="1">
-        <v>2659968.5</v>
+        <v>12611250</v>
       </c>
       <c r="AG17" s="1">
-        <v>7979.9055</v>
+        <v>37833.75</v>
       </c>
       <c r="AH17" s="1">
-        <v>398.995275</v>
+        <v>1891.6875</v>
       </c>
       <c r="AI17" s="1">
         <v>25</v>
       </c>
       <c r="AJ17" s="1">
-        <v>328764.2207749998</v>
+        <v>442261.2475000005</v>
       </c>
       <c r="AK17" s="1">
-        <v>24657.31655812499</v>
+        <v>33169.59356250003</v>
       </c>
       <c r="AL17" s="1">
-        <v>-353421.54</v>
+        <v>-475430.84</v>
       </c>
       <c r="AM17" s="1">
-        <v>-11.86</v>
+        <v>-3.65</v>
       </c>
       <c r="AN17" s="1" t="s">
-        <v>167</v>
+        <v>260</v>
+      </c>
+      <c r="AO17" s="1" t="s">
+        <v>262</v>
       </c>
     </row>
-    <row r="18" spans="1:40">
+    <row r="18" spans="1:41">
       <c r="A18" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="C18" s="1">
-        <v>236901</v>
+        <v>243900</v>
       </c>
       <c r="D18" s="1">
         <v>11400</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>69</v>
+        <v>90</v>
       </c>
       <c r="F18" s="1">
-        <v>3200</v>
+        <v>1000</v>
       </c>
       <c r="G18" s="1">
         <v>0</v>
       </c>
       <c r="H18" s="1">
-        <v>3200</v>
+        <v>0</v>
       </c>
       <c r="I18" s="1">
         <v>0</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>86</v>
+        <v>109</v>
       </c>
       <c r="K18" s="1">
         <v>0</v>
       </c>
       <c r="L18" s="1">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>91</v>
+        <v>135</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>108</v>
+        <v>150</v>
       </c>
       <c r="O18" s="1" t="s">
-        <v>129</v>
+        <v>190</v>
       </c>
       <c r="P18" s="1">
-        <v>33241</v>
+        <v>1000</v>
       </c>
       <c r="Q18" s="1">
-        <v>256.02</v>
+        <v>477.07</v>
       </c>
       <c r="R18" s="1">
-        <v>8510258.82</v>
+        <v>477067.6</v>
       </c>
       <c r="S18" s="1" t="s">
-        <v>142</v>
+        <v>216</v>
       </c>
       <c r="T18" s="1" t="s">
-        <v>154</v>
+        <v>216</v>
       </c>
       <c r="U18" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V18" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="W18" s="1" t="s">
-        <v>159</v>
+        <v>0</v>
       </c>
       <c r="X18" s="1" t="s">
-        <v>162</v>
+        <v>254</v>
       </c>
       <c r="Y18" s="1">
-        <v>0</v>
+        <v>1624741.28</v>
       </c>
       <c r="Z18" s="1" t="s">
-        <v>166</v>
+        <v>256</v>
       </c>
       <c r="AA18" s="1">
-        <v>1209353.92</v>
+        <v>0</v>
       </c>
       <c r="AB18" s="1">
-        <v>3200</v>
+        <v>0</v>
       </c>
       <c r="AC18" s="1">
-        <v>1209353.92</v>
+        <v>477070</v>
       </c>
       <c r="AD18" s="1">
-        <v>377.9231</v>
+        <v>477.07</v>
       </c>
       <c r="AE18" s="1">
-        <v>388.9</v>
+        <v>506.1</v>
       </c>
       <c r="AF18" s="1">
-        <v>1244480</v>
+        <v>506100</v>
       </c>
       <c r="AG18" s="1">
-        <v>3733.44</v>
+        <v>1518.3</v>
       </c>
       <c r="AH18" s="1">
-        <v>186.672</v>
+        <v>75.91499999999999</v>
       </c>
       <c r="AI18" s="1">
         <v>25</v>
       </c>
       <c r="AJ18" s="1">
-        <v>-31180.96800000011</v>
+        <v>-27410.78500000003</v>
       </c>
       <c r="AK18" s="1">
-        <v>-2338.572600000008</v>
+        <v>-2055.808875000002</v>
       </c>
       <c r="AL18" s="1">
-        <v>33519.54</v>
+        <v>29466.59</v>
       </c>
       <c r="AM18" s="1">
-        <v>2.77</v>
+        <v>6.18</v>
       </c>
       <c r="AN18" s="1" t="s">
-        <v>167</v>
+        <v>260</v>
+      </c>
+      <c r="AO18" s="1" t="s">
+        <v>261</v>
       </c>
     </row>
-    <row r="19" spans="1:40">
+    <row r="19" spans="1:41">
       <c r="A19" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>65</v>
+        <v>86</v>
       </c>
       <c r="C19" s="1">
         <v>236901</v>
@@ -3071,22 +3401,22 @@
         <v>11400</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="F19" s="1">
-        <v>2416</v>
+        <v>11641</v>
       </c>
       <c r="G19" s="1">
         <v>0</v>
       </c>
       <c r="H19" s="1">
-        <v>2416</v>
+        <v>11641</v>
       </c>
       <c r="I19" s="1">
         <v>0</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>87</v>
+        <v>110</v>
       </c>
       <c r="K19" s="1">
         <v>0</v>
@@ -3095,13 +3425,13 @@
         <v>0</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>91</v>
+        <v>135</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>109</v>
+        <v>151</v>
       </c>
       <c r="O19" s="1" t="s">
-        <v>130</v>
+        <v>191</v>
       </c>
       <c r="P19" s="1">
         <v>33241</v>
@@ -3113,132 +3443,132 @@
         <v>8510258.82</v>
       </c>
       <c r="S19" s="1" t="s">
-        <v>143</v>
+        <v>216</v>
       </c>
       <c r="T19" s="1" t="s">
-        <v>155</v>
+        <v>216</v>
       </c>
       <c r="U19" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V19" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="W19" s="1" t="s">
-        <v>161</v>
+        <v>0</v>
       </c>
       <c r="X19" s="1" t="s">
-        <v>162</v>
+        <v>254</v>
       </c>
       <c r="Y19" s="1">
-        <v>0</v>
+        <v>442.24</v>
       </c>
       <c r="Z19" s="1" t="s">
-        <v>166</v>
+        <v>257</v>
       </c>
       <c r="AA19" s="1">
-        <v>1102708.0054</v>
+        <v>0</v>
       </c>
       <c r="AB19" s="1">
-        <v>2416</v>
+        <v>0</v>
       </c>
       <c r="AC19" s="1">
-        <v>1102708.0054</v>
+        <v>2980328.82</v>
       </c>
       <c r="AD19" s="1">
-        <v>456.4188764072848</v>
+        <v>256.02</v>
       </c>
       <c r="AE19" s="1">
-        <v>480</v>
+        <v>226.7</v>
       </c>
       <c r="AF19" s="1">
-        <v>1159680</v>
+        <v>2639014.7</v>
       </c>
       <c r="AG19" s="1">
-        <v>3479.04</v>
+        <v>7917.044099999999</v>
       </c>
       <c r="AH19" s="1">
-        <v>173.952</v>
+        <v>395.8522049999999</v>
       </c>
       <c r="AI19" s="1">
         <v>25</v>
       </c>
       <c r="AJ19" s="1">
-        <v>-53294.00260000001</v>
+        <v>349652.0163050001</v>
       </c>
       <c r="AK19" s="1">
-        <v>-3997.050195</v>
+        <v>26223.901222875</v>
       </c>
       <c r="AL19" s="1">
-        <v>57291.05</v>
+        <v>-375875.92</v>
       </c>
       <c r="AM19" s="1">
-        <v>5.2</v>
+        <v>-12.61</v>
       </c>
       <c r="AN19" s="1" t="s">
-        <v>167</v>
+        <v>260</v>
+      </c>
+      <c r="AO19" s="1" t="s">
+        <v>262</v>
       </c>
     </row>
-    <row r="20" spans="1:40">
+    <row r="20" spans="1:41">
       <c r="A20" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="C20" s="1">
-        <v>236901</v>
+        <v>243900</v>
       </c>
       <c r="D20" s="1">
         <v>11400</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>69</v>
+        <v>90</v>
       </c>
       <c r="F20" s="1">
-        <v>7</v>
+        <v>3761</v>
       </c>
       <c r="G20" s="1">
         <v>0</v>
       </c>
       <c r="H20" s="1">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I20" s="1">
         <v>0</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>88</v>
+        <v>111</v>
       </c>
       <c r="K20" s="1">
         <v>0</v>
       </c>
       <c r="L20" s="1">
-        <v>0</v>
+        <v>3761</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>91</v>
+        <v>135</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>110</v>
+        <v>152</v>
       </c>
       <c r="O20" s="1" t="s">
-        <v>131</v>
+        <v>192</v>
       </c>
       <c r="P20" s="1">
-        <v>11000</v>
+        <v>3761</v>
       </c>
       <c r="Q20" s="1">
-        <v>274.33</v>
+        <v>491.56</v>
       </c>
       <c r="R20" s="1">
-        <v>3017632.8</v>
-      </c>
-      <c r="S20" s="1">
-        <v>0</v>
-      </c>
-      <c r="T20" s="1">
-        <v>0</v>
+        <v>1848756.03</v>
+      </c>
+      <c r="S20" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="T20" s="1" t="s">
+        <v>216</v>
       </c>
       <c r="U20" s="1">
         <v>0</v>
@@ -3247,13 +3577,13 @@
         <v>0</v>
       </c>
       <c r="X20" s="1" t="s">
-        <v>162</v>
+        <v>254</v>
       </c>
       <c r="Y20" s="1">
-        <v>0</v>
+        <v>1624741.28</v>
       </c>
       <c r="Z20" s="1" t="s">
-        <v>166</v>
+        <v>256</v>
       </c>
       <c r="AA20" s="1">
         <v>0</v>
@@ -3262,72 +3592,75 @@
         <v>0</v>
       </c>
       <c r="AC20" s="1">
-        <v>1920.31</v>
+        <v>1848757.16</v>
       </c>
       <c r="AD20" s="1">
-        <v>274.33</v>
+        <v>491.56</v>
       </c>
       <c r="AE20" s="1">
-        <v>247.9</v>
+        <v>434.9</v>
       </c>
       <c r="AF20" s="1">
-        <v>1735.3</v>
+        <v>1635658.9</v>
       </c>
       <c r="AG20" s="1">
-        <v>5.2059</v>
+        <v>4906.9767</v>
       </c>
       <c r="AH20" s="1">
-        <v>0.2602949999999999</v>
+        <v>245.348835</v>
       </c>
       <c r="AI20" s="1">
         <v>25</v>
       </c>
       <c r="AJ20" s="1">
-        <v>215.476195</v>
+        <v>218275.5855350001</v>
       </c>
       <c r="AK20" s="1">
-        <v>16.160714625</v>
+        <v>16370.668915125</v>
       </c>
       <c r="AL20" s="1">
-        <v>-231.64</v>
+        <v>-234646.25</v>
       </c>
       <c r="AM20" s="1">
-        <v>-12.06</v>
+        <v>-12.69</v>
       </c>
       <c r="AN20" s="1" t="s">
-        <v>167</v>
+        <v>260</v>
+      </c>
+      <c r="AO20" s="1" t="s">
+        <v>261</v>
       </c>
     </row>
-    <row r="21" spans="1:40">
+    <row r="21" spans="1:41">
       <c r="A21" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>65</v>
+        <v>89</v>
       </c>
       <c r="C21" s="1">
-        <v>236901</v>
+        <v>1744740</v>
       </c>
       <c r="D21" s="1">
-        <v>11400</v>
+        <v>12600</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>69</v>
+        <v>94</v>
       </c>
       <c r="F21" s="1">
-        <v>3330</v>
+        <v>500</v>
       </c>
       <c r="G21" s="1">
         <v>0</v>
       </c>
       <c r="H21" s="1">
-        <v>3330</v>
+        <v>500</v>
       </c>
       <c r="I21" s="1">
         <v>0</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="K21" s="1">
         <v>0</v>
@@ -3336,96 +3669,99 @@
         <v>0</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>91</v>
+        <v>135</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>111</v>
+        <v>153</v>
       </c>
       <c r="O21" s="1" t="s">
-        <v>132</v>
+        <v>193</v>
       </c>
       <c r="P21" s="1">
-        <v>11000</v>
+        <v>210</v>
       </c>
       <c r="Q21" s="1">
-        <v>274.33</v>
+        <v>642.6900000000001</v>
       </c>
       <c r="R21" s="1">
-        <v>3017632.8</v>
+        <v>134964.14</v>
       </c>
       <c r="S21" s="1" t="s">
-        <v>144</v>
+        <v>224</v>
       </c>
       <c r="T21" s="1" t="s">
-        <v>156</v>
+        <v>239</v>
       </c>
       <c r="U21" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V21" s="1" t="b">
         <v>1</v>
       </c>
       <c r="W21" s="1" t="s">
-        <v>159</v>
+        <v>250</v>
       </c>
       <c r="X21" s="1" t="s">
-        <v>162</v>
+        <v>254</v>
       </c>
       <c r="Y21" s="1">
         <v>0</v>
       </c>
       <c r="Z21" s="1" t="s">
-        <v>166</v>
+        <v>259</v>
       </c>
       <c r="AA21" s="1">
-        <v>2357395.686</v>
+        <v>152097.85</v>
       </c>
       <c r="AB21" s="1">
-        <v>3330</v>
+        <v>500</v>
       </c>
       <c r="AC21" s="1">
-        <v>2357395.686</v>
+        <v>152097.85</v>
       </c>
       <c r="AD21" s="1">
-        <v>707.9266324324324</v>
+        <v>304.1957</v>
       </c>
       <c r="AE21" s="1">
-        <v>698</v>
+        <v>244</v>
       </c>
       <c r="AF21" s="1">
-        <v>2324340</v>
+        <v>122000</v>
       </c>
       <c r="AG21" s="1">
-        <v>6973.02</v>
+        <v>366</v>
       </c>
       <c r="AH21" s="1">
-        <v>348.651</v>
+        <v>18.3</v>
       </c>
       <c r="AI21" s="1">
         <v>25</v>
       </c>
       <c r="AJ21" s="1">
-        <v>40402.35699999984</v>
+        <v>30507.14999999999</v>
       </c>
       <c r="AK21" s="1">
-        <v>3030.176774999988</v>
+        <v>2288.03625</v>
       </c>
       <c r="AL21" s="1">
-        <v>-43432.53</v>
+        <v>-32795.19</v>
       </c>
       <c r="AM21" s="1">
-        <v>-1.84</v>
+        <v>-21.56</v>
       </c>
       <c r="AN21" s="1" t="s">
-        <v>167</v>
+        <v>260</v>
+      </c>
+      <c r="AO21" s="1" t="s">
+        <v>264</v>
       </c>
     </row>
-    <row r="22" spans="1:40">
+    <row r="22" spans="1:41">
       <c r="A22" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>65</v>
+        <v>86</v>
       </c>
       <c r="C22" s="1">
         <v>236901</v>
@@ -3434,22 +3770,22 @@
         <v>11400</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="F22" s="1">
-        <v>6200</v>
+        <v>2200</v>
       </c>
       <c r="G22" s="1">
         <v>0</v>
       </c>
       <c r="H22" s="1">
-        <v>6200</v>
+        <v>2200</v>
       </c>
       <c r="I22" s="1">
         <v>0</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="K22" s="1">
         <v>0</v>
@@ -3458,96 +3794,96 @@
         <v>0</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>91</v>
+        <v>135</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>96</v>
+        <v>154</v>
       </c>
       <c r="O22" s="1" t="s">
-        <v>117</v>
+        <v>194</v>
       </c>
       <c r="P22" s="1">
-        <v>11000</v>
+        <v>3300</v>
       </c>
       <c r="Q22" s="1">
-        <v>274.33</v>
+        <v>421.87</v>
       </c>
       <c r="R22" s="1">
-        <v>3017632.8</v>
+        <v>1392162.84</v>
       </c>
       <c r="S22" s="1" t="s">
-        <v>145</v>
+        <v>216</v>
       </c>
       <c r="T22" s="1" t="s">
-        <v>157</v>
+        <v>216</v>
       </c>
       <c r="U22" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V22" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="W22" s="1" t="s">
-        <v>159</v>
+        <v>0</v>
       </c>
       <c r="X22" s="1" t="s">
-        <v>162</v>
+        <v>254</v>
       </c>
       <c r="Y22" s="1">
-        <v>0</v>
+        <v>442.24</v>
       </c>
       <c r="Z22" s="1" t="s">
-        <v>166</v>
+        <v>257</v>
       </c>
       <c r="AA22" s="1">
-        <v>3557574.72</v>
+        <v>0</v>
       </c>
       <c r="AB22" s="1">
-        <v>6200</v>
+        <v>0</v>
       </c>
       <c r="AC22" s="1">
-        <v>3557574.72</v>
+        <v>928114</v>
       </c>
       <c r="AD22" s="1">
-        <v>573.8023741935483</v>
+        <v>421.87</v>
       </c>
       <c r="AE22" s="1">
-        <v>617</v>
+        <v>465</v>
       </c>
       <c r="AF22" s="1">
-        <v>3825400</v>
+        <v>1023000</v>
       </c>
       <c r="AG22" s="1">
-        <v>11476.2</v>
+        <v>3069</v>
       </c>
       <c r="AH22" s="1">
-        <v>573.8099999999999</v>
+        <v>153.45</v>
       </c>
       <c r="AI22" s="1">
         <v>25</v>
       </c>
       <c r="AJ22" s="1">
-        <v>-255750.27</v>
+        <v>-91638.55000000005</v>
       </c>
       <c r="AK22" s="1">
-        <v>-19181.27025</v>
+        <v>-6872.891250000003</v>
       </c>
       <c r="AL22" s="1">
-        <v>274931.54</v>
+        <v>98511.44</v>
       </c>
       <c r="AM22" s="1">
-        <v>7.73</v>
+        <v>10.61</v>
       </c>
       <c r="AN22" s="1" t="s">
-        <v>167</v>
+        <v>260</v>
+      </c>
+      <c r="AO22" s="1" t="s">
+        <v>262</v>
       </c>
     </row>
-    <row r="23" spans="1:40">
+    <row r="23" spans="1:41">
       <c r="A23" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>65</v>
+        <v>86</v>
       </c>
       <c r="C23" s="1">
         <v>236901</v>
@@ -3556,22 +3892,22 @@
         <v>11400</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="F23" s="1">
-        <v>2800</v>
+        <v>2416</v>
       </c>
       <c r="G23" s="1">
         <v>0</v>
       </c>
       <c r="H23" s="1">
-        <v>2800</v>
+        <v>2416</v>
       </c>
       <c r="I23" s="1">
         <v>0</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>90</v>
+        <v>114</v>
       </c>
       <c r="K23" s="1">
         <v>0</v>
@@ -3580,85 +3916,2799 @@
         <v>0</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>91</v>
+        <v>135</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>112</v>
+        <v>155</v>
       </c>
       <c r="O23" s="1" t="s">
-        <v>133</v>
+        <v>195</v>
       </c>
       <c r="P23" s="1">
-        <v>3300</v>
+        <v>33241</v>
       </c>
       <c r="Q23" s="1">
-        <v>421.87</v>
+        <v>256.02</v>
       </c>
       <c r="R23" s="1">
-        <v>1392162.84</v>
-      </c>
-      <c r="S23" s="1">
-        <v>0</v>
-      </c>
-      <c r="T23" s="1">
-        <v>0</v>
+        <v>8510258.82</v>
+      </c>
+      <c r="S23" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="T23" s="1" t="s">
+        <v>240</v>
       </c>
       <c r="U23" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V23" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="W23" s="1" t="s">
+        <v>252</v>
       </c>
       <c r="X23" s="1" t="s">
-        <v>162</v>
+        <v>254</v>
       </c>
       <c r="Y23" s="1">
-        <v>0</v>
+        <v>442.24</v>
       </c>
       <c r="Z23" s="1" t="s">
-        <v>166</v>
+        <v>257</v>
       </c>
       <c r="AA23" s="1">
-        <v>0</v>
+        <v>1102708.0054</v>
       </c>
       <c r="AB23" s="1">
-        <v>0</v>
+        <v>2416</v>
       </c>
       <c r="AC23" s="1">
-        <v>1181236</v>
+        <v>1102708.0054</v>
       </c>
       <c r="AD23" s="1">
-        <v>421.87</v>
+        <v>456.4188764072848</v>
       </c>
       <c r="AE23" s="1">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="AF23" s="1">
-        <v>1313200</v>
+        <v>1128272</v>
       </c>
       <c r="AG23" s="1">
-        <v>3939.6</v>
+        <v>3384.816</v>
       </c>
       <c r="AH23" s="1">
-        <v>196.98</v>
+        <v>169.2408</v>
       </c>
       <c r="AI23" s="1">
         <v>25</v>
       </c>
       <c r="AJ23" s="1">
-        <v>-127802.4199999999</v>
+        <v>-21984.93779999996</v>
       </c>
       <c r="AK23" s="1">
-        <v>-9585.181499999993</v>
+        <v>-1648.870334999997</v>
       </c>
       <c r="AL23" s="1">
-        <v>137387.6</v>
+        <v>23633.81</v>
       </c>
       <c r="AM23" s="1">
-        <v>11.63</v>
+        <v>2.14</v>
       </c>
       <c r="AN23" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="AO23" s="1" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="24" spans="1:41">
+      <c r="A24" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C24" s="1">
+        <v>236901</v>
+      </c>
+      <c r="D24" s="1">
+        <v>11400</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="F24" s="1">
+        <v>7</v>
+      </c>
+      <c r="G24" s="1">
+        <v>0</v>
+      </c>
+      <c r="H24" s="1">
+        <v>7</v>
+      </c>
+      <c r="I24" s="1">
+        <v>0</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="K24" s="1">
+        <v>0</v>
+      </c>
+      <c r="L24" s="1">
+        <v>0</v>
+      </c>
+      <c r="M24" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="N24" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="O24" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="P24" s="1">
+        <v>11000</v>
+      </c>
+      <c r="Q24" s="1">
+        <v>274.33</v>
+      </c>
+      <c r="R24" s="1">
+        <v>3017632.8</v>
+      </c>
+      <c r="S24" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="T24" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="U24" s="1">
+        <v>0</v>
+      </c>
+      <c r="V24" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="X24" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="Y24" s="1">
+        <v>442.24</v>
+      </c>
+      <c r="Z24" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="AA24" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB24" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC24" s="1">
+        <v>1920.31</v>
+      </c>
+      <c r="AD24" s="1">
+        <v>274.33</v>
+      </c>
+      <c r="AE24" s="1">
+        <v>249.5</v>
+      </c>
+      <c r="AF24" s="1">
+        <v>1746.5</v>
+      </c>
+      <c r="AG24" s="1">
+        <v>5.2395</v>
+      </c>
+      <c r="AH24" s="1">
+        <v>0.261975</v>
+      </c>
+      <c r="AI24" s="1">
+        <v>25</v>
+      </c>
+      <c r="AJ24" s="1">
+        <v>204.3114749999997</v>
+      </c>
+      <c r="AK24" s="1">
+        <v>15.32336062499998</v>
+      </c>
+      <c r="AL24" s="1">
+        <v>-219.63</v>
+      </c>
+      <c r="AM24" s="1">
+        <v>-11.44</v>
+      </c>
+      <c r="AN24" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="AO24" s="1" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="25" spans="1:41">
+      <c r="A25" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C25" s="1">
+        <v>243900</v>
+      </c>
+      <c r="D25" s="1">
+        <v>11400</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="F25" s="1">
+        <v>2700</v>
+      </c>
+      <c r="G25" s="1">
+        <v>0</v>
+      </c>
+      <c r="H25" s="1">
+        <v>0</v>
+      </c>
+      <c r="I25" s="1">
+        <v>0</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="K25" s="1">
+        <v>0</v>
+      </c>
+      <c r="L25" s="1">
+        <v>2700</v>
+      </c>
+      <c r="M25" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="N25" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="O25" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="P25" s="1">
+        <v>2700</v>
+      </c>
+      <c r="Q25" s="1">
+        <v>695.29</v>
+      </c>
+      <c r="R25" s="1">
+        <v>1877295.31</v>
+      </c>
+      <c r="S25" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="T25" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="U25" s="1">
+        <v>0</v>
+      </c>
+      <c r="V25" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="X25" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="Y25" s="1">
+        <v>1624741.28</v>
+      </c>
+      <c r="Z25" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="AA25" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB25" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC25" s="1">
+        <v>1877283</v>
+      </c>
+      <c r="AD25" s="1">
+        <v>695.29</v>
+      </c>
+      <c r="AE25" s="1">
+        <v>671.4</v>
+      </c>
+      <c r="AF25" s="1">
+        <v>1812780</v>
+      </c>
+      <c r="AG25" s="1">
+        <v>5438.34</v>
+      </c>
+      <c r="AH25" s="1">
+        <v>271.917</v>
+      </c>
+      <c r="AI25" s="1">
+        <v>25</v>
+      </c>
+      <c r="AJ25" s="1">
+        <v>70238.25699999998</v>
+      </c>
+      <c r="AK25" s="1">
+        <v>5267.869274999998</v>
+      </c>
+      <c r="AL25" s="1">
+        <v>-75506.13</v>
+      </c>
+      <c r="AM25" s="1">
+        <v>-4.02</v>
+      </c>
+      <c r="AN25" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="AO25" s="1" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="26" spans="1:41">
+      <c r="A26" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C26" s="1">
+        <v>243900</v>
+      </c>
+      <c r="D26" s="1">
+        <v>11400</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="F26" s="1">
+        <v>2091</v>
+      </c>
+      <c r="G26" s="1">
+        <v>0</v>
+      </c>
+      <c r="H26" s="1">
+        <v>149</v>
+      </c>
+      <c r="I26" s="1">
+        <v>0</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="K26" s="1">
+        <v>0</v>
+      </c>
+      <c r="L26" s="1">
+        <v>1942</v>
+      </c>
+      <c r="M26" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="N26" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="O26" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="P26" s="1">
+        <v>1942</v>
+      </c>
+      <c r="Q26" s="1">
+        <v>460.07</v>
+      </c>
+      <c r="R26" s="1">
+        <v>893455.16</v>
+      </c>
+      <c r="S26" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="T26" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="U26" s="1">
+        <v>1</v>
+      </c>
+      <c r="V26" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="W26" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="X26" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="Y26" s="1">
+        <v>1624741.28</v>
+      </c>
+      <c r="Z26" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="AA26" s="1">
+        <v>60877.2131</v>
+      </c>
+      <c r="AB26" s="1">
+        <v>149</v>
+      </c>
+      <c r="AC26" s="1">
+        <v>954333.1531</v>
+      </c>
+      <c r="AD26" s="1">
+        <v>456.4003601626016</v>
+      </c>
+      <c r="AE26" s="1">
+        <v>396.5</v>
+      </c>
+      <c r="AF26" s="1">
+        <v>829081.5</v>
+      </c>
+      <c r="AG26" s="1">
+        <v>2487.2445</v>
+      </c>
+      <c r="AH26" s="1">
+        <v>124.362225</v>
+      </c>
+      <c r="AI26" s="1">
+        <v>25</v>
+      </c>
+      <c r="AJ26" s="1">
+        <v>127888.2598250001</v>
+      </c>
+      <c r="AK26" s="1">
+        <v>9591.619486875004</v>
+      </c>
+      <c r="AL26" s="1">
+        <v>-137479.88</v>
+      </c>
+      <c r="AM26" s="1">
+        <v>-14.41</v>
+      </c>
+      <c r="AN26" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="AO26" s="1" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="27" spans="1:41">
+      <c r="A27" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C27" s="1">
+        <v>243900</v>
+      </c>
+      <c r="D27" s="1">
+        <v>11400</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="F27" s="1">
+        <v>1000</v>
+      </c>
+      <c r="G27" s="1">
+        <v>0</v>
+      </c>
+      <c r="H27" s="1">
+        <v>1000</v>
+      </c>
+      <c r="I27" s="1">
+        <v>0</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="K27" s="1">
+        <v>0</v>
+      </c>
+      <c r="L27" s="1">
+        <v>0</v>
+      </c>
+      <c r="M27" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="N27" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="O27" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="P27" s="1">
+        <v>500</v>
+      </c>
+      <c r="Q27" s="1">
+        <v>209.5</v>
+      </c>
+      <c r="R27" s="1">
+        <v>104748.45</v>
+      </c>
+      <c r="S27" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="T27" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="U27" s="1">
+        <v>1</v>
+      </c>
+      <c r="V27" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="W27" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="X27" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="Y27" s="1">
+        <v>1624741.28</v>
+      </c>
+      <c r="Z27" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="AA27" s="1">
+        <v>95854.5</v>
+      </c>
+      <c r="AB27" s="1">
+        <v>500</v>
+      </c>
+      <c r="AC27" s="1">
+        <v>200604.5</v>
+      </c>
+      <c r="AD27" s="1">
+        <v>200.6045</v>
+      </c>
+      <c r="AE27" s="1">
+        <v>190</v>
+      </c>
+      <c r="AF27" s="1">
+        <v>190000</v>
+      </c>
+      <c r="AG27" s="1">
+        <v>570</v>
+      </c>
+      <c r="AH27" s="1">
+        <v>28.5</v>
+      </c>
+      <c r="AI27" s="1">
+        <v>25</v>
+      </c>
+      <c r="AJ27" s="1">
+        <v>11228</v>
+      </c>
+      <c r="AK27" s="1">
+        <v>842.1</v>
+      </c>
+      <c r="AL27" s="1">
+        <v>-12070.1</v>
+      </c>
+      <c r="AM27" s="1">
+        <v>-6.02</v>
+      </c>
+      <c r="AN27" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="AO27" s="1" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="28" spans="1:41">
+      <c r="A28" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C28" s="1">
+        <v>233742</v>
+      </c>
+      <c r="D28" s="1">
+        <v>11400</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="F28" s="1">
+        <v>3000</v>
+      </c>
+      <c r="G28" s="1">
+        <v>0</v>
+      </c>
+      <c r="H28" s="1">
+        <v>3000</v>
+      </c>
+      <c r="I28" s="1">
+        <v>0</v>
+      </c>
+      <c r="J28" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="K28" s="1">
+        <v>0</v>
+      </c>
+      <c r="L28" s="1">
+        <v>0</v>
+      </c>
+      <c r="M28" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="N28" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="O28" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="P28" s="1">
+        <v>3730</v>
+      </c>
+      <c r="Q28" s="1">
+        <v>770.4400000000001</v>
+      </c>
+      <c r="R28" s="1">
+        <v>2873726.65</v>
+      </c>
+      <c r="S28" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="T28" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="U28" s="1">
+        <v>0</v>
+      </c>
+      <c r="V28" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="X28" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="Y28" s="1">
+        <v>592006.89</v>
+      </c>
+      <c r="Z28" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="AA28" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB28" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC28" s="1">
+        <v>2311320</v>
+      </c>
+      <c r="AD28" s="1">
+        <v>770.4400000000001</v>
+      </c>
+      <c r="AE28" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF28" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG28" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH28" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI28" s="1">
+        <v>25</v>
+      </c>
+      <c r="AJ28" s="1">
+        <v>2311345</v>
+      </c>
+      <c r="AK28" s="1">
+        <v>173350.875</v>
+      </c>
+      <c r="AL28" s="1">
+        <v>-2484695.88</v>
+      </c>
+      <c r="AM28" s="1">
+        <v>-107.5</v>
+      </c>
+      <c r="AN28" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="AO28" s="1" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="29" spans="1:41">
+      <c r="A29" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C29" s="1">
+        <v>243900</v>
+      </c>
+      <c r="D29" s="1">
+        <v>11400</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="F29" s="1">
+        <v>1000</v>
+      </c>
+      <c r="G29" s="1">
+        <v>0</v>
+      </c>
+      <c r="H29" s="1">
+        <v>1000</v>
+      </c>
+      <c r="I29" s="1">
+        <v>0</v>
+      </c>
+      <c r="J29" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="K29" s="1">
+        <v>0</v>
+      </c>
+      <c r="L29" s="1">
+        <v>0</v>
+      </c>
+      <c r="M29" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="N29" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="O29" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="P29" s="1">
+        <v>1000</v>
+      </c>
+      <c r="Q29" s="1">
+        <v>603.35</v>
+      </c>
+      <c r="R29" s="1">
+        <v>603349.3</v>
+      </c>
+      <c r="S29" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="T29" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="U29" s="1">
+        <v>0</v>
+      </c>
+      <c r="V29" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="X29" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="Y29" s="1">
+        <v>1624741.28</v>
+      </c>
+      <c r="Z29" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="AA29" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="1">
+        <v>603350</v>
+      </c>
+      <c r="AD29" s="1">
+        <v>603.35</v>
+      </c>
+      <c r="AE29" s="1">
+        <v>588</v>
+      </c>
+      <c r="AF29" s="1">
+        <v>588000</v>
+      </c>
+      <c r="AG29" s="1">
+        <v>1764</v>
+      </c>
+      <c r="AH29" s="1">
+        <v>88.19999999999999</v>
+      </c>
+      <c r="AI29" s="1">
+        <v>25</v>
+      </c>
+      <c r="AJ29" s="1">
+        <v>17227.19999999995</v>
+      </c>
+      <c r="AK29" s="1">
+        <v>1292.039999999997</v>
+      </c>
+      <c r="AL29" s="1">
+        <v>-18519.24</v>
+      </c>
+      <c r="AM29" s="1">
+        <v>-3.07</v>
+      </c>
+      <c r="AN29" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="AO29" s="1" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="30" spans="1:41">
+      <c r="A30" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C30" s="1">
+        <v>236901</v>
+      </c>
+      <c r="D30" s="1">
+        <v>11400</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="F30" s="1">
+        <v>6200</v>
+      </c>
+      <c r="G30" s="1">
+        <v>0</v>
+      </c>
+      <c r="H30" s="1">
+        <v>6200</v>
+      </c>
+      <c r="I30" s="1">
+        <v>0</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="K30" s="1">
+        <v>0</v>
+      </c>
+      <c r="L30" s="1">
+        <v>0</v>
+      </c>
+      <c r="M30" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="N30" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="O30" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="P30" s="1">
+        <v>11000</v>
+      </c>
+      <c r="Q30" s="1">
+        <v>274.33</v>
+      </c>
+      <c r="R30" s="1">
+        <v>3017632.8</v>
+      </c>
+      <c r="S30" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="T30" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="U30" s="1">
+        <v>2</v>
+      </c>
+      <c r="V30" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="W30" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="X30" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="Y30" s="1">
+        <v>442.24</v>
+      </c>
+      <c r="Z30" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="AA30" s="1">
+        <v>3557574.72</v>
+      </c>
+      <c r="AB30" s="1">
+        <v>6200</v>
+      </c>
+      <c r="AC30" s="1">
+        <v>3557574.72</v>
+      </c>
+      <c r="AD30" s="1">
+        <v>573.8023741935483</v>
+      </c>
+      <c r="AE30" s="1">
+        <v>588</v>
+      </c>
+      <c r="AF30" s="1">
+        <v>3645600</v>
+      </c>
+      <c r="AG30" s="1">
+        <v>10936.8</v>
+      </c>
+      <c r="AH30" s="1">
+        <v>546.8399999999999</v>
+      </c>
+      <c r="AI30" s="1">
+        <v>25</v>
+      </c>
+      <c r="AJ30" s="1">
+        <v>-76516.6400000006</v>
+      </c>
+      <c r="AK30" s="1">
+        <v>-5738.748000000044</v>
+      </c>
+      <c r="AL30" s="1">
+        <v>82255.39</v>
+      </c>
+      <c r="AM30" s="1">
+        <v>2.31</v>
+      </c>
+      <c r="AN30" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="AO30" s="1" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="31" spans="1:41">
+      <c r="A31" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C31" s="1">
+        <v>243900</v>
+      </c>
+      <c r="D31" s="1">
+        <v>11400</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="F31" s="1">
+        <v>1185</v>
+      </c>
+      <c r="G31" s="1">
+        <v>0</v>
+      </c>
+      <c r="H31" s="1">
+        <v>0</v>
+      </c>
+      <c r="I31" s="1">
+        <v>0</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="K31" s="1">
+        <v>0</v>
+      </c>
+      <c r="L31" s="1">
+        <v>1185</v>
+      </c>
+      <c r="M31" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="N31" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="O31" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="P31" s="1">
+        <v>1185</v>
+      </c>
+      <c r="Q31" s="1">
+        <v>366.85</v>
+      </c>
+      <c r="R31" s="1">
+        <v>434714.46</v>
+      </c>
+      <c r="S31" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="T31" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="U31" s="1">
+        <v>0</v>
+      </c>
+      <c r="V31" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="X31" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="Y31" s="1">
+        <v>1624741.28</v>
+      </c>
+      <c r="Z31" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="AA31" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB31" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC31" s="1">
+        <v>434717.25</v>
+      </c>
+      <c r="AD31" s="1">
+        <v>366.85</v>
+      </c>
+      <c r="AE31" s="1">
+        <v>320</v>
+      </c>
+      <c r="AF31" s="1">
+        <v>379200</v>
+      </c>
+      <c r="AG31" s="1">
+        <v>1137.6</v>
+      </c>
+      <c r="AH31" s="1">
+        <v>56.88</v>
+      </c>
+      <c r="AI31" s="1">
+        <v>25</v>
+      </c>
+      <c r="AJ31" s="1">
+        <v>56736.72999999998</v>
+      </c>
+      <c r="AK31" s="1">
+        <v>4255.254749999998</v>
+      </c>
+      <c r="AL31" s="1">
+        <v>-60991.98</v>
+      </c>
+      <c r="AM31" s="1">
+        <v>-14.03</v>
+      </c>
+      <c r="AN31" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="AO31" s="1" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="32" spans="1:41">
+      <c r="A32" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C32" s="1">
+        <v>233742</v>
+      </c>
+      <c r="D32" s="1">
+        <v>11400</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="F32" s="1">
+        <v>10650</v>
+      </c>
+      <c r="G32" s="1">
+        <v>0</v>
+      </c>
+      <c r="H32" s="1">
+        <v>3550</v>
+      </c>
+      <c r="I32" s="1">
+        <v>0</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="K32" s="1">
+        <v>0</v>
+      </c>
+      <c r="L32" s="1">
+        <v>7100</v>
+      </c>
+      <c r="M32" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="N32" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="O32" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="P32" s="1">
+        <v>12150</v>
+      </c>
+      <c r="Q32" s="1">
+        <v>983.53</v>
+      </c>
+      <c r="R32" s="1">
+        <v>11949900.2</v>
+      </c>
+      <c r="S32" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="T32" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="U32" s="1">
+        <v>0</v>
+      </c>
+      <c r="V32" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="X32" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="Y32" s="1">
+        <v>592006.89</v>
+      </c>
+      <c r="Z32" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="AA32" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC32" s="1">
+        <v>10474594.5</v>
+      </c>
+      <c r="AD32" s="1">
+        <v>983.53</v>
+      </c>
+      <c r="AE32" s="1">
+        <v>1031.1</v>
+      </c>
+      <c r="AF32" s="1">
+        <v>10981215</v>
+      </c>
+      <c r="AG32" s="1">
+        <v>32943.645</v>
+      </c>
+      <c r="AH32" s="1">
+        <v>1647.18225</v>
+      </c>
+      <c r="AI32" s="1">
+        <v>25</v>
+      </c>
+      <c r="AJ32" s="1">
+        <v>-472004.672749998</v>
+      </c>
+      <c r="AK32" s="1">
+        <v>-35400.35045624985</v>
+      </c>
+      <c r="AL32" s="1">
+        <v>507405.02</v>
+      </c>
+      <c r="AM32" s="1">
+        <v>4.84</v>
+      </c>
+      <c r="AN32" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="AO32" s="1" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="33" spans="1:41">
+      <c r="A33" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C33" s="1">
+        <v>243900</v>
+      </c>
+      <c r="D33" s="1">
+        <v>11400</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="F33" s="1">
+        <v>10501</v>
+      </c>
+      <c r="G33" s="1">
+        <v>0</v>
+      </c>
+      <c r="H33" s="1">
+        <v>10501</v>
+      </c>
+      <c r="I33" s="1">
+        <v>0</v>
+      </c>
+      <c r="J33" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="K33" s="1">
+        <v>0</v>
+      </c>
+      <c r="L33" s="1">
+        <v>0</v>
+      </c>
+      <c r="M33" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="N33" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="O33" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="P33" s="1">
+        <v>2700</v>
+      </c>
+      <c r="Q33" s="1">
+        <v>695.29</v>
+      </c>
+      <c r="R33" s="1">
+        <v>1877295.31</v>
+      </c>
+      <c r="S33" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="T33" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="U33" s="1">
+        <v>1</v>
+      </c>
+      <c r="V33" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="W33" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="X33" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="Y33" s="1">
+        <v>1624741.28</v>
+      </c>
+      <c r="Z33" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="AA33" s="1">
+        <v>1050100</v>
+      </c>
+      <c r="AB33" s="1">
+        <v>10501</v>
+      </c>
+      <c r="AC33" s="1">
+        <v>1050100</v>
+      </c>
+      <c r="AD33" s="1">
+        <v>100</v>
+      </c>
+      <c r="AE33" s="1">
+        <v>290</v>
+      </c>
+      <c r="AF33" s="1">
+        <v>3045290</v>
+      </c>
+      <c r="AG33" s="1">
+        <v>9135.870000000001</v>
+      </c>
+      <c r="AH33" s="1">
+        <v>456.7934999999999</v>
+      </c>
+      <c r="AI33" s="1">
+        <v>25</v>
+      </c>
+      <c r="AJ33" s="1">
+        <v>-1985572.3365</v>
+      </c>
+      <c r="AK33" s="1">
+        <v>-148917.9252375</v>
+      </c>
+      <c r="AL33" s="1">
+        <v>2134490.26</v>
+      </c>
+      <c r="AM33" s="1">
+        <v>203.27</v>
+      </c>
+      <c r="AN33" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="AO33" s="1" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="34" spans="1:41">
+      <c r="A34" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C34" s="1">
+        <v>1744740</v>
+      </c>
+      <c r="D34" s="1">
+        <v>12600</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="F34" s="1">
+        <v>10</v>
+      </c>
+      <c r="G34" s="1">
+        <v>0</v>
+      </c>
+      <c r="H34" s="1">
+        <v>10</v>
+      </c>
+      <c r="I34" s="1">
+        <v>0</v>
+      </c>
+      <c r="J34" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="K34" s="1">
+        <v>0</v>
+      </c>
+      <c r="L34" s="1">
+        <v>0</v>
+      </c>
+      <c r="M34" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="N34" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="O34" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="P34" s="1">
+        <v>210</v>
+      </c>
+      <c r="Q34" s="1">
+        <v>642.6900000000001</v>
+      </c>
+      <c r="R34" s="1">
+        <v>134964.14</v>
+      </c>
+      <c r="S34" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="T34" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="U34" s="1">
+        <v>0</v>
+      </c>
+      <c r="V34" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="X34" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="Y34" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z34" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="AA34" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB34" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC34" s="1">
+        <v>6426.900000000001</v>
+      </c>
+      <c r="AD34" s="1">
+        <v>642.6900000000001</v>
+      </c>
+      <c r="AE34" s="1">
+        <v>649.9</v>
+      </c>
+      <c r="AF34" s="1">
+        <v>6499</v>
+      </c>
+      <c r="AG34" s="1">
+        <v>19.497</v>
+      </c>
+      <c r="AH34" s="1">
+        <v>0.9748499999999999</v>
+      </c>
+      <c r="AI34" s="1">
+        <v>25</v>
+      </c>
+      <c r="AJ34" s="1">
+        <v>-26.62814999999955</v>
+      </c>
+      <c r="AK34" s="1">
+        <v>-1.997111249999966</v>
+      </c>
+      <c r="AL34" s="1">
+        <v>28.63</v>
+      </c>
+      <c r="AM34" s="1">
+        <v>0.45</v>
+      </c>
+      <c r="AN34" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="AO34" s="1" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="35" spans="1:41">
+      <c r="A35" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C35" s="1">
+        <v>243900</v>
+      </c>
+      <c r="D35" s="1">
+        <v>11400</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="F35" s="1">
+        <v>1512</v>
+      </c>
+      <c r="G35" s="1">
+        <v>0</v>
+      </c>
+      <c r="H35" s="1">
+        <v>0</v>
+      </c>
+      <c r="I35" s="1">
+        <v>0</v>
+      </c>
+      <c r="J35" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="K35" s="1">
+        <v>0</v>
+      </c>
+      <c r="L35" s="1">
+        <v>1512</v>
+      </c>
+      <c r="M35" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="N35" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="O35" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="P35" s="1">
+        <v>1512</v>
+      </c>
+      <c r="Q35" s="1">
+        <v>430.74</v>
+      </c>
+      <c r="R35" s="1">
+        <v>651284.9300000001</v>
+      </c>
+      <c r="S35" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="T35" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="U35" s="1">
+        <v>0</v>
+      </c>
+      <c r="V35" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="X35" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="Y35" s="1">
+        <v>1624741.28</v>
+      </c>
+      <c r="Z35" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="AA35" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB35" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC35" s="1">
+        <v>651278.88</v>
+      </c>
+      <c r="AD35" s="1">
+        <v>430.74</v>
+      </c>
+      <c r="AE35" s="1">
+        <v>406</v>
+      </c>
+      <c r="AF35" s="1">
+        <v>613872</v>
+      </c>
+      <c r="AG35" s="1">
+        <v>1841.616</v>
+      </c>
+      <c r="AH35" s="1">
+        <v>92.0808</v>
+      </c>
+      <c r="AI35" s="1">
+        <v>25</v>
+      </c>
+      <c r="AJ35" s="1">
+        <v>39365.57680000004</v>
+      </c>
+      <c r="AK35" s="1">
+        <v>2952.418260000003</v>
+      </c>
+      <c r="AL35" s="1">
+        <v>-42318</v>
+      </c>
+      <c r="AM35" s="1">
+        <v>-6.5</v>
+      </c>
+      <c r="AN35" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="AO35" s="1" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="36" spans="1:41">
+      <c r="A36" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C36" s="1">
+        <v>236901</v>
+      </c>
+      <c r="D36" s="1">
+        <v>11400</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="F36" s="1">
+        <v>3596</v>
+      </c>
+      <c r="G36" s="1">
+        <v>0</v>
+      </c>
+      <c r="H36" s="1">
+        <v>3596</v>
+      </c>
+      <c r="I36" s="1">
+        <v>0</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="K36" s="1">
+        <v>0</v>
+      </c>
+      <c r="L36" s="1">
+        <v>0</v>
+      </c>
+      <c r="M36" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="N36" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="O36" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="P36" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="1">
+        <v>0</v>
+      </c>
+      <c r="R36" s="1">
+        <v>0</v>
+      </c>
+      <c r="S36" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="T36" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="U36" s="1">
+        <v>2</v>
+      </c>
+      <c r="V36" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="W36" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="X36" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="Y36" s="1">
+        <v>442.24</v>
+      </c>
+      <c r="Z36" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="AA36" s="1">
+        <v>3232526.8576</v>
+      </c>
+      <c r="AB36" s="1">
+        <v>3596</v>
+      </c>
+      <c r="AC36" s="1">
+        <v>3232526.8576</v>
+      </c>
+      <c r="AD36" s="1">
+        <v>898.9229303670745</v>
+      </c>
+      <c r="AE36" s="1">
+        <v>875</v>
+      </c>
+      <c r="AF36" s="1">
+        <v>3146500</v>
+      </c>
+      <c r="AG36" s="1">
+        <v>9439.5</v>
+      </c>
+      <c r="AH36" s="1">
+        <v>471.975</v>
+      </c>
+      <c r="AI36" s="1">
+        <v>25</v>
+      </c>
+      <c r="AJ36" s="1">
+        <v>95963.33259999985</v>
+      </c>
+      <c r="AK36" s="1">
+        <v>7197.249944999989</v>
+      </c>
+      <c r="AL36" s="1">
+        <v>-103160.58</v>
+      </c>
+      <c r="AM36" s="1">
+        <v>-3.19</v>
+      </c>
+      <c r="AN36" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="AO36" s="1" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="37" spans="1:41">
+      <c r="A37" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C37" s="1">
+        <v>243900</v>
+      </c>
+      <c r="D37" s="1">
+        <v>11400</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="F37" s="1">
+        <v>1500</v>
+      </c>
+      <c r="G37" s="1">
+        <v>0</v>
+      </c>
+      <c r="H37" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I37" s="1">
+        <v>0</v>
+      </c>
+      <c r="J37" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="K37" s="1">
+        <v>0</v>
+      </c>
+      <c r="L37" s="1">
+        <v>0</v>
+      </c>
+      <c r="M37" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="N37" s="1" t="s">
         <v>167</v>
+      </c>
+      <c r="O37" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="P37" s="1">
+        <v>1500</v>
+      </c>
+      <c r="Q37" s="1">
+        <v>212.56</v>
+      </c>
+      <c r="R37" s="1">
+        <v>318846.05</v>
+      </c>
+      <c r="S37" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="T37" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="U37" s="1">
+        <v>0</v>
+      </c>
+      <c r="V37" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="X37" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="Y37" s="1">
+        <v>1624741.28</v>
+      </c>
+      <c r="Z37" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="AA37" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB37" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC37" s="1">
+        <v>318840</v>
+      </c>
+      <c r="AD37" s="1">
+        <v>212.56</v>
+      </c>
+      <c r="AE37" s="1">
+        <v>181.9</v>
+      </c>
+      <c r="AF37" s="1">
+        <v>272850</v>
+      </c>
+      <c r="AG37" s="1">
+        <v>818.5500000000001</v>
+      </c>
+      <c r="AH37" s="1">
+        <v>40.92749999999999</v>
+      </c>
+      <c r="AI37" s="1">
+        <v>25</v>
+      </c>
+      <c r="AJ37" s="1">
+        <v>46874.47749999998</v>
+      </c>
+      <c r="AK37" s="1">
+        <v>3515.585812499998</v>
+      </c>
+      <c r="AL37" s="1">
+        <v>-50390.06</v>
+      </c>
+      <c r="AM37" s="1">
+        <v>-15.8</v>
+      </c>
+      <c r="AN37" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="AO37" s="1" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="38" spans="1:41">
+      <c r="A38" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C38" s="1">
+        <v>1744740</v>
+      </c>
+      <c r="D38" s="1">
+        <v>12600</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="F38" s="1">
+        <v>13</v>
+      </c>
+      <c r="G38" s="1">
+        <v>0</v>
+      </c>
+      <c r="H38" s="1">
+        <v>13</v>
+      </c>
+      <c r="I38" s="1">
+        <v>0</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="K38" s="1">
+        <v>0</v>
+      </c>
+      <c r="L38" s="1">
+        <v>0</v>
+      </c>
+      <c r="M38" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="N38" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="O38" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="P38" s="1">
+        <v>13</v>
+      </c>
+      <c r="Q38" s="1">
+        <v>100</v>
+      </c>
+      <c r="R38" s="1">
+        <v>1300</v>
+      </c>
+      <c r="S38" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="T38" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="U38" s="1">
+        <v>0</v>
+      </c>
+      <c r="V38" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="X38" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="Y38" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z38" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="AA38" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB38" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC38" s="1">
+        <v>1300</v>
+      </c>
+      <c r="AD38" s="1">
+        <v>100</v>
+      </c>
+      <c r="AE38" s="1">
+        <v>1538</v>
+      </c>
+      <c r="AF38" s="1">
+        <v>19994</v>
+      </c>
+      <c r="AG38" s="1">
+        <v>59.982</v>
+      </c>
+      <c r="AH38" s="1">
+        <v>2.9991</v>
+      </c>
+      <c r="AI38" s="1">
+        <v>25</v>
+      </c>
+      <c r="AJ38" s="1">
+        <v>-18606.0189</v>
+      </c>
+      <c r="AK38" s="1">
+        <v>-1395.4514175</v>
+      </c>
+      <c r="AL38" s="1">
+        <v>20001.47</v>
+      </c>
+      <c r="AM38" s="1">
+        <v>1538.57</v>
+      </c>
+      <c r="AN38" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="AO38" s="1" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="39" spans="1:41">
+      <c r="A39" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C39" s="1">
+        <v>243900</v>
+      </c>
+      <c r="D39" s="1">
+        <v>11400</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="F39" s="1">
+        <v>2006</v>
+      </c>
+      <c r="G39" s="1">
+        <v>0</v>
+      </c>
+      <c r="H39" s="1">
+        <v>2006</v>
+      </c>
+      <c r="I39" s="1">
+        <v>0</v>
+      </c>
+      <c r="J39" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="K39" s="1">
+        <v>0</v>
+      </c>
+      <c r="L39" s="1">
+        <v>0</v>
+      </c>
+      <c r="M39" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="N39" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="O39" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="P39" s="1">
+        <v>3197</v>
+      </c>
+      <c r="Q39" s="1">
+        <v>851.5599999999999</v>
+      </c>
+      <c r="R39" s="1">
+        <v>2722441.78</v>
+      </c>
+      <c r="S39" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="T39" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="U39" s="1">
+        <v>0</v>
+      </c>
+      <c r="V39" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="X39" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="Y39" s="1">
+        <v>1624741.28</v>
+      </c>
+      <c r="Z39" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="AA39" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB39" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC39" s="1">
+        <v>1708229.36</v>
+      </c>
+      <c r="AD39" s="1">
+        <v>851.5599999999999</v>
+      </c>
+      <c r="AE39" s="1">
+        <v>828</v>
+      </c>
+      <c r="AF39" s="1">
+        <v>1660968</v>
+      </c>
+      <c r="AG39" s="1">
+        <v>4982.904</v>
+      </c>
+      <c r="AH39" s="1">
+        <v>249.1452</v>
+      </c>
+      <c r="AI39" s="1">
+        <v>25</v>
+      </c>
+      <c r="AJ39" s="1">
+        <v>52518.40919999988</v>
+      </c>
+      <c r="AK39" s="1">
+        <v>3938.880689999991</v>
+      </c>
+      <c r="AL39" s="1">
+        <v>-56457.29</v>
+      </c>
+      <c r="AM39" s="1">
+        <v>-3.31</v>
+      </c>
+      <c r="AN39" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="AO39" s="1" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="40" spans="1:41">
+      <c r="A40" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C40" s="1">
+        <v>233742</v>
+      </c>
+      <c r="D40" s="1">
+        <v>11400</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="F40" s="1">
+        <v>2189</v>
+      </c>
+      <c r="G40" s="1">
+        <v>0</v>
+      </c>
+      <c r="H40" s="1">
+        <v>2189</v>
+      </c>
+      <c r="I40" s="1">
+        <v>0</v>
+      </c>
+      <c r="J40" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="K40" s="1">
+        <v>0</v>
+      </c>
+      <c r="L40" s="1">
+        <v>0</v>
+      </c>
+      <c r="M40" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="N40" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="O40" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="P40" s="1">
+        <v>210</v>
+      </c>
+      <c r="Q40" s="1">
+        <v>2543.42</v>
+      </c>
+      <c r="R40" s="1">
+        <v>534117.8199999999</v>
+      </c>
+      <c r="S40" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="T40" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="U40" s="1">
+        <v>2</v>
+      </c>
+      <c r="V40" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="W40" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="X40" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="Y40" s="1">
+        <v>592006.89</v>
+      </c>
+      <c r="Z40" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="AA40" s="1">
+        <v>4757941.258800001</v>
+      </c>
+      <c r="AB40" s="1">
+        <v>1979</v>
+      </c>
+      <c r="AC40" s="1">
+        <v>5292059.458800001</v>
+      </c>
+      <c r="AD40" s="1">
+        <v>2417.56941927821</v>
+      </c>
+      <c r="AE40" s="1">
+        <v>2350</v>
+      </c>
+      <c r="AF40" s="1">
+        <v>5144150</v>
+      </c>
+      <c r="AG40" s="1">
+        <v>15432.45</v>
+      </c>
+      <c r="AH40" s="1">
+        <v>771.6224999999999</v>
+      </c>
+      <c r="AI40" s="1">
+        <v>25</v>
+      </c>
+      <c r="AJ40" s="1">
+        <v>164138.5313000008</v>
+      </c>
+      <c r="AK40" s="1">
+        <v>12310.38984750006</v>
+      </c>
+      <c r="AL40" s="1">
+        <v>-176448.92</v>
+      </c>
+      <c r="AM40" s="1">
+        <v>-3.33</v>
+      </c>
+      <c r="AN40" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="AO40" s="1" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="41" spans="1:41">
+      <c r="A41" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C41" s="1">
+        <v>243900</v>
+      </c>
+      <c r="D41" s="1">
+        <v>11400</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="F41" s="1">
+        <v>2000</v>
+      </c>
+      <c r="G41" s="1">
+        <v>0</v>
+      </c>
+      <c r="H41" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I41" s="1">
+        <v>0</v>
+      </c>
+      <c r="J41" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="K41" s="1">
+        <v>0</v>
+      </c>
+      <c r="L41" s="1">
+        <v>0</v>
+      </c>
+      <c r="M41" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="N41" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="O41" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="P41" s="1">
+        <v>1500</v>
+      </c>
+      <c r="Q41" s="1">
+        <v>291.85</v>
+      </c>
+      <c r="R41" s="1">
+        <v>437779.9</v>
+      </c>
+      <c r="S41" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="T41" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="U41" s="1">
+        <v>1</v>
+      </c>
+      <c r="V41" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="W41" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="X41" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="Y41" s="1">
+        <v>1624741.28</v>
+      </c>
+      <c r="Z41" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="AA41" s="1">
+        <v>150040.8</v>
+      </c>
+      <c r="AB41" s="1">
+        <v>500</v>
+      </c>
+      <c r="AC41" s="1">
+        <v>587815.8</v>
+      </c>
+      <c r="AD41" s="1">
+        <v>293.9079</v>
+      </c>
+      <c r="AE41" s="1">
+        <v>292.3</v>
+      </c>
+      <c r="AF41" s="1">
+        <v>584600</v>
+      </c>
+      <c r="AG41" s="1">
+        <v>1753.8</v>
+      </c>
+      <c r="AH41" s="1">
+        <v>87.69</v>
+      </c>
+      <c r="AI41" s="1">
+        <v>25</v>
+      </c>
+      <c r="AJ41" s="1">
+        <v>5082.290000000037</v>
+      </c>
+      <c r="AK41" s="1">
+        <v>381.1717500000028</v>
+      </c>
+      <c r="AL41" s="1">
+        <v>-5463.46</v>
+      </c>
+      <c r="AM41" s="1">
+        <v>-0.93</v>
+      </c>
+      <c r="AN41" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="AO41" s="1" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="42" spans="1:41">
+      <c r="A42" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C42" s="1">
+        <v>243900</v>
+      </c>
+      <c r="D42" s="1">
+        <v>11400</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="F42" s="1">
+        <v>500</v>
+      </c>
+      <c r="G42" s="1">
+        <v>0</v>
+      </c>
+      <c r="H42" s="1">
+        <v>500</v>
+      </c>
+      <c r="I42" s="1">
+        <v>0</v>
+      </c>
+      <c r="J42" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="K42" s="1">
+        <v>0</v>
+      </c>
+      <c r="L42" s="1">
+        <v>0</v>
+      </c>
+      <c r="M42" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="N42" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="O42" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="P42" s="1">
+        <v>500</v>
+      </c>
+      <c r="Q42" s="1">
+        <v>241.92</v>
+      </c>
+      <c r="R42" s="1">
+        <v>120959.65</v>
+      </c>
+      <c r="S42" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="T42" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="U42" s="1">
+        <v>0</v>
+      </c>
+      <c r="V42" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="X42" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="Y42" s="1">
+        <v>1624741.28</v>
+      </c>
+      <c r="Z42" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="AA42" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB42" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC42" s="1">
+        <v>120960</v>
+      </c>
+      <c r="AD42" s="1">
+        <v>241.92</v>
+      </c>
+      <c r="AE42" s="1">
+        <v>227</v>
+      </c>
+      <c r="AF42" s="1">
+        <v>113500</v>
+      </c>
+      <c r="AG42" s="1">
+        <v>340.5</v>
+      </c>
+      <c r="AH42" s="1">
+        <v>17.025</v>
+      </c>
+      <c r="AI42" s="1">
+        <v>25</v>
+      </c>
+      <c r="AJ42" s="1">
+        <v>7842.524999999994</v>
+      </c>
+      <c r="AK42" s="1">
+        <v>588.1893749999996</v>
+      </c>
+      <c r="AL42" s="1">
+        <v>-8430.709999999999</v>
+      </c>
+      <c r="AM42" s="1">
+        <v>-6.97</v>
+      </c>
+      <c r="AN42" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="AO42" s="1" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="43" spans="1:41">
+      <c r="A43" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C43" s="1">
+        <v>243900</v>
+      </c>
+      <c r="D43" s="1">
+        <v>11400</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="F43" s="1">
+        <v>1000</v>
+      </c>
+      <c r="G43" s="1">
+        <v>0</v>
+      </c>
+      <c r="H43" s="1">
+        <v>1000</v>
+      </c>
+      <c r="I43" s="1">
+        <v>0</v>
+      </c>
+      <c r="J43" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="K43" s="1">
+        <v>0</v>
+      </c>
+      <c r="L43" s="1">
+        <v>0</v>
+      </c>
+      <c r="M43" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="N43" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="O43" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="P43" s="1">
+        <v>1000</v>
+      </c>
+      <c r="Q43" s="1">
+        <v>257.2</v>
+      </c>
+      <c r="R43" s="1">
+        <v>257197</v>
+      </c>
+      <c r="S43" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="T43" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="U43" s="1">
+        <v>0</v>
+      </c>
+      <c r="V43" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="X43" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="Y43" s="1">
+        <v>1624741.28</v>
+      </c>
+      <c r="Z43" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="AA43" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB43" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC43" s="1">
+        <v>257200</v>
+      </c>
+      <c r="AD43" s="1">
+        <v>257.2</v>
+      </c>
+      <c r="AE43" s="1">
+        <v>244</v>
+      </c>
+      <c r="AF43" s="1">
+        <v>244000</v>
+      </c>
+      <c r="AG43" s="1">
+        <v>732</v>
+      </c>
+      <c r="AH43" s="1">
+        <v>36.59999999999999</v>
+      </c>
+      <c r="AI43" s="1">
+        <v>25</v>
+      </c>
+      <c r="AJ43" s="1">
+        <v>13993.60000000001</v>
+      </c>
+      <c r="AK43" s="1">
+        <v>1049.52</v>
+      </c>
+      <c r="AL43" s="1">
+        <v>-15043.12</v>
+      </c>
+      <c r="AM43" s="1">
+        <v>-5.85</v>
+      </c>
+      <c r="AN43" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="AO43" s="1" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="44" spans="1:41">
+      <c r="A44" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C44" s="1">
+        <v>236901</v>
+      </c>
+      <c r="D44" s="1">
+        <v>11400</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="F44" s="1">
+        <v>3330</v>
+      </c>
+      <c r="G44" s="1">
+        <v>0</v>
+      </c>
+      <c r="H44" s="1">
+        <v>3330</v>
+      </c>
+      <c r="I44" s="1">
+        <v>0</v>
+      </c>
+      <c r="J44" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="K44" s="1">
+        <v>0</v>
+      </c>
+      <c r="L44" s="1">
+        <v>0</v>
+      </c>
+      <c r="M44" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="N44" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="O44" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="P44" s="1">
+        <v>11000</v>
+      </c>
+      <c r="Q44" s="1">
+        <v>274.33</v>
+      </c>
+      <c r="R44" s="1">
+        <v>3017632.8</v>
+      </c>
+      <c r="S44" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="T44" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="U44" s="1">
+        <v>2</v>
+      </c>
+      <c r="V44" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="W44" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="X44" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="Y44" s="1">
+        <v>442.24</v>
+      </c>
+      <c r="Z44" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="AA44" s="1">
+        <v>2357395.686</v>
+      </c>
+      <c r="AB44" s="1">
+        <v>3330</v>
+      </c>
+      <c r="AC44" s="1">
+        <v>2357395.686</v>
+      </c>
+      <c r="AD44" s="1">
+        <v>707.9266324324324</v>
+      </c>
+      <c r="AE44" s="1">
+        <v>708</v>
+      </c>
+      <c r="AF44" s="1">
+        <v>2357640</v>
+      </c>
+      <c r="AG44" s="1">
+        <v>7072.92</v>
+      </c>
+      <c r="AH44" s="1">
+        <v>353.646</v>
+      </c>
+      <c r="AI44" s="1">
+        <v>25</v>
+      </c>
+      <c r="AJ44" s="1">
+        <v>7207.251999999862</v>
+      </c>
+      <c r="AK44" s="1">
+        <v>540.5438999999897</v>
+      </c>
+      <c r="AL44" s="1">
+        <v>-7747.8</v>
+      </c>
+      <c r="AM44" s="1">
+        <v>-0.33</v>
+      </c>
+      <c r="AN44" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="AO44" s="1" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="45" spans="1:41">
+      <c r="A45" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C45" s="1">
+        <v>243900</v>
+      </c>
+      <c r="D45" s="1">
+        <v>11400</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="F45" s="1">
+        <v>1500</v>
+      </c>
+      <c r="G45" s="1">
+        <v>0</v>
+      </c>
+      <c r="H45" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I45" s="1">
+        <v>0</v>
+      </c>
+      <c r="J45" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="K45" s="1">
+        <v>0</v>
+      </c>
+      <c r="L45" s="1">
+        <v>0</v>
+      </c>
+      <c r="M45" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="N45" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="O45" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="P45" s="1">
+        <v>1500</v>
+      </c>
+      <c r="Q45" s="1">
+        <v>279.33</v>
+      </c>
+      <c r="R45" s="1">
+        <v>418990.4</v>
+      </c>
+      <c r="S45" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="T45" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="U45" s="1">
+        <v>0</v>
+      </c>
+      <c r="V45" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="X45" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="Y45" s="1">
+        <v>1624741.28</v>
+      </c>
+      <c r="Z45" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="AA45" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB45" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC45" s="1">
+        <v>418995</v>
+      </c>
+      <c r="AD45" s="1">
+        <v>279.33</v>
+      </c>
+      <c r="AE45" s="1">
+        <v>251</v>
+      </c>
+      <c r="AF45" s="1">
+        <v>376500</v>
+      </c>
+      <c r="AG45" s="1">
+        <v>1129.5</v>
+      </c>
+      <c r="AH45" s="1">
+        <v>56.47499999999999</v>
+      </c>
+      <c r="AI45" s="1">
+        <v>25</v>
+      </c>
+      <c r="AJ45" s="1">
+        <v>43705.97499999998</v>
+      </c>
+      <c r="AK45" s="1">
+        <v>3277.948124999998</v>
+      </c>
+      <c r="AL45" s="1">
+        <v>-46983.92</v>
+      </c>
+      <c r="AM45" s="1">
+        <v>-11.21</v>
+      </c>
+      <c r="AN45" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="AO45" s="1" t="s">
+        <v>261</v>
       </c>
     </row>
   </sheetData>
